--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -482,6 +482,9 @@
   </x:si>
   <x:si>
     <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>AKFYE</x:t>
@@ -1433,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>149.1</x:v>
+        <x:v>149.8</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1465,7 +1468,7 @@
         <x:v>0.77</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>5.57</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.2</x:v>
@@ -1500,7 +1503,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>27.42</x:v>
+        <x:v>27.18</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1535,7 +1538,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>15.46</x:v>
+        <x:v>16.05</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1570,7 +1573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.58</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1602,7 +1605,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.82</x:v>
+        <x:v>23.36</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1637,7 +1640,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.08</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>24.8</x:v>
@@ -1672,7 +1675,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.41</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1707,7 +1710,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>40.16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1742,7 +1745,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>62</x:v>
+        <x:v>64.2</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1777,7 +1780,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.02</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1812,7 +1815,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.7</x:v>
+        <x:v>6.76</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1844,7 +1847,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>139.2</x:v>
+        <x:v>128.6</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1879,7 +1882,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.05</x:v>
+        <x:v>6.08</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1914,7 +1917,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>73</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1949,7 +1952,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.7</x:v>
+        <x:v>22.56</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1984,7 +1987,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.02</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2016,7 +2019,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>8.67</x:v>
+        <x:v>9.14</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2051,7 +2054,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>47.4</x:v>
+        <x:v>45.54</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2086,7 +2089,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>744</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2121,7 +2124,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.08</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2156,7 +2159,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.67</x:v>
+        <x:v>9.14</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2191,7 +2194,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.22</x:v>
+        <x:v>7.33</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
@@ -2226,7 +2229,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>16.82</x:v>
+        <x:v>17.07</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
@@ -2261,7 +2264,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2296,7 +2299,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.42</x:v>
+        <x:v>9.38</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2331,7 +2334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>33.76</x:v>
+        <x:v>34.7</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2363,7 +2366,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>4.38</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2398,7 +2401,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.18</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.06</x:v>
@@ -2433,7 +2436,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>44.1</x:v>
+        <x:v>44.4</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2468,7 +2471,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>76.05</x:v>
+        <x:v>76.15</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
@@ -2503,7 +2506,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>42</x:v>
+        <x:v>41.98</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2535,7 +2538,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.48</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2570,7 +2573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>38</x:v>
+        <x:v>38.3</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2602,7 +2605,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>316.75</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
@@ -2637,7 +2640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21</x:v>
+        <x:v>21.16</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2669,7 +2672,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>141.4</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
@@ -2704,7 +2707,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.26</x:v>
+        <x:v>35.7</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2736,7 +2739,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>37.72</x:v>
+        <x:v>36.9</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
@@ -2771,7 +2774,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.45</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
@@ -2806,7 +2809,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>12.07</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2838,7 +2841,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.17</x:v>
+        <x:v>8.18</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2870,7 +2873,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.39</x:v>
+        <x:v>6.43</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2905,7 +2908,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
@@ -2940,7 +2943,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>16.82</x:v>
+        <x:v>17.07</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
@@ -2975,7 +2978,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.32</x:v>
+        <x:v>23.54</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
@@ -3010,7 +3013,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>209.5</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3042,7 +3045,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>39.66</x:v>
+        <x:v>40.22</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
@@ -3077,7 +3080,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>31.76</x:v>
+        <x:v>28.6</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
@@ -3112,7 +3115,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>37.72</x:v>
+        <x:v>36.9</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
@@ -3147,7 +3150,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>79.6</x:v>
+        <x:v>81.45</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
@@ -3182,7 +3185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>19.05</x:v>
+        <x:v>19.02</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3214,7 +3217,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.48</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
@@ -3249,7 +3252,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>86</x:v>
+        <x:v>86.95</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
@@ -3284,7 +3287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>58.75</x:v>
+        <x:v>59.2</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3316,7 +3319,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>3.91</x:v>
+        <x:v>3.81</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3348,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>36.36</x:v>
+        <x:v>37.24</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3380,7 +3383,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.5</x:v>
+        <x:v>10.44</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
@@ -3415,7 +3418,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>17.99</x:v>
+        <x:v>18.53</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3450,7 +3453,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.04</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
@@ -3485,7 +3488,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>35.9</x:v>
+        <x:v>35.86</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
@@ -3520,7 +3523,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>1.97</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
@@ -3555,7 +3558,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>115.7</x:v>
+        <x:v>116.3</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
@@ -3590,7 +3593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>39.86</x:v>
+        <x:v>39.78</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3622,7 +3625,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3657,7 +3660,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>60.45</x:v>
+        <x:v>61.8</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3674,7 +3677,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>7749148</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D68" s="0">
         <x:v>11000000</x:v>
@@ -3683,27 +3686,27 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>163840651</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>2.04</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.26</x:v>
+        <x:v>19.51</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>21.14</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>148</x:v>
@@ -3727,7 +3730,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>22.02</x:v>
+        <x:v>21.84</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3738,7 +3741,7 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>148</x:v>
@@ -3762,21 +3765,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.54</x:v>
+        <x:v>7.56</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3797,21 +3800,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>45.9</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3832,21 +3835,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>63.05</x:v>
+        <x:v>63.65</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3867,7 +3870,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>43.6</x:v>
+        <x:v>43.52</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3875,10 +3878,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3899,7 +3902,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.48</x:v>
+        <x:v>7.58</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3907,10 +3910,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3931,21 +3934,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.8</x:v>
+        <x:v>8.85</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3977,10 +3980,10 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4001,21 +4004,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>10.69</x:v>
+        <x:v>10.91</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4036,7 +4039,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.65</x:v>
+        <x:v>4.86</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
@@ -4047,10 +4050,10 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4071,21 +4074,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>281.75</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4106,21 +4109,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.26</x:v>
+        <x:v>10.91</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4141,21 +4144,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>369.25</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4176,21 +4179,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>33.76</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4211,21 +4214,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>27.06</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4246,21 +4249,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1221</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4281,7 +4284,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>14.38</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4292,10 +4295,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4316,21 +4319,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.18</x:v>
+        <x:v>8.69</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4351,7 +4354,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>15.89</x:v>
+        <x:v>16.29</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4359,10 +4362,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4383,7 +4386,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.13</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
@@ -4397,7 +4400,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4418,21 +4421,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>149.1</x:v>
+        <x:v>149.8</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4453,21 +4456,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>93</x:v>
+        <x:v>94.25</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4488,13 +4491,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.06</x:v>
+        <x:v>5.01</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -4502,7 +4505,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4523,7 +4526,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>744</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
@@ -4534,10 +4537,10 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4558,21 +4561,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.25</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4593,7 +4596,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.17</x:v>
+        <x:v>10.25</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
@@ -4604,10 +4607,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4628,7 +4631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.56</x:v>
+        <x:v>3.61</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4636,10 +4639,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4660,21 +4663,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>28.9</x:v>
+        <x:v>29.34</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4695,21 +4698,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.63</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4730,7 +4733,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>33.8</x:v>
+        <x:v>34.88</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4741,7 +4744,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4762,7 +4765,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>23.08</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
@@ -4776,7 +4779,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4797,21 +4800,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>8.67</x:v>
+        <x:v>9.14</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4832,7 +4835,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.12</x:v>
+        <x:v>4.18</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4840,10 +4843,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4864,7 +4867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>7.02</x:v>
+        <x:v>6.96</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4872,10 +4875,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4896,13 +4899,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>133</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4910,7 +4913,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>4529358</x:v>
@@ -4931,21 +4934,21 @@
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>12.07</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.44</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1090000</x:v>
@@ -4966,7 +4969,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>41.6</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>36.91</x:v>
@@ -4977,10 +4980,10 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5001,21 +5004,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>94.05</x:v>
+        <x:v>96.35</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5036,7 +5039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>505</x:v>
+        <x:v>503.5</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5044,10 +5047,10 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5068,7 +5071,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>33.42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
@@ -5079,10 +5082,10 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5103,21 +5106,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.2</x:v>
+        <x:v>14.31</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5138,7 +5141,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.06</x:v>
+        <x:v>16.2</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
@@ -5149,10 +5152,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5173,21 +5176,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>34.28</x:v>
+        <x:v>34.26</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>2975773</x:v>
@@ -5208,7 +5211,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>27.96</x:v>
+        <x:v>28.42</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5219,10 +5222,10 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>10994323</x:v>
@@ -5243,21 +5246,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.67</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>25876543</x:v>
@@ -5278,21 +5281,21 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>16.06</x:v>
+        <x:v>16.55</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5100000</x:v>
@@ -5313,21 +5316,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>61.7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>13</x:v>
@@ -5348,7 +5351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5356,10 +5359,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>5000000</x:v>
@@ -5380,21 +5383,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>9.26</x:v>
+        <x:v>9.65</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>590777</x:v>
@@ -5415,21 +5418,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>17.25</x:v>
+        <x:v>17.72</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>13</x:v>
@@ -5450,7 +5453,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>80.5</x:v>
+        <x:v>88.55</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5458,10 +5461,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5482,7 +5485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>505</x:v>
+        <x:v>503.5</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5490,10 +5493,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>53584</x:v>
@@ -5514,7 +5517,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>237</x:v>
+        <x:v>235.4</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5525,10 +5528,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>7550000</x:v>
@@ -5549,13 +5552,13 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>69.65</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5563,7 +5566,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>772649</x:v>
@@ -5584,21 +5587,21 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.02</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2097716</x:v>
@@ -5619,21 +5622,21 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.51</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>5185302</x:v>
@@ -5654,7 +5657,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.49</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
@@ -5665,10 +5668,10 @@
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>669111</x:v>
@@ -5689,21 +5692,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>546</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>38840</x:v>
@@ -5724,21 +5727,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>505</x:v>
+        <x:v>503.5</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>2146559</x:v>
@@ -5759,21 +5762,21 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>483</x:v>
+        <x:v>492.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>2250000</x:v>
@@ -5794,21 +5797,21 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>69.65</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>109200</x:v>
@@ -5829,7 +5832,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>67.25</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
@@ -5840,10 +5843,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>1127000</x:v>
@@ -5864,7 +5867,7 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>58</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
@@ -5875,10 +5878,10 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>3435564</x:v>
@@ -5899,7 +5902,7 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>408</x:v>
+        <x:v>407.25</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
@@ -5910,10 +5913,10 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>109200</x:v>
@@ -5934,7 +5937,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>67.25</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
@@ -5945,10 +5948,10 @@
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>2550000</x:v>
@@ -5969,21 +5972,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>11.37</x:v>
+        <x:v>10.86</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1500000</x:v>
@@ -6004,21 +6007,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>14.51</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>281228</x:v>
@@ -6050,10 +6053,10 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>12514496</x:v>
@@ -6074,13 +6077,13 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>38.66</x:v>
+        <x:v>39.04</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -6088,7 +6091,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
@@ -6109,7 +6112,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>141.4</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6117,10 +6120,10 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>2550028</x:v>
@@ -6141,13 +6144,13 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>27.06</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6155,7 +6158,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>2000000</x:v>
@@ -6176,13 +6179,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>744</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6190,7 +6193,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>845945</x:v>
@@ -6211,21 +6214,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.48</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>280000</x:v>
@@ -6246,21 +6249,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>52.5</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>47311439</x:v>
@@ -6281,7 +6284,7 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
@@ -6292,10 +6295,10 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>20000000</x:v>
@@ -6316,21 +6319,21 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>69.65</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>21446</x:v>
@@ -6351,7 +6354,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>56.4</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
@@ -6362,10 +6365,10 @@
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>19000</x:v>
@@ -6386,13 +6389,13 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>16.05</x:v>
+        <x:v>16.12</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
@@ -6400,7 +6403,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>10000000</x:v>
@@ -6421,21 +6424,21 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.17</x:v>
+        <x:v>8.18</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C148" s="0">
         <x:v>850000</x:v>
@@ -6462,15 +6465,15 @@
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C149" s="0">
         <x:v>15000000</x:v>
@@ -6491,21 +6494,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.41</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>6397124</x:v>
@@ -6526,13 +6529,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>4.71</x:v>
+        <x:v>4.86</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -6540,7 +6543,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>8578668</x:v>
@@ -6561,7 +6564,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.7</x:v>
+        <x:v>22.56</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6572,10 +6575,10 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>9350000</x:v>
@@ -6596,21 +6599,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.05</x:v>
+        <x:v>7.97</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>13</x:v>
@@ -6642,7 +6645,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C154" s="0">
         <x:v>1468255</x:v>
@@ -6663,21 +6666,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>76.05</x:v>
+        <x:v>76.15</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>500000</x:v>
@@ -6698,7 +6701,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
@@ -6709,10 +6712,10 @@
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>18900000</x:v>
@@ -6733,13 +6736,13 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>61.7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
@@ -6747,7 +6750,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>725000</x:v>
@@ -6768,21 +6771,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>38</x:v>
+        <x:v>38.3</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>4350000</x:v>
@@ -6803,21 +6806,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>93</x:v>
+        <x:v>94.25</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C159" s="0">
         <x:v>361000</x:v>
@@ -6838,21 +6841,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>52.5</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C160" s="0">
         <x:v>226000</x:v>
@@ -6873,7 +6876,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>253.5</x:v>
+        <x:v>256.75</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
@@ -6887,7 +6890,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>1060056</x:v>
@@ -6908,21 +6911,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>209.5</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>1725000</x:v>
@@ -6943,13 +6946,13 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.42</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
@@ -6957,7 +6960,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>132750000</x:v>
@@ -6978,7 +6981,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
@@ -6989,10 +6992,10 @@
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C164" s="0">
         <x:v>7921744</x:v>
@@ -7013,21 +7016,21 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.67</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>373000</x:v>
@@ -7048,21 +7051,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.37</x:v>
+        <x:v>7.31</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>13430000</x:v>
@@ -7083,21 +7086,21 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>118.3</x:v>
+        <x:v>120.5</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>15000000</x:v>
@@ -7118,21 +7121,21 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.49</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>10759347</x:v>
@@ -7153,7 +7156,7 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>11.6</x:v>
+        <x:v>11.67</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
@@ -7164,10 +7167,10 @@
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>10000000</x:v>
@@ -7188,21 +7191,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>5.28</x:v>
+        <x:v>5.06</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C170" s="0">
         <x:v>3081843</x:v>
@@ -7223,21 +7226,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>7.88</x:v>
+        <x:v>7.94</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>1348769</x:v>
@@ -7258,21 +7261,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>256.25</x:v>
+        <x:v>281.75</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>927506</x:v>
@@ -7293,21 +7296,21 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.04</x:v>
+        <x:v>19.15</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C173" s="0">
         <x:v>1699946</x:v>
@@ -7328,13 +7331,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>237</x:v>
+        <x:v>235.4</x:v>
       </x:c>
       <x:c r="J173" s="0">
         <x:v>64.31</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -64,126 +64,129 @@
     <x:t>25.03.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>13.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
@@ -265,384 +268,381 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
     <x:t>07.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
@@ -1019,9 +1019,6 @@
   </x:si>
   <x:si>
     <x:t>24.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2023</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1372,7 +1369,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K173"/>
+  <x:dimension ref="A1:K172"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1436,7 +1433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>149.8</x:v>
+        <x:v>148.2</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1450,7 +1447,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>16879000</x:v>
+        <x:v>17879000</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
@@ -1459,19 +1456,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>121568880</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0.77</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>6.12</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>7.2</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>16</x:v>
@@ -1503,7 +1500,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>27.18</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1538,7 +1535,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>16.05</x:v>
+        <x:v>16.33</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1573,7 +1570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.7</x:v>
+        <x:v>5.75</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1605,7 +1602,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.36</x:v>
+        <x:v>22.9</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1622,7 +1619,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>14983442</x:v>
+        <x:v>15235728</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1631,19 +1628,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>371595752</x:v>
+        <x:v>377560802</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.58</x:v>
+        <x:v>0.59</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.7</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.8</x:v>
+        <x:v>24.78</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>16</x:v>
@@ -1675,7 +1672,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.34</x:v>
+        <x:v>13.35</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1710,7 +1707,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>40</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1745,7 +1742,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>64.2</x:v>
+        <x:v>63.8</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1780,7 +1777,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.21</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1815,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.76</x:v>
+        <x:v>6.59</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1847,7 +1844,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>128.6</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1882,7 +1879,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.08</x:v>
+        <x:v>6.14</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1917,7 +1914,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>77.7</x:v>
+        <x:v>85.45</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1952,7 +1949,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.56</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1987,7 +1984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.21</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2019,21 +2016,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>16445115</x:v>
@@ -2054,21 +2051,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>45.54</x:v>
+        <x:v>46.82</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>1110000</x:v>
@@ -2089,7 +2086,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>752</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2103,7 +2100,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>24398659</x:v>
@@ -2124,13 +2121,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>23.7</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -2138,7 +2135,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>46563878</x:v>
@@ -2159,21 +2156,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>226257</x:v>
@@ -2194,21 +2191,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.33</x:v>
+        <x:v>7.24</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1969635</x:v>
@@ -2229,21 +2226,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>17.07</x:v>
+        <x:v>17.4</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>1000000</x:v>
@@ -2264,21 +2261,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.15</x:v>
+        <x:v>3.21</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>100000</x:v>
@@ -2299,21 +2296,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.38</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2334,7 +2331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>34.7</x:v>
+        <x:v>34.28</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2342,10 +2339,10 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>5831653</x:v>
@@ -2366,24 +2363,24 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>4.81</x:v>
+        <x:v>5.29</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>12400000</x:v>
+        <x:v>12400339</x:v>
       </x:c>
       <x:c r="D30" s="0">
         <x:v>79451200</x:v>
@@ -2392,7 +2389,7 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>484318292</x:v>
+        <x:v>484332923</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
@@ -2401,13 +2398,13 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.74</x:v>
+        <x:v>43.82</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.06</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
@@ -2436,7 +2433,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>44.4</x:v>
+        <x:v>44.52</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2471,7 +2468,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>76.15</x:v>
+        <x:v>75.9</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
@@ -2506,7 +2503,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>41.98</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2538,7 +2535,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.55</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2573,7 +2570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>38.3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2605,7 +2602,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>324</x:v>
+        <x:v>319.25</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
@@ -2640,7 +2637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.16</x:v>
+        <x:v>21.2</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2672,7 +2669,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>143</x:v>
+        <x:v>144.5</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
@@ -2707,7 +2704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.7</x:v>
+        <x:v>34.9</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2739,7 +2736,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>36.9</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
@@ -2774,7 +2771,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>10.45</x:v>
+        <x:v>10.71</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
@@ -2809,7 +2806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13</x:v>
+        <x:v>13.24</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2841,7 +2838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.18</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2873,7 +2870,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.43</x:v>
+        <x:v>6.54</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2908,7 +2905,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
@@ -2919,7 +2916,7 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>115</x:v>
@@ -2943,7 +2940,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>17.07</x:v>
+        <x:v>17.4</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
@@ -2978,7 +2975,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.54</x:v>
+        <x:v>23.84</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
@@ -3013,7 +3010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>221</x:v>
+        <x:v>213.7</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3045,7 +3042,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>40.22</x:v>
+        <x:v>40.72</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
@@ -3080,7 +3077,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>28.6</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
@@ -3115,7 +3112,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>36.9</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
@@ -3150,7 +3147,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>81.45</x:v>
+        <x:v>80.55</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
@@ -3185,7 +3182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>19.02</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3217,7 +3214,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.8</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
@@ -3252,7 +3249,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>86.95</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
@@ -3287,7 +3284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>59.2</x:v>
+        <x:v>59.45</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3319,7 +3316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>3.81</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3351,7 +3348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>37.24</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3383,7 +3380,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.44</x:v>
+        <x:v>10.19</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
@@ -3418,7 +3415,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.53</x:v>
+        <x:v>18.59</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3453,7 +3450,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.23</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
@@ -3488,7 +3485,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>35.86</x:v>
+        <x:v>36.28</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
@@ -3523,7 +3520,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.02</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
@@ -3558,7 +3555,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>116.3</x:v>
+        <x:v>117.1</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
@@ -3593,7 +3590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>39.78</x:v>
+        <x:v>40.06</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3625,7 +3622,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3660,7 +3657,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>61.8</x:v>
+        <x:v>61.55</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3695,18 +3692,18 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.51</x:v>
+        <x:v>19.67</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>148</x:v>
@@ -3730,7 +3727,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.84</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3741,7 +3738,7 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>148</x:v>
@@ -3765,21 +3762,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.56</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3800,21 +3797,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>47</x:v>
+        <x:v>45.96</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3835,21 +3832,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>63.65</x:v>
+        <x:v>63.9</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3870,7 +3867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>43.52</x:v>
+        <x:v>43.34</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3878,10 +3875,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3902,7 +3899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.58</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3910,10 +3907,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3934,21 +3931,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.85</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3969,7 +3966,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.06</x:v>
+        <x:v>13.29</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
@@ -3980,10 +3977,10 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4004,21 +4001,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>10.91</x:v>
+        <x:v>11.13</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4039,7 +4036,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.86</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
@@ -4050,10 +4047,10 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4074,21 +4071,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>266</x:v>
+        <x:v>253.25</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4109,21 +4106,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>10.91</x:v>
+        <x:v>11.15</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4144,21 +4141,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>370</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4179,21 +4176,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>34</x:v>
+        <x:v>34.74</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4214,21 +4211,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>27.5</x:v>
+        <x:v>27.8</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4249,21 +4246,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1225</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4284,7 +4281,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>14.8</x:v>
+        <x:v>15.09</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4295,10 +4292,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4319,21 +4316,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.69</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4354,7 +4351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.29</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4362,10 +4359,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4386,7 +4383,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.78</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
@@ -4400,7 +4397,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4421,21 +4418,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>149.8</x:v>
+        <x:v>148.2</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4456,21 +4453,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>94.25</x:v>
+        <x:v>94.05</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4491,21 +4488,21 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.01</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4526,7 +4523,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>752</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
@@ -4537,10 +4534,10 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4561,21 +4558,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.29</x:v>
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4596,7 +4593,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.25</x:v>
+        <x:v>10.45</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
@@ -4607,10 +4604,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4631,7 +4628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.61</x:v>
+        <x:v>3.63</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4639,10 +4636,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4663,21 +4660,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.34</x:v>
+        <x:v>29.68</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4698,21 +4695,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.63</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4733,7 +4730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>34.88</x:v>
+        <x:v>34.02</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4744,7 +4741,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4765,7 +4762,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>23.7</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
@@ -4779,7 +4776,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4800,21 +4797,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4835,7 +4832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.18</x:v>
+        <x:v>4.59</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4843,10 +4840,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4867,7 +4864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>6.96</x:v>
+        <x:v>7.05</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4875,10 +4872,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4899,13 +4896,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>126</x:v>
+        <x:v>126.3</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4913,7 +4910,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>4529358</x:v>
@@ -4934,21 +4931,21 @@
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13</x:v>
+        <x:v>13.24</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.44</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1090000</x:v>
@@ -4969,13 +4966,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>41</x:v>
+        <x:v>41.54</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>36.91</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -4983,7 +4980,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5004,7 +5001,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>96.35</x:v>
+        <x:v>95.7</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
@@ -5018,7 +5015,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5039,7 +5036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>503.5</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5050,7 +5047,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5071,7 +5068,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>35</x:v>
+        <x:v>31.52</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
@@ -5085,7 +5082,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5106,13 +5103,13 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.31</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -5120,7 +5117,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5155,7 +5152,7 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5176,7 +5173,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>34.26</x:v>
+        <x:v>34.12</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
@@ -5211,7 +5208,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>28.42</x:v>
+        <x:v>29.32</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5246,7 +5243,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.96</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
@@ -5281,7 +5278,7 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>16.55</x:v>
+        <x:v>16.13</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
@@ -5316,7 +5313,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>60</x:v>
+        <x:v>58.45</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
@@ -5351,7 +5348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.4</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5383,7 +5380,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.63</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
@@ -5418,7 +5415,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>17.72</x:v>
+        <x:v>18.11</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
@@ -5453,7 +5450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>88.55</x:v>
+        <x:v>97.4</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5485,7 +5482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>503.5</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5517,7 +5514,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>235.4</x:v>
+        <x:v>235.1</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5552,7 +5549,7 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>70.5</x:v>
+        <x:v>70.75</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
@@ -5587,7 +5584,7 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.21</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
@@ -5622,13 +5619,13 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.49</x:v>
+        <x:v>15.11</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -5657,7 +5654,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.6</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
@@ -5692,13 +5689,13 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>551</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -5727,7 +5724,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>503.5</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
@@ -5762,13 +5759,13 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>492.5</x:v>
+        <x:v>529.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -5797,7 +5794,7 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>70.5</x:v>
+        <x:v>70.75</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
@@ -5832,7 +5829,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>68.5</x:v>
+        <x:v>69.05</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
@@ -5902,7 +5899,7 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>407.25</x:v>
+        <x:v>429.5</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
@@ -5937,7 +5934,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>68.5</x:v>
+        <x:v>69.05</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
@@ -5972,7 +5969,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.86</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
@@ -6007,7 +6004,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>14.49</x:v>
+        <x:v>15.11</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
@@ -6042,7 +6039,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>137.1</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6077,7 +6074,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.04</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
@@ -6112,7 +6109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>143</x:v>
+        <x:v>144.5</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6120,7 +6117,7 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>269</x:v>
@@ -6144,18 +6141,18 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>27.5</x:v>
+        <x:v>27.8</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>270</x:v>
@@ -6179,7 +6176,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>752</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
@@ -6214,7 +6211,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.55</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
@@ -6249,7 +6246,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>55.2</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
@@ -6284,7 +6281,7 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.4</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
@@ -6319,7 +6316,7 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>70.5</x:v>
+        <x:v>70.75</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
@@ -6354,7 +6351,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>59</x:v>
+        <x:v>60.15</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
@@ -6389,7 +6386,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>16.12</x:v>
+        <x:v>16.17</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
@@ -6424,7 +6421,7 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.18</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
@@ -6459,13 +6456,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>7.56</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -6494,7 +6491,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.42</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
@@ -6529,7 +6526,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>4.86</x:v>
+        <x:v>5.04</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
@@ -6564,13 +6561,13 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.56</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
@@ -6599,7 +6596,7 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>7.97</x:v>
+        <x:v>8.19</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
@@ -6634,7 +6631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.65</x:v>
+        <x:v>6.76</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6666,7 +6663,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>76.15</x:v>
+        <x:v>75.9</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
@@ -6701,7 +6698,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.13</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
@@ -6736,7 +6733,7 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>60</x:v>
+        <x:v>58.45</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
@@ -6771,7 +6768,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>38.3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
@@ -6782,7 +6779,7 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>306</x:v>
@@ -6806,7 +6803,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>94.25</x:v>
+        <x:v>94.05</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
@@ -6841,7 +6838,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>55.2</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
@@ -6876,7 +6873,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>256.75</x:v>
+        <x:v>257.5</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
@@ -6911,7 +6908,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>221</x:v>
+        <x:v>213.7</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
@@ -6946,7 +6943,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.44</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
@@ -6981,7 +6978,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
@@ -7016,7 +7013,7 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.96</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
@@ -7051,7 +7048,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.31</x:v>
+        <x:v>7.51</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
@@ -7086,7 +7083,7 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>120.5</x:v>
+        <x:v>121.1</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
@@ -7121,7 +7118,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.6</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
@@ -7156,7 +7153,7 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>11.67</x:v>
+        <x:v>12.13</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
@@ -7191,7 +7188,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>5.06</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
@@ -7226,7 +7223,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>7.94</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
@@ -7261,7 +7258,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>281.75</x:v>
+        <x:v>282.25</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
@@ -7296,48 +7293,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.15</x:v>
+        <x:v>19.65</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
         <x:v>334</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:11">
-      <x:c r="A173" s="0" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="C173" s="0">
-        <x:v>1699946</x:v>
-      </x:c>
-      <x:c r="D173" s="0">
-        <x:v>1800000000</x:v>
-      </x:c>
-      <x:c r="E173" s="0">
-        <x:v>750000000</x:v>
-      </x:c>
-      <x:c r="F173" s="0">
-        <x:v>109323109</x:v>
-      </x:c>
-      <x:c r="G173" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H173" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="I173" s="0">
-        <x:v>235.4</x:v>
-      </x:c>
-      <x:c r="J173" s="0">
-        <x:v>64.31</x:v>
-      </x:c>
-      <x:c r="K173" s="0" t="s">
-        <x:v>303</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -101,6 +101,9 @@
   </x:si>
   <x:si>
     <x:t>23.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
@@ -1433,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>148.2</x:v>
+        <x:v>146.6</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1465,7 +1468,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>6.73</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1500,7 +1503,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>27.24</x:v>
+        <x:v>26.92</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1535,7 +1538,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>16.33</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1570,7 +1573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.75</x:v>
+        <x:v>5.74</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1602,7 +1605,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>22.9</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1619,7 +1622,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>15235728</x:v>
+        <x:v>15474869</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1628,30 +1631,30 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>377560802</x:v>
+        <x:v>383282250</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>24.1</x:v>
+        <x:v>24.92</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.78</x:v>
+        <x:v>24.77</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>7024156</x:v>
@@ -1672,7 +1675,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.35</x:v>
+        <x:v>13.09</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1683,10 +1686,10 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>3500000</x:v>
@@ -1707,7 +1710,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>39.56</x:v>
+        <x:v>39.26</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1718,10 +1721,10 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>3753472</x:v>
@@ -1742,21 +1745,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>63.8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>3189049</x:v>
@@ -1777,21 +1780,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>13</x:v>
@@ -1812,7 +1815,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.59</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1820,10 +1823,10 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>875000</x:v>
@@ -1844,21 +1847,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>133</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>6248196</x:v>
@@ -1879,21 +1882,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.14</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>236122</x:v>
@@ -1914,21 +1917,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>85.45</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>1000000</x:v>
@@ -1949,21 +1952,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.74</x:v>
+        <x:v>22.12</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>13</x:v>
@@ -1984,7 +1987,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -1992,10 +1995,10 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>84837201</x:v>
@@ -2016,21 +2019,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9</x:v>
+        <x:v>9.18</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>16445115</x:v>
@@ -2051,21 +2054,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>46.82</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>1110000</x:v>
@@ -2086,13 +2089,13 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>753</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -2100,7 +2103,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>24398659</x:v>
@@ -2121,21 +2124,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>24.1</x:v>
+        <x:v>24.92</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>46563878</x:v>
@@ -2156,21 +2159,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9</x:v>
+        <x:v>9.18</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>226257</x:v>
@@ -2191,21 +2194,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.24</x:v>
+        <x:v>7.12</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1969635</x:v>
@@ -2226,21 +2229,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>17.4</x:v>
+        <x:v>19.14</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>1000000</x:v>
@@ -2261,21 +2264,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.21</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>100000</x:v>
@@ -2296,21 +2299,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.4</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2331,7 +2334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>34.28</x:v>
+        <x:v>36.3</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2339,10 +2342,10 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>5831653</x:v>
@@ -2363,21 +2366,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>5.29</x:v>
+        <x:v>5.81</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>12400339</x:v>
@@ -2398,7 +2401,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.82</x:v>
+        <x:v>43.92</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.06</x:v>
@@ -2409,10 +2412,10 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>1120876</x:v>
@@ -2433,21 +2436,21 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>44.52</x:v>
+        <x:v>45.54</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>1973951</x:v>
@@ -2468,21 +2471,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>75.9</x:v>
+        <x:v>76.1</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2503,7 +2506,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>41.6</x:v>
+        <x:v>41.88</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2511,10 +2514,10 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>3337681</x:v>
@@ -2535,21 +2538,21 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.61</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2570,7 +2573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39</x:v>
+        <x:v>38.58</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2578,10 +2581,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>1364000</x:v>
@@ -2602,21 +2605,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>319.25</x:v>
+        <x:v>317.25</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2637,7 +2640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.2</x:v>
+        <x:v>20.96</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2645,10 +2648,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>507440</x:v>
@@ -2669,21 +2672,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>144.5</x:v>
+        <x:v>143.2</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2704,7 +2707,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>34.9</x:v>
+        <x:v>35.02</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2712,10 +2715,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>2000000</x:v>
@@ -2736,21 +2739,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>37.7</x:v>
+        <x:v>38.64</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>324474</x:v>
@@ -2771,21 +2774,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>10.71</x:v>
+        <x:v>11.02</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2806,7 +2809,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.24</x:v>
+        <x:v>13.17</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2814,10 +2817,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2838,7 +2841,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.13</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2846,10 +2849,10 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>2000000</x:v>
@@ -2870,7 +2873,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.54</x:v>
+        <x:v>6.62</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2881,10 +2884,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>174500000</x:v>
@@ -2905,21 +2908,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>2.99</x:v>
+        <x:v>3.06</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>635229</x:v>
@@ -2940,21 +2943,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>17.4</x:v>
+        <x:v>19.14</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>130000</x:v>
@@ -2975,21 +2978,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>23.84</x:v>
+        <x:v>24.26</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -3010,7 +3013,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>213.7</x:v>
+        <x:v>214.7</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3018,10 +3021,10 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>447761</x:v>
@@ -3042,21 +3045,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>40.72</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>200000</x:v>
@@ -3077,21 +3080,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.4</x:v>
+        <x:v>23.76</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>575841</x:v>
@@ -3112,21 +3115,21 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>37.7</x:v>
+        <x:v>38.64</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>946718</x:v>
@@ -3147,21 +3150,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>80.55</x:v>
+        <x:v>80.9</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3182,7 +3185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>20.02</x:v>
+        <x:v>20.26</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3190,10 +3193,10 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>3043115</x:v>
@@ -3214,21 +3217,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.7</x:v>
+        <x:v>21.66</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>2382736</x:v>
@@ -3249,21 +3252,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>87.2</x:v>
+        <x:v>91.2</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>13</x:v>
@@ -3284,7 +3287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>59.45</x:v>
+        <x:v>59.65</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3292,10 +3295,10 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>13</x:v>
@@ -3316,7 +3319,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>3.85</x:v>
+        <x:v>3.99</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3324,10 +3327,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>13</x:v>
@@ -3348,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>37.66</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3356,10 +3359,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>310000</x:v>
@@ -3380,21 +3383,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.19</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>2000000</x:v>
@@ -3415,7 +3418,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.59</x:v>
+        <x:v>18.28</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3426,10 +3429,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1250000</x:v>
@@ -3450,21 +3453,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.23</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>3077160</x:v>
@@ -3485,21 +3488,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>36.28</x:v>
+        <x:v>35.06</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3520,21 +3523,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.05</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3555,21 +3558,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>117.1</x:v>
+        <x:v>117.3</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>13</x:v>
@@ -3590,7 +3593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.06</x:v>
+        <x:v>39.42</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3598,10 +3601,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3622,21 +3625,21 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3657,21 +3660,21 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>61.55</x:v>
+        <x:v>60.6</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3692,7 +3695,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.67</x:v>
+        <x:v>19.49</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3703,10 +3706,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3727,21 +3730,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.66</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3762,21 +3765,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.76</x:v>
+        <x:v>7.64</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3797,21 +3800,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>45.96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3832,21 +3835,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>63.9</x:v>
+        <x:v>63.4</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3867,7 +3870,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>43.34</x:v>
+        <x:v>43.42</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3875,10 +3878,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3899,7 +3902,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.8</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3907,10 +3910,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3931,21 +3934,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3966,21 +3969,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.29</x:v>
+        <x:v>13.32</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4001,21 +4004,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.13</x:v>
+        <x:v>10.95</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4036,21 +4039,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.8</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4071,21 +4074,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>253.25</x:v>
+        <x:v>253.5</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4106,21 +4109,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.15</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4147,15 +4150,15 @@
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4176,21 +4179,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>34.74</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4211,21 +4214,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>27.8</x:v>
+        <x:v>27.52</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4246,21 +4249,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1146</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4281,21 +4284,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.09</x:v>
+        <x:v>15.02</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4316,21 +4319,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.2</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4351,7 +4354,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.62</x:v>
+        <x:v>16.23</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4359,10 +4362,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4383,13 +4386,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.78</x:v>
+        <x:v>18.2</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4397,7 +4400,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4418,21 +4421,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>148.2</x:v>
+        <x:v>146.6</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4453,21 +4456,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>94.05</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4488,21 +4491,21 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4523,21 +4526,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>753</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4564,15 +4567,15 @@
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4593,21 +4596,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.45</x:v>
+        <x:v>10.29</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4628,7 +4631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.63</x:v>
+        <x:v>3.61</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4636,10 +4639,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4660,21 +4663,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.68</x:v>
+        <x:v>28.9</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4695,21 +4698,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.82</x:v>
+        <x:v>3.77</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4730,7 +4733,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>34.02</x:v>
+        <x:v>34.92</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4741,7 +4744,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4762,21 +4765,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>24.1</x:v>
+        <x:v>24.92</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4797,21 +4800,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9</x:v>
+        <x:v>9.18</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4832,7 +4835,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.59</x:v>
+        <x:v>4.41</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4840,10 +4843,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4864,7 +4867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>7.05</x:v>
+        <x:v>7.31</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4872,10 +4875,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4896,21 +4899,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>126.3</x:v>
+        <x:v>122.2</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>4529358</x:v>
@@ -4931,21 +4934,21 @@
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.24</x:v>
+        <x:v>13.17</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.44</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1090000</x:v>
@@ -4966,21 +4969,21 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>41.54</x:v>
+        <x:v>41.66</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>36.91</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5001,21 +5004,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>95.7</x:v>
+        <x:v>96.85</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5036,7 +5039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5044,10 +5047,10 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5068,21 +5071,21 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.52</x:v>
+        <x:v>31.42</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5103,21 +5106,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.6</x:v>
+        <x:v>14.28</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5138,21 +5141,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16.28</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5173,21 +5176,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>34.12</x:v>
+        <x:v>33.82</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>2975773</x:v>
@@ -5208,21 +5211,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>29.32</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>10994323</x:v>
@@ -5243,21 +5246,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.96</x:v>
+        <x:v>15.55</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>25876543</x:v>
@@ -5278,21 +5281,21 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>16.13</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5100000</x:v>
@@ -5313,21 +5316,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>58.45</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>13</x:v>
@@ -5348,7 +5351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.46</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5356,10 +5359,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>5000000</x:v>
@@ -5380,21 +5383,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>9.63</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>590777</x:v>
@@ -5415,21 +5418,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>18.11</x:v>
+        <x:v>17.89</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>13</x:v>
@@ -5450,7 +5453,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>97.4</x:v>
+        <x:v>99.15</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5458,10 +5461,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5482,7 +5485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5490,10 +5493,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>53584</x:v>
@@ -5514,7 +5517,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>235.1</x:v>
+        <x:v>234.3</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5525,10 +5528,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>7550000</x:v>
@@ -5549,21 +5552,21 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>70.75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>772649</x:v>
@@ -5584,21 +5587,21 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2097716</x:v>
@@ -5619,21 +5622,21 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.11</x:v>
+        <x:v>16.04</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>5185302</x:v>
@@ -5654,21 +5657,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.68</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>669111</x:v>
@@ -5689,21 +5692,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>560</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>38840</x:v>
@@ -5724,21 +5727,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>2146559</x:v>
@@ -5759,21 +5762,21 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>529.5</x:v>
+        <x:v>523.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>2250000</x:v>
@@ -5794,21 +5797,21 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>70.75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>109200</x:v>
@@ -5829,21 +5832,21 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>69.05</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>1127000</x:v>
@@ -5864,21 +5867,21 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>61.45</x:v>
+        <x:v>61.65</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>3435564</x:v>
@@ -5899,21 +5902,21 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>429.5</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>109200</x:v>
@@ -5934,21 +5937,21 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>69.05</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>260</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>2550000</x:v>
@@ -5969,21 +5972,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>11.25</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1500000</x:v>
@@ -6004,21 +6007,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.11</x:v>
+        <x:v>16.04</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>281228</x:v>
@@ -6039,7 +6042,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>138</x:v>
+        <x:v>140.2</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6050,10 +6053,10 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>12514496</x:v>
@@ -6074,21 +6077,21 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.62</x:v>
+        <x:v>39.16</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
@@ -6109,7 +6112,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>144.5</x:v>
+        <x:v>143.2</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6117,10 +6120,10 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>2550028</x:v>
@@ -6141,21 +6144,21 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>27.8</x:v>
+        <x:v>27.52</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>2000000</x:v>
@@ -6176,21 +6179,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>753</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>845945</x:v>
@@ -6211,21 +6214,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.61</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>280000</x:v>
@@ -6246,21 +6249,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>54.45</x:v>
+        <x:v>55.4</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>47311439</x:v>
@@ -6281,21 +6284,21 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.46</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>20000000</x:v>
@@ -6316,21 +6319,21 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>70.75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>21446</x:v>
@@ -6351,21 +6354,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>60.15</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>19000</x:v>
@@ -6386,21 +6389,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>16.17</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>10000000</x:v>
@@ -6421,21 +6424,21 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.13</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C148" s="0">
         <x:v>850000</x:v>
@@ -6456,21 +6459,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>7.9</x:v>
+        <x:v>7.79</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C149" s="0">
         <x:v>15000000</x:v>
@@ -6491,21 +6494,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>6397124</x:v>
@@ -6526,21 +6529,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>5.04</x:v>
+        <x:v>5.06</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>8578668</x:v>
@@ -6561,21 +6564,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.74</x:v>
+        <x:v>22.12</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>9350000</x:v>
@@ -6596,21 +6599,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.19</x:v>
+        <x:v>8.49</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>13</x:v>
@@ -6631,7 +6634,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.76</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6639,10 +6642,10 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C154" s="0">
         <x:v>1468255</x:v>
@@ -6663,21 +6666,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>75.9</x:v>
+        <x:v>76.1</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>500000</x:v>
@@ -6698,21 +6701,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.02</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>18900000</x:v>
@@ -6733,21 +6736,21 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>58.45</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>725000</x:v>
@@ -6768,21 +6771,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>39</x:v>
+        <x:v>38.58</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>4350000</x:v>
@@ -6803,21 +6806,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>94.05</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C159" s="0">
         <x:v>361000</x:v>
@@ -6838,21 +6841,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>54.45</x:v>
+        <x:v>55.4</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C160" s="0">
         <x:v>226000</x:v>
@@ -6873,21 +6876,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>257.5</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>1060056</x:v>
@@ -6908,21 +6911,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>213.7</x:v>
+        <x:v>214.7</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>1725000</x:v>
@@ -6949,15 +6952,15 @@
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>132750000</x:v>
@@ -6978,21 +6981,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>2.99</x:v>
+        <x:v>3.06</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C164" s="0">
         <x:v>7921744</x:v>
@@ -7013,21 +7016,21 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.96</x:v>
+        <x:v>15.55</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>373000</x:v>
@@ -7048,21 +7051,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.51</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>13430000</x:v>
@@ -7083,21 +7086,21 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>121.1</x:v>
+        <x:v>117.9</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>15000000</x:v>
@@ -7118,21 +7121,21 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.68</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>10759347</x:v>
@@ -7153,21 +7156,21 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>12.13</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>10000000</x:v>
@@ -7188,21 +7191,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>5.15</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C170" s="0">
         <x:v>3081843</x:v>
@@ -7223,21 +7226,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>7.95</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>1348769</x:v>
@@ -7258,21 +7261,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>282.25</x:v>
+        <x:v>310.25</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>927506</x:v>
@@ -7293,13 +7296,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.65</x:v>
+        <x:v>19.33</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -103,7 +103,7 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>15.04.2026</x:t>
+    <x:t>16.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
@@ -641,9 +641,6 @@
   </x:si>
   <x:si>
     <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -1436,7 +1433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>146.6</x:v>
+        <x:v>147.5</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1468,7 +1465,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>7.4</x:v>
+        <x:v>8.14</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1503,7 +1500,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.92</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1538,7 +1535,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>16.18</x:v>
+        <x:v>16.52</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1573,7 +1570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.74</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1605,7 +1602,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.62</x:v>
+        <x:v>23.06</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1622,7 +1619,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>15474869</x:v>
+        <x:v>15677590</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1631,7 +1628,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>383282250</x:v>
+        <x:v>388330814</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
@@ -1640,7 +1637,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>24.92</x:v>
+        <x:v>25.34</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>24.77</x:v>
@@ -1675,7 +1672,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.09</x:v>
+        <x:v>13.62</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1710,7 +1707,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>39.26</x:v>
+        <x:v>40.46</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1745,7 +1742,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>61</x:v>
+        <x:v>62.7</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1780,7 +1777,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1815,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.58</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1847,7 +1844,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>143.4</x:v>
+        <x:v>148.6</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1882,7 +1879,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.04</x:v>
+        <x:v>6.21</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1917,7 +1914,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>93.95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1952,7 +1949,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.12</x:v>
+        <x:v>22.54</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1987,7 +1984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2019,7 +2016,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.18</x:v>
+        <x:v>9.29</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2054,7 +2051,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>50</x:v>
+        <x:v>51.25</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2089,7 +2086,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>746</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2124,7 +2121,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>24.92</x:v>
+        <x:v>25.34</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2159,7 +2156,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.18</x:v>
+        <x:v>9.29</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2194,7 +2191,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.12</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
@@ -2229,7 +2226,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>19.14</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
@@ -2264,7 +2261,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2299,7 +2296,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.93</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2334,7 +2331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>36.3</x:v>
+        <x:v>35.58</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2366,7 +2363,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>5.81</x:v>
+        <x:v>6.39</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2401,7 +2398,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.92</x:v>
+        <x:v>45.4</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.06</x:v>
@@ -2436,7 +2433,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>45.54</x:v>
+        <x:v>46.68</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2471,7 +2468,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>76.1</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
@@ -2538,7 +2535,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2573,7 +2570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>38.58</x:v>
+        <x:v>40.04</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2605,7 +2602,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>317.25</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
@@ -2640,7 +2637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>20.96</x:v>
+        <x:v>22.34</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2672,7 +2669,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>143.2</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
@@ -2707,7 +2704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.02</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2739,7 +2736,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>38.64</x:v>
+        <x:v>41.66</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
@@ -2774,7 +2771,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.02</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
@@ -2809,7 +2806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.17</x:v>
+        <x:v>13.07</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2841,7 +2838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.11</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2873,7 +2870,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.62</x:v>
+        <x:v>6.68</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2908,7 +2905,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.06</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
@@ -2943,7 +2940,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>19.14</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
@@ -2978,7 +2975,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.26</x:v>
+        <x:v>24.4</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
@@ -3013,7 +3010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>214.7</x:v>
+        <x:v>215.1</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3045,7 +3042,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>40.7</x:v>
+        <x:v>42.28</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
@@ -3080,7 +3077,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>23.76</x:v>
+        <x:v>21.92</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
@@ -3115,7 +3112,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>38.64</x:v>
+        <x:v>41.66</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
@@ -3150,7 +3147,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>80.9</x:v>
+        <x:v>80.3</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
@@ -3185,7 +3182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>20.26</x:v>
+        <x:v>19.65</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3217,7 +3214,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.66</x:v>
+        <x:v>21.44</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
@@ -3252,7 +3249,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>91.2</x:v>
+        <x:v>89.3</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
@@ -3287,7 +3284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>59.65</x:v>
+        <x:v>63.6</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3319,7 +3316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>3.99</x:v>
+        <x:v>4.38</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3351,7 +3348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>37</x:v>
+        <x:v>38.36</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3383,7 +3380,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.36</x:v>
+        <x:v>10.34</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
@@ -3418,7 +3415,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.28</x:v>
+        <x:v>18.45</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3453,7 +3450,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>2.94</x:v>
+        <x:v>3.23</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
@@ -3488,7 +3485,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>35.06</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
@@ -3523,7 +3520,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.01</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
@@ -3558,7 +3555,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>117.3</x:v>
+        <x:v>120.5</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
@@ -3593,7 +3590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>39.42</x:v>
+        <x:v>41.14</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3625,7 +3622,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.89</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3660,7 +3657,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>60.6</x:v>
+        <x:v>61.15</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3695,7 +3692,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.49</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3730,7 +3727,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.66</x:v>
+        <x:v>21.46</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3765,7 +3762,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.64</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
@@ -3800,7 +3797,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>45</x:v>
+        <x:v>49.16</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
@@ -3835,7 +3832,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>63.4</x:v>
+        <x:v>66.15</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
@@ -3870,7 +3867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>43.42</x:v>
+        <x:v>45.12</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3902,7 +3899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.83</x:v>
+        <x:v>8.12</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3934,7 +3931,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.7</x:v>
+        <x:v>8.51</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
@@ -3969,7 +3966,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.32</x:v>
+        <x:v>13.73</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
@@ -4004,7 +4001,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>10.95</x:v>
+        <x:v>11.27</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
@@ -4039,7 +4036,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.76</x:v>
+        <x:v>4.74</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
@@ -4074,7 +4071,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>253.5</x:v>
+        <x:v>255.5</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
@@ -4109,7 +4106,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.25</x:v>
+        <x:v>11.55</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
@@ -4144,7 +4141,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>375</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
@@ -4179,7 +4176,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>38.2</x:v>
+        <x:v>38.52</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
@@ -4214,7 +4211,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>27.52</x:v>
+        <x:v>27.46</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4249,7 +4246,7 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1152</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
@@ -4284,7 +4281,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.02</x:v>
+        <x:v>15.89</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4319,7 +4316,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.11</x:v>
+        <x:v>8.33</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
@@ -4354,7 +4351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.23</x:v>
+        <x:v>16.71</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4386,7 +4383,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.2</x:v>
+        <x:v>18.51</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
@@ -4421,7 +4418,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>146.6</x:v>
+        <x:v>147.5</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
@@ -4456,7 +4453,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>93.2</x:v>
+        <x:v>95.55</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
@@ -4491,7 +4488,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4.99</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
@@ -4526,7 +4523,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>746</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
@@ -4561,7 +4558,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.32</x:v>
+        <x:v>4.49</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
@@ -4596,7 +4593,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.29</x:v>
+        <x:v>10.68</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
@@ -4631,7 +4628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.61</x:v>
+        <x:v>3.72</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4663,7 +4660,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>28.9</x:v>
+        <x:v>29.98</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
@@ -4698,7 +4695,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.77</x:v>
+        <x:v>3.88</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
@@ -4733,7 +4730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>34.92</x:v>
+        <x:v>35.06</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4765,7 +4762,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>24.92</x:v>
+        <x:v>25.34</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
@@ -4800,7 +4797,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.18</x:v>
+        <x:v>9.29</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
@@ -4835,7 +4832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.41</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4867,7 +4864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>7.31</x:v>
+        <x:v>7.57</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4899,7 +4896,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>122.2</x:v>
+        <x:v>121.6</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
@@ -4934,7 +4931,7 @@
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.17</x:v>
+        <x:v>13.07</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.44</x:v>
@@ -4951,7 +4948,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1090000</x:v>
+        <x:v>1190000</x:v>
       </x:c>
       <x:c r="D105" s="0">
         <x:v>2160000</x:v>
@@ -4960,27 +4957,27 @@
         <x:v>35000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>40230627</x:v>
+        <x:v>44416627</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>41.66</x:v>
+        <x:v>41.4</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>36.91</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>190</x:v>
@@ -5004,18 +5001,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>96.85</x:v>
+        <x:v>97.7</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>190</x:v>
@@ -5039,7 +5036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>518</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5047,7 +5044,7 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>190</x:v>
@@ -5071,7 +5068,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.42</x:v>
+        <x:v>31.9</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
@@ -5082,7 +5079,7 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>190</x:v>
@@ -5106,7 +5103,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.28</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
@@ -5117,7 +5114,7 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>190</x:v>
@@ -5141,7 +5138,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.28</x:v>
+        <x:v>16.49</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
@@ -5152,7 +5149,7 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>190</x:v>
@@ -5176,21 +5173,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>33.82</x:v>
+        <x:v>35.4</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>2975773</x:v>
@@ -5211,7 +5208,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>28.3</x:v>
+        <x:v>30.32</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5222,10 +5219,10 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>10994323</x:v>
@@ -5246,21 +5243,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.55</x:v>
+        <x:v>15.84</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>25876543</x:v>
@@ -5281,21 +5278,21 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>15.9</x:v>
+        <x:v>16.21</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5100000</x:v>
@@ -5316,21 +5313,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>59.5</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>13</x:v>
@@ -5351,7 +5348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.51</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5359,10 +5356,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>5000000</x:v>
@@ -5383,21 +5380,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>9.5</x:v>
+        <x:v>9.53</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>590777</x:v>
@@ -5418,21 +5415,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>17.89</x:v>
+        <x:v>18.4</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>13</x:v>
@@ -5453,7 +5450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>99.15</x:v>
+        <x:v>98.5</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5461,10 +5458,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5485,7 +5482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>518</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5493,10 +5490,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>53584</x:v>
@@ -5517,7 +5514,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>234.3</x:v>
+        <x:v>236.3</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5528,10 +5525,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>7550000</x:v>
@@ -5552,13 +5549,13 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>71</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5566,7 +5563,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>772649</x:v>
@@ -5587,21 +5584,21 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2097716</x:v>
@@ -5622,7 +5619,7 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>16.04</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
@@ -5633,10 +5630,10 @@
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>5185302</x:v>
@@ -5657,7 +5654,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.82</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
@@ -5668,10 +5665,10 @@
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>669111</x:v>
@@ -5692,7 +5689,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>570</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
@@ -5703,10 +5700,10 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>38840</x:v>
@@ -5727,21 +5724,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>518</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>2146559</x:v>
@@ -5762,7 +5759,7 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>523.5</x:v>
+        <x:v>539.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
@@ -5773,10 +5770,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>2250000</x:v>
@@ -5797,21 +5794,21 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>71</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>109200</x:v>
@@ -5832,7 +5829,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>69.4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
@@ -5843,10 +5840,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>1127000</x:v>
@@ -5867,7 +5864,7 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>61.65</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
@@ -5878,10 +5875,10 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>3435564</x:v>
@@ -5902,7 +5899,7 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
@@ -5913,10 +5910,10 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>109200</x:v>
@@ -5937,7 +5934,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>69.4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
@@ -5948,10 +5945,10 @@
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>2550000</x:v>
@@ -5972,21 +5969,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.7</x:v>
+        <x:v>10.63</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1500000</x:v>
@@ -6007,21 +6004,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>16.04</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>281228</x:v>
@@ -6042,7 +6039,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>140.2</x:v>
+        <x:v>144.3</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6053,10 +6050,10 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>12514496</x:v>
@@ -6077,13 +6074,13 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.16</x:v>
+        <x:v>40.98</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -6091,7 +6088,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
@@ -6112,7 +6109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>143.2</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6123,7 +6120,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>2550028</x:v>
@@ -6144,7 +6141,7 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>27.52</x:v>
+        <x:v>27.46</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
@@ -6158,7 +6155,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>2000000</x:v>
@@ -6179,13 +6176,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>746</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6193,7 +6190,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>845945</x:v>
@@ -6214,21 +6211,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>280000</x:v>
@@ -6249,21 +6246,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>55.4</x:v>
+        <x:v>56.1</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>47311439</x:v>
@@ -6284,7 +6281,7 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.51</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
@@ -6295,10 +6292,10 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>20000000</x:v>
@@ -6319,21 +6316,21 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>71</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>21446</x:v>
@@ -6354,7 +6351,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>61.4</x:v>
+        <x:v>63.5</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
@@ -6365,10 +6362,10 @@
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>19000</x:v>
@@ -6389,13 +6386,13 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>16.62</x:v>
+        <x:v>18.28</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
@@ -6403,7 +6400,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>10000000</x:v>
@@ -6424,21 +6421,21 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.11</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="C148" s="0">
         <x:v>850000</x:v>
@@ -6459,7 +6456,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>7.79</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
@@ -6470,10 +6467,10 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C149" s="0">
         <x:v>15000000</x:v>
@@ -6494,21 +6491,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.75</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>6397124</x:v>
@@ -6529,13 +6526,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>5.06</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -6543,7 +6540,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>8578668</x:v>
@@ -6564,7 +6561,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.12</x:v>
+        <x:v>22.54</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6575,10 +6572,10 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>9350000</x:v>
@@ -6599,21 +6596,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.49</x:v>
+        <x:v>8.79</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>298</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>13</x:v>
@@ -6634,7 +6631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6645,7 +6642,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C154" s="0">
         <x:v>1468255</x:v>
@@ -6666,21 +6663,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>76.1</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>500000</x:v>
@@ -6701,7 +6698,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.01</x:v>
+        <x:v>3.07</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
@@ -6712,10 +6709,10 @@
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>18900000</x:v>
@@ -6736,13 +6733,13 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>59.5</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
@@ -6750,7 +6747,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>725000</x:v>
@@ -6771,13 +6768,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>38.58</x:v>
+        <x:v>40.04</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
@@ -6785,7 +6782,7 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>4350000</x:v>
@@ -6806,21 +6803,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>93.2</x:v>
+        <x:v>95.55</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C159" s="0">
         <x:v>361000</x:v>
@@ -6841,21 +6838,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>55.4</x:v>
+        <x:v>56.1</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C160" s="0">
         <x:v>226000</x:v>
@@ -6876,7 +6873,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>257</x:v>
+        <x:v>265.5</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
@@ -6890,7 +6887,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>1060056</x:v>
@@ -6911,21 +6908,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>214.7</x:v>
+        <x:v>215.1</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>1725000</x:v>
@@ -6946,13 +6943,13 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.45</x:v>
+        <x:v>1.49</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
@@ -6960,7 +6957,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>132750000</x:v>
@@ -6981,7 +6978,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>3.06</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
@@ -6992,10 +6989,10 @@
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C164" s="0">
         <x:v>7921744</x:v>
@@ -7016,21 +7013,21 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.55</x:v>
+        <x:v>15.84</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>319</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>373000</x:v>
@@ -7051,21 +7048,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.41</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>322</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>13430000</x:v>
@@ -7086,21 +7083,21 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>117.9</x:v>
+        <x:v>120.8</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>15000000</x:v>
@@ -7121,21 +7118,21 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.82</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>324</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>10759347</x:v>
@@ -7156,7 +7153,7 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>11.9</x:v>
+        <x:v>12.28</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
@@ -7167,10 +7164,10 @@
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>326</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>10000000</x:v>
@@ -7191,21 +7188,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>5.1</x:v>
+        <x:v>5.04</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C170" s="0">
         <x:v>3081843</x:v>
@@ -7226,21 +7223,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>7.76</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>1348769</x:v>
@@ -7261,21 +7258,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>310.25</x:v>
+        <x:v>319.75</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>927506</x:v>
@@ -7296,13 +7293,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.33</x:v>
+        <x:v>19.8</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -103,544 +103,547 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
     <x:t>16.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -1433,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>147.5</x:v>
+        <x:v>145.2</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1465,7 +1468,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.14</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1500,7 +1503,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.96</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1535,7 +1538,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>16.52</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1570,7 +1573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.84</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1602,7 +1605,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.06</x:v>
+        <x:v>23.98</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1619,7 +1622,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>15677590</x:v>
+        <x:v>16190506</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1628,19 +1631,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>388330814</x:v>
+        <x:v>401305024</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>25.34</x:v>
+        <x:v>26.16</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.77</x:v>
+        <x:v>24.79</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>29</x:v>
@@ -1672,7 +1675,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.62</x:v>
+        <x:v>13.53</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1707,7 +1710,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>40.46</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1742,7 +1745,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>62.7</x:v>
+        <x:v>62.5</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1777,7 +1780,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.7</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1812,7 +1815,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.56</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1844,7 +1847,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>148.6</x:v>
+        <x:v>150.1</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1879,7 +1882,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.21</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1914,7 +1917,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1949,7 +1952,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.54</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1984,7 +1987,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.7</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2016,7 +2019,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.29</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2051,7 +2054,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>51.25</x:v>
+        <x:v>50.7</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2086,7 +2089,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>765</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2121,7 +2124,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>25.34</x:v>
+        <x:v>26.16</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2156,7 +2159,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.29</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2226,7 +2229,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>20.08</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
@@ -2261,7 +2264,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.3</x:v>
+        <x:v>3.37</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2296,7 +2299,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.93</x:v>
+        <x:v>9.53</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2331,7 +2334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>35.58</x:v>
+        <x:v>34.66</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2363,7 +2366,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>6.39</x:v>
+        <x:v>7.02</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2398,7 +2401,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>45.4</x:v>
+        <x:v>44.54</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.06</x:v>
@@ -2433,7 +2436,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>46.68</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2468,7 +2471,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>80</x:v>
+        <x:v>79.8</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
@@ -2503,7 +2506,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>41.88</x:v>
+        <x:v>41.66</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2535,7 +2538,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2570,7 +2573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>40.04</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2602,7 +2605,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>329</x:v>
+        <x:v>328.25</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
@@ -2637,7 +2640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>22.34</x:v>
+        <x:v>21.82</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2669,7 +2672,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>148</x:v>
+        <x:v>143.8</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
@@ -2704,7 +2707,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35</x:v>
+        <x:v>35.42</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2736,7 +2739,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>41.66</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
@@ -2771,7 +2774,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.2</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
@@ -2806,7 +2809,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.07</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2838,7 +2841,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.2</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2870,7 +2873,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.68</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2905,7 +2908,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.14</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
@@ -2940,7 +2943,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>20.08</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
@@ -2975,7 +2978,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.4</x:v>
+        <x:v>25.26</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
@@ -3010,7 +3013,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>215.1</x:v>
+        <x:v>215.3</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3042,7 +3045,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>42.28</x:v>
+        <x:v>41.5</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
@@ -3077,7 +3080,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>21.92</x:v>
+        <x:v>22.84</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
@@ -3112,7 +3115,7 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>41.66</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
@@ -3147,7 +3150,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>80.3</x:v>
+        <x:v>79.55</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
@@ -3182,7 +3185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>19.65</x:v>
+        <x:v>18.84</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3214,7 +3217,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
@@ -3249,7 +3252,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>89.3</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
@@ -3284,7 +3287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>63.6</x:v>
+        <x:v>62.5</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3316,7 +3319,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>4.38</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3348,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>38.36</x:v>
+        <x:v>38.12</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3380,7 +3383,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.34</x:v>
+        <x:v>10.05</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
@@ -3415,7 +3418,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.45</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3450,7 +3453,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.23</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
@@ -3485,7 +3488,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>36.4</x:v>
+        <x:v>35.52</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
@@ -3520,7 +3523,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.1</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
@@ -3555,7 +3558,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>120.5</x:v>
+        <x:v>117.7</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
@@ -3590,7 +3593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>41.14</x:v>
+        <x:v>40.72</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3622,7 +3625,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.89</x:v>
+        <x:v>2.86</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3657,7 +3660,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>61.15</x:v>
+        <x:v>59.8</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3692,7 +3695,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.4</x:v>
+        <x:v>20.54</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3727,7 +3730,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.46</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3762,7 +3765,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>8.4</x:v>
+        <x:v>8.12</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
@@ -3797,7 +3800,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>49.16</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
@@ -3832,7 +3835,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>66.15</x:v>
+        <x:v>66.75</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
@@ -3867,7 +3870,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>45.12</x:v>
+        <x:v>44.68</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3899,7 +3902,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>8.12</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3931,7 +3934,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.51</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
@@ -3966,7 +3969,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.73</x:v>
+        <x:v>13.59</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
@@ -4001,7 +4004,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.27</x:v>
+        <x:v>11.32</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
@@ -4036,7 +4039,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.74</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
@@ -4071,7 +4074,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>255.5</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
@@ -4106,7 +4109,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.55</x:v>
+        <x:v>11.27</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
@@ -4141,7 +4144,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>396</x:v>
+        <x:v>356.5</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
@@ -4176,7 +4179,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>38.52</x:v>
+        <x:v>38.92</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
@@ -4211,7 +4214,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>27.46</x:v>
+        <x:v>26.32</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4246,7 +4249,7 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1175</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
@@ -4281,7 +4284,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.89</x:v>
+        <x:v>16.13</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4316,7 +4319,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
@@ -4351,7 +4354,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.71</x:v>
+        <x:v>17.14</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4383,7 +4386,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.51</x:v>
+        <x:v>18.59</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
@@ -4418,7 +4421,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>147.5</x:v>
+        <x:v>145.2</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
@@ -4453,7 +4456,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>95.55</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
@@ -4488,7 +4491,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.07</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
@@ -4523,7 +4526,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>765</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
@@ -4558,7 +4561,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.49</x:v>
+        <x:v>4.42</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
@@ -4593,7 +4596,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.68</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
@@ -4628,7 +4631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.72</x:v>
+        <x:v>3.67</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4660,7 +4663,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.98</x:v>
+        <x:v>29.96</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
@@ -4695,7 +4698,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.88</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
@@ -4730,7 +4733,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>35.06</x:v>
+        <x:v>36.18</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4762,7 +4765,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>25.34</x:v>
+        <x:v>26.16</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
@@ -4797,7 +4800,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.29</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
@@ -4864,7 +4867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>7.57</x:v>
+        <x:v>8.32</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4896,7 +4899,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>121.6</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
@@ -4931,7 +4934,7 @@
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.07</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.44</x:v>
@@ -4966,18 +4969,18 @@
         <x:v>0.68</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>41.4</x:v>
+        <x:v>40.8</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>37.32</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>190</x:v>
@@ -5001,18 +5004,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>97.7</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>190</x:v>
@@ -5036,7 +5039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5044,7 +5047,7 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>190</x:v>
@@ -5068,7 +5071,7 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.9</x:v>
+        <x:v>31.2</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
@@ -5079,7 +5082,7 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>190</x:v>
@@ -5103,7 +5106,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>15.19</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
@@ -5114,7 +5117,7 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>190</x:v>
@@ -5138,7 +5141,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.49</x:v>
+        <x:v>16.24</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
@@ -5149,7 +5152,7 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>190</x:v>
@@ -5173,21 +5176,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>35.4</x:v>
+        <x:v>34.66</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>2975773</x:v>
@@ -5208,7 +5211,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>30.32</x:v>
+        <x:v>29.14</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5219,10 +5222,10 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>10994323</x:v>
@@ -5243,21 +5246,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.84</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>25876543</x:v>
@@ -5278,21 +5281,21 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>16.21</x:v>
+        <x:v>15.98</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5100000</x:v>
@@ -5313,21 +5316,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>60.3</x:v>
+        <x:v>60.1</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>13</x:v>
@@ -5348,7 +5351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5356,10 +5359,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>5000000</x:v>
@@ -5380,21 +5383,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>9.53</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>590777</x:v>
@@ -5415,21 +5418,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>18.4</x:v>
+        <x:v>18.35</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>13</x:v>
@@ -5450,7 +5453,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>98.5</x:v>
+        <x:v>98.15</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5458,10 +5461,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5482,7 +5485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5490,10 +5493,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>53584</x:v>
@@ -5514,7 +5517,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>236.3</x:v>
+        <x:v>238.1</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5525,10 +5528,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>7550000</x:v>
@@ -5549,13 +5552,13 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>74.1</x:v>
+        <x:v>74.85</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5563,7 +5566,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>772649</x:v>
@@ -5584,21 +5587,21 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.7</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2097716</x:v>
@@ -5619,7 +5622,7 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.59</x:v>
+        <x:v>15.35</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
@@ -5630,10 +5633,10 @@
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>5185302</x:v>
@@ -5654,7 +5657,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.98</x:v>
+        <x:v>5.92</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
@@ -5665,10 +5668,10 @@
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>669111</x:v>
@@ -5689,7 +5692,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>593</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
@@ -5700,10 +5703,10 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>38840</x:v>
@@ -5724,21 +5727,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>2146559</x:v>
@@ -5759,7 +5762,7 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>539.5</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
@@ -5770,10 +5773,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>2250000</x:v>
@@ -5794,21 +5797,21 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>74.1</x:v>
+        <x:v>74.85</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>109200</x:v>
@@ -5829,7 +5832,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
@@ -5840,10 +5843,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>1127000</x:v>
@@ -5864,7 +5867,7 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>62.8</x:v>
+        <x:v>60.75</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
@@ -5875,10 +5878,10 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>3435564</x:v>
@@ -5899,7 +5902,7 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>450</x:v>
+        <x:v>444.25</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
@@ -5910,10 +5913,10 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>109200</x:v>
@@ -5934,7 +5937,7 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
@@ -5945,10 +5948,10 @@
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>260</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>2550000</x:v>
@@ -5969,21 +5972,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.63</x:v>
+        <x:v>10.58</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1500000</x:v>
@@ -6004,21 +6007,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.59</x:v>
+        <x:v>15.35</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>281228</x:v>
@@ -6039,7 +6042,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>144.3</x:v>
+        <x:v>141.1</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6050,10 +6053,10 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>12514496</x:v>
@@ -6074,13 +6077,13 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>40.98</x:v>
+        <x:v>39.94</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -6088,7 +6091,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
@@ -6109,7 +6112,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>148</x:v>
+        <x:v>143.8</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6120,7 +6123,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>2550028</x:v>
@@ -6141,7 +6144,7 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>27.46</x:v>
+        <x:v>26.32</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
@@ -6155,7 +6158,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>2000000</x:v>
@@ -6176,13 +6179,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>765</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6190,7 +6193,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>845945</x:v>
@@ -6211,21 +6214,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>280000</x:v>
@@ -6246,21 +6249,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>56.1</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>47311439</x:v>
@@ -6281,7 +6284,7 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
@@ -6292,10 +6295,10 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>20000000</x:v>
@@ -6316,21 +6319,21 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>74.1</x:v>
+        <x:v>74.85</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>21446</x:v>
@@ -6351,7 +6354,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>63.5</x:v>
+        <x:v>64.05</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
@@ -6362,10 +6365,10 @@
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>19000</x:v>
@@ -6386,13 +6389,13 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>18.28</x:v>
+        <x:v>17.04</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
@@ -6400,7 +6403,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>10000000</x:v>
@@ -6421,21 +6424,21 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.2</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C148" s="0">
         <x:v>850000</x:v>
@@ -6456,7 +6459,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>7.96</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
@@ -6467,10 +6470,10 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C149" s="0">
         <x:v>15000000</x:v>
@@ -6491,21 +6494,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>3.02</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>6397124</x:v>
@@ -6526,13 +6529,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>5.1</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -6540,7 +6543,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>8578668</x:v>
@@ -6561,7 +6564,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.54</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6572,10 +6575,10 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>9350000</x:v>
@@ -6596,21 +6599,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.79</x:v>
+        <x:v>8.82</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>13</x:v>
@@ -6631,7 +6634,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.83</x:v>
+        <x:v>6.86</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6642,7 +6645,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C154" s="0">
         <x:v>1468255</x:v>
@@ -6663,21 +6666,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>80</x:v>
+        <x:v>79.8</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>500000</x:v>
@@ -6698,7 +6701,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.07</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
@@ -6709,10 +6712,10 @@
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>18900000</x:v>
@@ -6733,13 +6736,13 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>60.3</x:v>
+        <x:v>60.1</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
@@ -6747,7 +6750,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>725000</x:v>
@@ -6768,13 +6771,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>40.04</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
@@ -6782,7 +6785,7 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>4350000</x:v>
@@ -6803,21 +6806,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>95.55</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C159" s="0">
         <x:v>361000</x:v>
@@ -6838,21 +6841,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>56.1</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C160" s="0">
         <x:v>226000</x:v>
@@ -6873,7 +6876,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>265.5</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
@@ -6887,7 +6890,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>1060056</x:v>
@@ -6908,21 +6911,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>215.1</x:v>
+        <x:v>215.3</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>1725000</x:v>
@@ -6943,13 +6946,13 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.49</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
@@ -6957,7 +6960,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>132750000</x:v>
@@ -6978,7 +6981,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>3.14</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
@@ -6989,10 +6992,10 @@
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C164" s="0">
         <x:v>7921744</x:v>
@@ -7013,21 +7016,21 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.84</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>373000</x:v>
@@ -7048,21 +7051,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.46</x:v>
+        <x:v>7.85</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>13430000</x:v>
@@ -7083,21 +7086,21 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>120.8</x:v>
+        <x:v>128.7</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>15000000</x:v>
@@ -7118,21 +7121,21 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.98</x:v>
+        <x:v>5.92</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>10759347</x:v>
@@ -7153,7 +7156,7 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>12.28</x:v>
+        <x:v>12.05</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
@@ -7164,10 +7167,10 @@
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>10000000</x:v>
@@ -7188,21 +7191,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>5.04</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C170" s="0">
         <x:v>3081843</x:v>
@@ -7223,21 +7226,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>8.13</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>1348769</x:v>
@@ -7258,21 +7261,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>319.75</x:v>
+        <x:v>337.25</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>927506</x:v>
@@ -7293,13 +7296,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.8</x:v>
+        <x:v>19.62</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -103,7 +103,7 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>17.04.2026</x:t>
+    <x:t>21.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
@@ -271,6 +271,9 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>PNLSN</x:t>
   </x:si>
   <x:si>
@@ -637,13 +640,7 @@
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>06.02.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -1436,7 +1433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>145.2</x:v>
+        <x:v>139.6</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1468,7 +1465,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.95</x:v>
+        <x:v>9.73</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1503,7 +1500,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.4</x:v>
+        <x:v>26.14</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1538,7 +1535,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>16.7</x:v>
+        <x:v>17.17</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1573,7 +1570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.8</x:v>
+        <x:v>5.83</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1605,7 +1602,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.98</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1622,7 +1619,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>16190506</x:v>
+        <x:v>16490506</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1631,19 +1628,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>401305024</x:v>
+        <x:v>409309024</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>26.16</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.79</x:v>
+        <x:v>24.82</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>29</x:v>
@@ -1675,7 +1672,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.53</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1710,7 +1707,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>41.02</x:v>
+        <x:v>40.6</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1745,7 +1742,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1780,7 +1777,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.9</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1815,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.56</x:v>
+        <x:v>6.54</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1847,7 +1844,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>150.1</x:v>
+        <x:v>145.7</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1882,7 +1879,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.1</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1917,7 +1914,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>86</x:v>
+        <x:v>86.9</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1952,7 +1949,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.52</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1987,7 +1984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.9</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2019,7 +2016,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.24</x:v>
+        <x:v>9.23</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2054,7 +2051,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>50.7</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2089,7 +2086,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>756</x:v>
+        <x:v>752.5</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2124,7 +2121,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>26.16</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2159,7 +2156,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.24</x:v>
+        <x:v>9.23</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2194,7 +2191,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.37</x:v>
+        <x:v>7.43</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
@@ -2229,7 +2226,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.08</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
@@ -2264,7 +2261,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.37</x:v>
+        <x:v>3.34</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2299,7 +2296,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.53</x:v>
+        <x:v>9.35</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2334,7 +2331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2366,7 +2363,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>7.02</x:v>
+        <x:v>7.72</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2383,7 +2380,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>12400339</x:v>
+        <x:v>12700000</x:v>
       </x:c>
       <x:c r="D30" s="0">
         <x:v>79451200</x:v>
@@ -2392,30 +2389,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>484332923</x:v>
+        <x:v>497724088</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1.56</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>44.54</x:v>
+        <x:v>43.82</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>39.06</x:v>
+        <x:v>39.19</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>1120876</x:v>
@@ -2436,7 +2433,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>47</x:v>
+        <x:v>47.02</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2447,10 +2444,10 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>1973951</x:v>
@@ -2471,21 +2468,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2506,7 +2503,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>41.66</x:v>
+        <x:v>40.24</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2514,10 +2511,10 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>3337681</x:v>
@@ -2538,7 +2535,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2549,10 +2546,10 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2573,7 +2570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2581,10 +2578,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>1364000</x:v>
@@ -2605,21 +2602,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>328.25</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2640,7 +2637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.82</x:v>
+        <x:v>21.32</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2648,10 +2645,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>507440</x:v>
@@ -2672,21 +2669,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>143.8</x:v>
+        <x:v>145.3</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2707,7 +2704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.42</x:v>
+        <x:v>35.2</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2715,10 +2712,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>2000000</x:v>
@@ -2739,21 +2736,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>40.94</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>324474</x:v>
@@ -2774,21 +2771,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.7</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2809,7 +2806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.15</x:v>
+        <x:v>13.26</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2817,10 +2814,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2841,7 +2838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.13</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2849,10 +2846,10 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>2000000</x:v>
@@ -2873,7 +2870,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.58</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2884,10 +2881,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>174500000</x:v>
@@ -2908,13 +2905,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -2922,7 +2919,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>635229</x:v>
@@ -2943,21 +2940,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>22.08</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>130000</x:v>
@@ -2978,21 +2975,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>25.26</x:v>
+        <x:v>24.82</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -3013,7 +3010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>215.3</x:v>
+        <x:v>216.4</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3021,10 +3018,10 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>447761</x:v>
@@ -3045,21 +3042,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>41.5</x:v>
+        <x:v>42.04</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>200000</x:v>
@@ -3080,21 +3077,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.84</x:v>
+        <x:v>20.56</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>575841</x:v>
@@ -3115,21 +3112,21 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>40.94</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>946718</x:v>
@@ -3150,21 +3147,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>79.55</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3185,7 +3182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>18.84</x:v>
+        <x:v>18.93</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3193,10 +3190,10 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>3043115</x:v>
@@ -3217,21 +3214,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21</x:v>
+        <x:v>21.28</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>2382736</x:v>
@@ -3252,21 +3249,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>91</x:v>
+        <x:v>91.6</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>13</x:v>
@@ -3287,7 +3284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>62.5</x:v>
+        <x:v>62.35</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3295,10 +3292,10 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>13</x:v>
@@ -3319,7 +3316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>4.52</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3327,10 +3324,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>13</x:v>
@@ -3351,7 +3348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>38.12</x:v>
+        <x:v>38.54</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3359,10 +3356,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>310000</x:v>
@@ -3383,21 +3380,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>10.05</x:v>
+        <x:v>9.93</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>2000000</x:v>
@@ -3418,7 +3415,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.8</x:v>
+        <x:v>19.18</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3429,10 +3426,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1250000</x:v>
@@ -3453,21 +3450,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.55</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>3077160</x:v>
@@ -3488,21 +3485,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>35.52</x:v>
+        <x:v>33.74</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3523,21 +3520,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.19</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3558,21 +3555,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>117.7</x:v>
+        <x:v>115.3</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>13</x:v>
@@ -3593,7 +3590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.72</x:v>
+        <x:v>40.74</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3601,10 +3598,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3636,10 +3633,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3660,21 +3657,21 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>59.8</x:v>
+        <x:v>59.05</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3695,7 +3692,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3706,10 +3703,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3730,7 +3727,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.9</x:v>
+        <x:v>21.52</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3741,10 +3738,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3765,21 +3762,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>8.12</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3800,21 +3797,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>49.8</x:v>
+        <x:v>50.45</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3835,21 +3832,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3870,7 +3867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>44.68</x:v>
+        <x:v>45.52</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3878,10 +3875,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3902,7 +3899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>8.1</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3910,10 +3907,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3934,21 +3931,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.95</x:v>
+        <x:v>7.66</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3975,15 +3972,15 @@
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4004,21 +4001,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.32</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4039,21 +4036,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.9</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4074,21 +4071,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>252</x:v>
+        <x:v>242.6</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4109,21 +4106,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.27</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4144,21 +4141,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>356.5</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4179,21 +4176,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>38.92</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4214,21 +4211,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>26.32</x:v>
+        <x:v>26.28</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4249,21 +4246,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1214</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4284,7 +4281,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>16.13</x:v>
+        <x:v>15.61</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4295,10 +4292,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4319,21 +4316,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.99</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4354,7 +4351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.14</x:v>
+        <x:v>18.49</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4362,10 +4359,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4386,13 +4383,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.59</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4400,7 +4397,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4421,21 +4418,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>145.2</x:v>
+        <x:v>139.6</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4456,21 +4453,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>94.4</x:v>
+        <x:v>93.9</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4491,13 +4488,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.09</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -4505,7 +4502,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4526,21 +4523,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>756</x:v>
+        <x:v>752.5</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4561,21 +4558,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.42</x:v>
+        <x:v>4.41</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4596,21 +4593,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.6</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4631,7 +4628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.67</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4639,10 +4636,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4663,21 +4660,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.96</x:v>
+        <x:v>29.6</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4704,15 +4701,15 @@
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4733,7 +4730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>36.18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4744,7 +4741,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4765,13 +4762,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>26.16</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -4779,7 +4776,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4800,21 +4797,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.24</x:v>
+        <x:v>9.23</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4835,7 +4832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.61</x:v>
+        <x:v>4.75</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4843,10 +4840,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4867,7 +4864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>8.32</x:v>
+        <x:v>8.44</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4875,10 +4872,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4899,24 +4896,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>118.5</x:v>
+        <x:v>115.5</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>4529358</x:v>
+        <x:v>4629834</x:v>
       </x:c>
       <x:c r="D104" s="0">
         <x:v>11160000</x:v>
@@ -4925,22 +4922,22 @@
         <x:v>125000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>42737485</x:v>
+        <x:v>44081332</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>4.06</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.15</x:v>
+        <x:v>13.26</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>9.44</x:v>
+        <x:v>9.52</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -4948,10 +4945,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1190000</x:v>
+        <x:v>1210000</x:v>
       </x:c>
       <x:c r="D105" s="0">
         <x:v>2160000</x:v>
@@ -4960,30 +4957,30 @@
         <x:v>35000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>44416627</x:v>
+        <x:v>45218625</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.68</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>40.8</x:v>
+        <x:v>40.32</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>37.32</x:v>
+        <x:v>37.37</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5004,21 +5001,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>103</x:v>
+        <x:v>104.9</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5039,7 +5036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>538</x:v>
+        <x:v>533.5</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5047,10 +5044,10 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5071,21 +5068,21 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.2</x:v>
+        <x:v>31.34</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5106,21 +5103,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.8</x:v>
+        <x:v>14.62</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5141,21 +5138,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.24</x:v>
+        <x:v>15.84</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5176,21 +5173,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>34.66</x:v>
+        <x:v>33.72</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>2975773</x:v>
@@ -5211,7 +5208,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>29.14</x:v>
+        <x:v>28.22</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5222,10 +5219,10 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>10994323</x:v>
@@ -5246,21 +5243,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.77</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>25876543</x:v>
@@ -5281,21 +5278,21 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.76</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5100000</x:v>
@@ -5316,21 +5313,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>60.1</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>13</x:v>
@@ -5351,7 +5348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5359,10 +5356,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>5000000</x:v>
@@ -5383,21 +5380,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.92</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>590777</x:v>
@@ -5418,21 +5415,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>18.35</x:v>
+        <x:v>18.14</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>13</x:v>
@@ -5453,7 +5450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>98.15</x:v>
+        <x:v>94.5</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5461,10 +5458,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5485,7 +5482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>538</x:v>
+        <x:v>533.5</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5493,10 +5490,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>53584</x:v>
@@ -5517,7 +5514,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>238.1</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5528,10 +5525,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>7550000</x:v>
@@ -5552,13 +5549,13 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>74.85</x:v>
+        <x:v>75.65</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5566,7 +5563,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>772649</x:v>
@@ -5587,21 +5584,21 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.9</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2097716</x:v>
@@ -5622,21 +5619,21 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.35</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>5185302</x:v>
@@ -5657,21 +5654,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.92</x:v>
+        <x:v>5.83</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>669111</x:v>
@@ -5692,21 +5689,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>594</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>38840</x:v>
@@ -5727,21 +5724,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>538</x:v>
+        <x:v>533.5</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>2146559</x:v>
@@ -5762,21 +5759,21 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>526</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>2250000</x:v>
@@ -5797,21 +5794,21 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>74.85</x:v>
+        <x:v>75.65</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>109200</x:v>
@@ -5832,21 +5829,21 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>73</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>1127000</x:v>
@@ -5867,21 +5864,21 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>60.75</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>3435564</x:v>
@@ -5902,21 +5899,21 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>444.25</x:v>
+        <x:v>449.75</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>109200</x:v>
@@ -5937,21 +5934,21 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>73</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>2550000</x:v>
@@ -5972,21 +5969,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.58</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1500000</x:v>
@@ -6007,21 +6004,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.35</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>281228</x:v>
@@ -6042,7 +6039,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>141.1</x:v>
+        <x:v>142.2</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6053,10 +6050,10 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>12514496</x:v>
@@ -6077,21 +6074,21 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.94</x:v>
+        <x:v>39.74</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
@@ -6112,7 +6109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>143.8</x:v>
+        <x:v>145.3</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6120,10 +6117,10 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>2550028</x:v>
@@ -6144,13 +6141,13 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>26.32</x:v>
+        <x:v>26.28</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6158,7 +6155,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>2000000</x:v>
@@ -6179,21 +6176,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>756</x:v>
+        <x:v>752.5</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>845945</x:v>
@@ -6214,21 +6211,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>280000</x:v>
@@ -6249,21 +6246,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>55.65</x:v>
+        <x:v>54.4</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>47311439</x:v>
@@ -6284,21 +6281,21 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>20000000</x:v>
@@ -6319,21 +6316,21 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>74.85</x:v>
+        <x:v>75.65</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>21446</x:v>
@@ -6354,21 +6351,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>64.05</x:v>
+        <x:v>61.05</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>19000</x:v>
@@ -6389,21 +6386,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>17.04</x:v>
+        <x:v>16.75</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>10000000</x:v>
@@ -6424,21 +6421,21 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>8.13</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="C148" s="0">
         <x:v>850000</x:v>
@@ -6459,21 +6456,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>8.6</x:v>
+        <x:v>9.1</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C149" s="0">
         <x:v>15000000</x:v>
@@ -6494,21 +6491,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>6397124</x:v>
@@ -6529,13 +6526,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>5.07</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -6543,7 +6540,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>8578668</x:v>
@@ -6564,7 +6561,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.52</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6575,10 +6572,10 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>9350000</x:v>
@@ -6599,21 +6596,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>298</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>13</x:v>
@@ -6634,7 +6631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.86</x:v>
+        <x:v>6.84</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6642,10 +6639,10 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C154" s="0">
         <x:v>1468255</x:v>
@@ -6666,21 +6663,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>500000</x:v>
@@ -6701,21 +6698,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>2.99</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>18900000</x:v>
@@ -6736,21 +6733,21 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>60.1</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>725000</x:v>
@@ -6771,21 +6768,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>4350000</x:v>
@@ -6806,21 +6803,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>94.4</x:v>
+        <x:v>93.9</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C159" s="0">
         <x:v>361000</x:v>
@@ -6841,21 +6838,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>55.65</x:v>
+        <x:v>54.4</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C160" s="0">
         <x:v>226000</x:v>
@@ -6876,21 +6873,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>265</x:v>
+        <x:v>259.25</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>1060056</x:v>
@@ -6911,21 +6908,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>215.3</x:v>
+        <x:v>216.4</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>1725000</x:v>
@@ -6946,21 +6943,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>132750000</x:v>
@@ -6981,21 +6978,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C164" s="0">
         <x:v>7921744</x:v>
@@ -7016,21 +7013,21 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.77</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>319</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>373000</x:v>
@@ -7051,21 +7048,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>322</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>13430000</x:v>
@@ -7086,21 +7083,21 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>128.7</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>15000000</x:v>
@@ -7121,21 +7118,21 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.92</x:v>
+        <x:v>5.83</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>324</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>10759347</x:v>
@@ -7156,21 +7153,21 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>12.05</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>326</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>10000000</x:v>
@@ -7191,21 +7188,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>4.99</x:v>
+        <x:v>4.85</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C170" s="0">
         <x:v>3081843</x:v>
@@ -7226,21 +7223,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>8.94</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>1348769</x:v>
@@ -7261,21 +7258,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>337.25</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>927506</x:v>
@@ -7296,13 +7293,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.62</x:v>
+        <x:v>19.5</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -271,373 +271,373 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>BLUME</x:t>
@@ -1433,7 +1433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>139.6</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1465,7 +1465,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>9.73</x:v>
+        <x:v>10.56</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1500,7 +1500,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.94</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>17.17</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1570,7 +1570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.83</x:v>
+        <x:v>5.77</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1602,7 +1602,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.7</x:v>
+        <x:v>23.34</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1637,7 +1637,7 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>26.96</x:v>
+        <x:v>27.22</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>24.82</x:v>
@@ -1672,7 +1672,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.1</x:v>
+        <x:v>13.14</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1707,7 +1707,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>40.6</x:v>
+        <x:v>41.12</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1742,7 +1742,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>60.9</x:v>
+        <x:v>61.05</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1777,7 +1777,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>8.1</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1812,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.54</x:v>
+        <x:v>6.49</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1844,7 +1844,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>145.7</x:v>
+        <x:v>141.1</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1879,7 +1879,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.26</x:v>
+        <x:v>6.51</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1914,7 +1914,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>86.9</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.26</x:v>
+        <x:v>22.1</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1984,7 +1984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>8.1</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2016,7 +2016,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.12</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2051,7 +2051,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>50.35</x:v>
+        <x:v>55.35</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>752.5</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2121,7 +2121,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>26.96</x:v>
+        <x:v>27.22</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2156,7 +2156,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.12</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.43</x:v>
+        <x:v>7.16</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
@@ -2261,7 +2261,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.34</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2296,7 +2296,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.35</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>34.62</x:v>
+        <x:v>34.98</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2363,7 +2363,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>7.72</x:v>
+        <x:v>6.95</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2380,7 +2380,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>12700000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="D30" s="0">
         <x:v>79451200</x:v>
@@ -2389,30 +2389,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>497724088</x:v>
+        <x:v>510900616</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1.6</x:v>
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.82</x:v>
+        <x:v>43.7</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>39.19</x:v>
+        <x:v>39.3</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>1120876</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>47.02</x:v>
+        <x:v>46.8</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2444,10 +2444,10 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>1973951</x:v>
@@ -2468,21 +2468,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>82.15</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2503,7 +2503,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>40.24</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2511,10 +2511,10 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>3337681</x:v>
@@ -2535,7 +2535,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2546,10 +2546,10 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2570,7 +2570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>40.08</x:v>
+        <x:v>39.4</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2578,10 +2578,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>1364000</x:v>
@@ -2602,21 +2602,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>327</x:v>
+        <x:v>323.5</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.32</x:v>
+        <x:v>21.16</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2645,10 +2645,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>507440</x:v>
@@ -2669,21 +2669,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>145.3</x:v>
+        <x:v>141.7</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2704,7 +2704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.2</x:v>
+        <x:v>35.9</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2712,10 +2712,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>2000000</x:v>
@@ -2736,21 +2736,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>40.9</x:v>
+        <x:v>41.4</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>324474</x:v>
@@ -2771,21 +2771,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.85</x:v>
+        <x:v>11.83</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2806,7 +2806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.26</x:v>
+        <x:v>13.41</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2814,10 +2814,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2838,7 +2838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>7.98</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2846,10 +2846,10 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>2000000</x:v>
@@ -2870,7 +2870,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.73</x:v>
+        <x:v>6.59</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2881,10 +2881,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>174500000</x:v>
@@ -2905,13 +2905,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.03</x:v>
+        <x:v>2.97</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -2919,7 +2919,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>635229</x:v>
@@ -2946,15 +2946,15 @@
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>130000</x:v>
@@ -2975,21 +2975,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.82</x:v>
+        <x:v>24.8</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -3010,7 +3010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>216.4</x:v>
+        <x:v>225.5</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3018,10 +3018,10 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>447761</x:v>
@@ -3042,21 +3042,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>42.04</x:v>
+        <x:v>41.98</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>200000</x:v>
@@ -3077,21 +3077,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>20.56</x:v>
+        <x:v>20.22</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>575841</x:v>
@@ -3112,21 +3112,21 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>40.9</x:v>
+        <x:v>41.4</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>946718</x:v>
@@ -3147,21 +3147,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>79</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3182,7 +3182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>18.93</x:v>
+        <x:v>18.54</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3190,10 +3190,10 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>3043115</x:v>
@@ -3214,21 +3214,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.28</x:v>
+        <x:v>21.14</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>2382736</x:v>
@@ -3249,21 +3249,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>91.6</x:v>
+        <x:v>94.2</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>13</x:v>
@@ -3284,7 +3284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>62.35</x:v>
+        <x:v>62.5</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3292,10 +3292,10 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>13</x:v>
@@ -3316,7 +3316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>4.63</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3324,10 +3324,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>13</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>38.54</x:v>
+        <x:v>38.64</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3356,10 +3356,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>310000</x:v>
@@ -3380,21 +3380,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>9.93</x:v>
+        <x:v>9.65</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>2000000</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>19.18</x:v>
+        <x:v>18.85</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3426,10 +3426,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1250000</x:v>
@@ -3450,21 +3450,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.42</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>3077160</x:v>
@@ -3485,21 +3485,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>33.74</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3520,21 +3520,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.18</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3555,21 +3555,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>115.3</x:v>
+        <x:v>114.1</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>13</x:v>
@@ -3590,7 +3590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.74</x:v>
+        <x:v>40.36</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3598,10 +3598,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3622,7 +3622,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.86</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3633,10 +3633,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3657,21 +3657,21 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>59.05</x:v>
+        <x:v>58.3</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3692,7 +3692,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.02</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3703,10 +3703,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3727,7 +3727,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.52</x:v>
+        <x:v>22.42</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3738,10 +3738,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3762,21 +3762,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>8.39</x:v>
+        <x:v>8.05</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3797,21 +3797,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>50.45</x:v>
+        <x:v>52.2</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3832,21 +3832,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>67.1</x:v>
+        <x:v>67.15</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3867,7 +3867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>45.52</x:v>
+        <x:v>47.5</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3875,10 +3875,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3899,7 +3899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>8.11</x:v>
+        <x:v>7.94</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3907,10 +3907,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3931,21 +3931,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.66</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3966,21 +3966,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.59</x:v>
+        <x:v>13.74</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4001,21 +4001,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.3</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4036,21 +4036,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.97</x:v>
+        <x:v>5.08</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4071,21 +4071,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>242.6</x:v>
+        <x:v>239.6</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4106,21 +4106,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.38</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4141,21 +4141,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>321</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4176,21 +4176,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>36.64</x:v>
+        <x:v>36.14</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4211,21 +4211,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>26.28</x:v>
+        <x:v>26.64</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4246,21 +4246,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1305</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4281,7 +4281,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.61</x:v>
+        <x:v>15.78</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4292,10 +4292,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4316,21 +4316,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>8.1</x:v>
+        <x:v>7.29</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4351,7 +4351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>18.49</x:v>
+        <x:v>18.75</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4359,10 +4359,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4383,13 +4383,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>18.9</x:v>
+        <x:v>19.75</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4397,7 +4397,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4418,21 +4418,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>139.6</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4453,21 +4453,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>93.9</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4488,13 +4488,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.07</x:v>
+        <x:v>5.02</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -4502,7 +4502,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4523,21 +4523,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>752.5</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4558,21 +4558,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.41</x:v>
+        <x:v>4.39</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4593,21 +4593,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.7</x:v>
+        <x:v>10.76</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4628,7 +4628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.7</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4636,10 +4636,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4660,21 +4660,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.6</x:v>
+        <x:v>29.4</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4695,21 +4695,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.82</x:v>
+        <x:v>3.88</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4730,7 +4730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>35</x:v>
+        <x:v>34.42</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4741,7 +4741,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4762,13 +4762,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>26.96</x:v>
+        <x:v>27.22</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -4776,7 +4776,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4797,21 +4797,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.12</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4832,7 +4832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.75</x:v>
+        <x:v>4.79</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4840,10 +4840,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4864,7 +4864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>8.44</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4872,10 +4872,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4896,21 +4896,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>115.5</x:v>
+        <x:v>113.5</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>4629834</x:v>
@@ -4931,13 +4931,13 @@
         <x:v>4.15</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.26</x:v>
+        <x:v>13.41</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>9.52</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -4945,7 +4945,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1210000</x:v>
@@ -4966,7 +4966,7 @@
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>40.32</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>37.37</x:v>
@@ -4980,7 +4980,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5001,7 +5001,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>104.9</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5036,7 +5036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>533.5</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5047,7 +5047,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5068,13 +5068,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.34</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -5082,7 +5082,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5103,13 +5103,13 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.62</x:v>
+        <x:v>14.39</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -5117,7 +5117,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5138,13 +5138,13 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>15.84</x:v>
+        <x:v>16.16</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -5152,7 +5152,7 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5173,7 +5173,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>33.72</x:v>
+        <x:v>33.34</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
@@ -5208,7 +5208,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>28.22</x:v>
+        <x:v>27.76</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5243,7 +5243,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.77</x:v>
+        <x:v>15.47</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
@@ -5278,7 +5278,7 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>15.76</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
@@ -5313,7 +5313,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>58.5</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
@@ -5348,7 +5348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5380,7 +5380,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>8.92</x:v>
+        <x:v>8.86</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
@@ -5415,7 +5415,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>18.14</x:v>
+        <x:v>18.01</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
@@ -5450,7 +5450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>94.5</x:v>
+        <x:v>90.95</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5482,7 +5482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>533.5</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5514,7 +5514,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>241</x:v>
+        <x:v>235.5</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5549,7 +5549,7 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>75.65</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
@@ -5584,7 +5584,7 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>8.1</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
@@ -5619,13 +5619,13 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.3</x:v>
+        <x:v>15.24</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -5654,13 +5654,13 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.83</x:v>
+        <x:v>5.88</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -5689,13 +5689,13 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>591</x:v>
+        <x:v>560.5</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -5724,7 +5724,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>533.5</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
@@ -5759,13 +5759,13 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>512</x:v>
+        <x:v>516.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -5794,7 +5794,7 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>75.65</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
@@ -5829,13 +5829,13 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>70.5</x:v>
+        <x:v>69.35</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
@@ -5864,13 +5864,13 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>62.1</x:v>
+        <x:v>61.5</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -5899,13 +5899,13 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>449.75</x:v>
+        <x:v>446.75</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
@@ -5934,13 +5934,13 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>70.5</x:v>
+        <x:v>69.35</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5969,7 +5969,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.27</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
@@ -6004,7 +6004,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.3</x:v>
+        <x:v>15.24</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
@@ -6039,7 +6039,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>142.2</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6074,7 +6074,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.74</x:v>
+        <x:v>39.6</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
@@ -6085,7 +6085,7 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>267</x:v>
@@ -6109,7 +6109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>145.3</x:v>
+        <x:v>141.7</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6117,7 +6117,7 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>269</x:v>
@@ -6141,13 +6141,13 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>26.28</x:v>
+        <x:v>26.64</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6176,7 +6176,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>752.5</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
@@ -6187,7 +6187,7 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>272</x:v>
@@ -6211,7 +6211,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
@@ -6246,7 +6246,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>54.4</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
@@ -6281,13 +6281,13 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -6316,7 +6316,7 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>75.65</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
@@ -6351,13 +6351,13 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>61.05</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
@@ -6386,7 +6386,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>16.75</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
@@ -6397,7 +6397,7 @@
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>282</x:v>
@@ -6421,7 +6421,7 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>7.98</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
@@ -6456,13 +6456,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>9.1</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -6491,7 +6491,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.82</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
@@ -6526,7 +6526,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>4.92</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
@@ -6561,7 +6561,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.26</x:v>
+        <x:v>22.1</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6596,7 +6596,7 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.54</x:v>
+        <x:v>8.91</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
@@ -6631,7 +6631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.84</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6639,7 +6639,7 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>298</x:v>
@@ -6663,7 +6663,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>82.15</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
@@ -6698,13 +6698,13 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.03</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -6733,7 +6733,7 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>58.5</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
@@ -6744,7 +6744,7 @@
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>304</x:v>
@@ -6768,7 +6768,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>40.08</x:v>
+        <x:v>39.4</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
@@ -6779,7 +6779,7 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>306</x:v>
@@ -6803,7 +6803,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>93.9</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
@@ -6838,7 +6838,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>54.4</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
@@ -6873,18 +6873,18 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>259.25</x:v>
+        <x:v>259.5</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>310</x:v>
@@ -6908,7 +6908,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>216.4</x:v>
+        <x:v>225.5</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
@@ -6943,7 +6943,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
@@ -6954,7 +6954,7 @@
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>315</x:v>
@@ -6978,13 +6978,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>3.03</x:v>
+        <x:v>2.97</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -7013,7 +7013,7 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.77</x:v>
+        <x:v>15.47</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
@@ -7048,7 +7048,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.53</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
@@ -7118,7 +7118,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.83</x:v>
+        <x:v>5.88</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
@@ -7153,13 +7153,13 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>11.77</x:v>
+        <x:v>11.64</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
@@ -7188,7 +7188,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>4.85</x:v>
+        <x:v>4.83</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
@@ -7223,7 +7223,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>8.4</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
@@ -7258,7 +7258,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>325</x:v>
+        <x:v>326.5</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
@@ -7293,7 +7293,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.5</x:v>
+        <x:v>19.18</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -103,174 +103,177 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>21.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>PNLSN</x:t>
   </x:si>
   <x:si>
@@ -635,9 +638,6 @@
   </x:si>
   <x:si>
     <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>BLUME</x:t>
@@ -1433,7 +1433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>145</x:v>
+        <x:v>144.6</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1465,7 +1465,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>10.56</x:v>
+        <x:v>11.61</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>7.13</x:v>
@@ -1500,7 +1500,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>25.94</x:v>
+        <x:v>26.08</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>28.75</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>17.29</x:v>
+        <x:v>17.64</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>15.08</x:v>
@@ -1570,7 +1570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>5.77</x:v>
+        <x:v>5.79</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1602,7 +1602,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.34</x:v>
+        <x:v>23.44</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>23.54</x:v>
@@ -1619,7 +1619,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>16490506</x:v>
+        <x:v>16690506</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>80000000</x:v>
@@ -1628,19 +1628,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>409309024</x:v>
+        <x:v>414733024</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>27.22</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.82</x:v>
+        <x:v>24.85</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>29</x:v>
@@ -1672,7 +1672,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.14</x:v>
+        <x:v>13.67</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>13.34</x:v>
@@ -1707,7 +1707,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>41.12</x:v>
+        <x:v>39.86</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>39.18</x:v>
@@ -1742,7 +1742,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>61.05</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>59.93</x:v>
@@ -1777,7 +1777,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.82</x:v>
+        <x:v>7.77</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>48.39</x:v>
@@ -1812,7 +1812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.49</x:v>
+        <x:v>6.29</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>0</x:v>
@@ -1844,7 +1844,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>141.1</x:v>
+        <x:v>136.8</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.97</x:v>
@@ -1879,7 +1879,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.51</x:v>
+        <x:v>6.41</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>6.75</x:v>
@@ -1914,7 +1914,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>61.87</x:v>
@@ -1949,7 +1949,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.1</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>21.06</x:v>
@@ -1984,7 +1984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.82</x:v>
+        <x:v>7.77</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>0</x:v>
@@ -2016,7 +2016,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.12</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>9.83</x:v>
@@ -2051,7 +2051,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>55.35</x:v>
+        <x:v>53.5</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>23.95</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>763</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>528.86</x:v>
@@ -2121,7 +2121,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>27.22</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>24.19</x:v>
@@ -2156,7 +2156,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.12</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>10.74</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.16</x:v>
+        <x:v>7.19</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>24.08</x:v>
@@ -2226,7 +2226,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>27.31</x:v>
@@ -2261,7 +2261,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.3</x:v>
+        <x:v>3.27</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>4.46</x:v>
@@ -2296,7 +2296,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.32</x:v>
+        <x:v>9.21</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>13.09</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>34.98</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2363,7 +2363,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>6.95</x:v>
+        <x:v>7.64</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>52.14</x:v>
@@ -2398,21 +2398,21 @@
         <x:v>1.64</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>43.7</x:v>
+        <x:v>44.08</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>39.3</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>1120876</x:v>
@@ -2433,7 +2433,7 @@
         <x:v>1.49</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>46.8</x:v>
+        <x:v>46.7</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>38.07</x:v>
@@ -2444,10 +2444,10 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>1973951</x:v>
@@ -2468,21 +2468,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>84</x:v>
+        <x:v>84.7</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2503,7 +2503,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>41</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>0</x:v>
@@ -2511,10 +2511,10 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>3337681</x:v>
@@ -2535,7 +2535,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>6.14</x:v>
@@ -2546,10 +2546,10 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2570,7 +2570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.4</x:v>
+        <x:v>39.68</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2578,10 +2578,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>1364000</x:v>
@@ -2602,21 +2602,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>323.5</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.16</x:v>
+        <x:v>21.18</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2645,10 +2645,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>507440</x:v>
@@ -2669,21 +2669,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>141.7</x:v>
+        <x:v>140.6</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2704,7 +2704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>35.9</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2712,10 +2712,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>2000000</x:v>
@@ -2736,21 +2736,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>41.4</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>324474</x:v>
@@ -2771,21 +2771,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.83</x:v>
+        <x:v>11.73</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2806,7 +2806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>13.41</x:v>
+        <x:v>14.75</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2814,10 +2814,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2838,7 +2838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>7.95</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>0</x:v>
@@ -2846,10 +2846,10 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>2000000</x:v>
@@ -2870,7 +2870,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.59</x:v>
+        <x:v>6.64</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.12</x:v>
@@ -2881,10 +2881,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>174500000</x:v>
@@ -2905,13 +2905,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>2.97</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -2919,7 +2919,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>635229</x:v>
@@ -2940,21 +2940,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>22.5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>130000</x:v>
@@ -2975,21 +2975,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.8</x:v>
+        <x:v>24.82</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -3010,7 +3010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>225.5</x:v>
+        <x:v>235.2</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>0</x:v>
@@ -3018,10 +3018,10 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>447761</x:v>
@@ -3042,21 +3042,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>41.98</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>200000</x:v>
@@ -3077,21 +3077,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>20.22</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>575841</x:v>
@@ -3112,21 +3112,21 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>41.4</x:v>
+        <x:v>43.1</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>45.38</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>946718</x:v>
@@ -3147,21 +3147,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>77.8</x:v>
+        <x:v>79.3</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3182,7 +3182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>18.54</x:v>
+        <x:v>18.49</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>0</x:v>
@@ -3190,10 +3190,10 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>3043115</x:v>
@@ -3214,21 +3214,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.14</x:v>
+        <x:v>21.48</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>2382736</x:v>
@@ -3249,21 +3249,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>94.2</x:v>
+        <x:v>92.9</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>13</x:v>
@@ -3284,7 +3284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>62.5</x:v>
+        <x:v>61.25</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>0</x:v>
@@ -3292,10 +3292,10 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>13</x:v>
@@ -3316,7 +3316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>4.73</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3324,10 +3324,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>13</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>38.64</x:v>
+        <x:v>38.32</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3356,10 +3356,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>310000</x:v>
@@ -3380,21 +3380,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.95</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>2000000</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.85</x:v>
+        <x:v>18.59</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>15.68</x:v>
@@ -3426,10 +3426,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1250000</x:v>
@@ -3450,21 +3450,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.22</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>3077160</x:v>
@@ -3485,21 +3485,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>32</x:v>
+        <x:v>33.02</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>10.92</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3520,21 +3520,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.15</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3555,21 +3555,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>114.1</x:v>
+        <x:v>114.3</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>13</x:v>
@@ -3590,7 +3590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.36</x:v>
+        <x:v>40.82</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3598,10 +3598,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3622,7 +3622,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.84</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3633,10 +3633,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3657,21 +3657,21 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>58.3</x:v>
+        <x:v>58.45</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3692,7 +3692,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.08</x:v>
+        <x:v>20.3</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3703,10 +3703,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3727,7 +3727,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>22.42</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3738,10 +3738,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3762,21 +3762,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>8.05</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3797,21 +3797,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>52.2</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3832,21 +3832,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>67.15</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>13</x:v>
@@ -3867,7 +3867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>47.5</x:v>
+        <x:v>45.72</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3875,10 +3875,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>13</x:v>
@@ -3899,7 +3899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.94</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3907,10 +3907,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3931,21 +3931,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.55</x:v>
+        <x:v>7.45</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3966,21 +3966,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.74</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4001,21 +4001,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.25</x:v>
+        <x:v>11.32</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4036,21 +4036,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>5.08</x:v>
+        <x:v>4.58</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4071,21 +4071,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>239.6</x:v>
+        <x:v>250.5</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4106,21 +4106,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>12.1</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4141,21 +4141,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>289</x:v>
+        <x:v>260.25</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>48000</x:v>
@@ -4176,21 +4176,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>36.14</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>29.38</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4211,21 +4211,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>26.64</x:v>
+        <x:v>26.1</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>195050</x:v>
@@ -4246,21 +4246,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1321</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>66.33</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>3228679</x:v>
@@ -4281,7 +4281,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.78</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>15.92</x:v>
@@ -4292,10 +4292,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>150000</x:v>
@@ -4316,21 +4316,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>7.29</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4351,7 +4351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>18.75</x:v>
+        <x:v>18.46</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0</x:v>
@@ -4359,10 +4359,10 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>366107</x:v>
@@ -4383,13 +4383,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>19.75</x:v>
+        <x:v>19.76</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4397,7 +4397,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>120000</x:v>
@@ -4418,21 +4418,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>145</x:v>
+        <x:v>144.6</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>13050000</x:v>
@@ -4453,21 +4453,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>92.4</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>12182251</x:v>
@@ -4488,13 +4488,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.02</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>4.06</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -4502,7 +4502,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>1000000</x:v>
@@ -4523,21 +4523,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>763</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>300000</x:v>
@@ -4558,21 +4558,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.39</x:v>
+        <x:v>4.38</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>2175097</x:v>
@@ -4593,21 +4593,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.76</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>13</x:v>
@@ -4628,7 +4628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.65</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>0</x:v>
@@ -4636,10 +4636,10 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>43000</x:v>
@@ -4660,21 +4660,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.4</x:v>
+        <x:v>29.42</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>9937037</x:v>
@@ -4695,21 +4695,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.88</x:v>
+        <x:v>3.81</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>13</x:v>
@@ -4730,7 +4730,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>34.42</x:v>
+        <x:v>33.96</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>0</x:v>
@@ -4741,7 +4741,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>13064888</x:v>
@@ -4762,13 +4762,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>27.22</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -4776,7 +4776,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>111673026</x:v>
@@ -4797,21 +4797,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.12</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
@@ -4832,7 +4832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.79</x:v>
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4840,10 +4840,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -4864,7 +4864,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>8.66</x:v>
+        <x:v>8.74</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>0</x:v>
@@ -4872,10 +4872,10 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1100000</x:v>
@@ -4896,24 +4896,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>113.5</x:v>
+        <x:v>114.1</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>4629834</x:v>
+        <x:v>4952647</x:v>
       </x:c>
       <x:c r="D104" s="0">
         <x:v>11160000</x:v>
@@ -4922,22 +4922,22 @@
         <x:v>125000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>44081332</x:v>
+        <x:v>48332157</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>4.15</x:v>
+        <x:v>4.44</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>13.41</x:v>
+        <x:v>14.75</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>9.52</x:v>
+        <x:v>9.76</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -4945,7 +4945,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1210000</x:v>
@@ -4966,13 +4966,13 @@
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>40.4</x:v>
+        <x:v>39.98</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>37.37</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -4980,7 +4980,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>1989802</x:v>
@@ -5001,7 +5001,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>105</x:v>
+        <x:v>105.3</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>39.56</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5036,7 +5036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>510</x:v>
+        <x:v>484.5</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5047,7 +5047,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>1000000</x:v>
@@ -5068,13 +5068,13 @@
         <x:v>1.22</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.08</x:v>
+        <x:v>31.7</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>24.03</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -5082,7 +5082,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>300000</x:v>
@@ -5103,13 +5103,13 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.39</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -5117,7 +5117,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>8291656</x:v>
@@ -5138,13 +5138,13 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -5152,7 +5152,7 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>76908759</x:v>
@@ -5173,7 +5173,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>33.34</x:v>
+        <x:v>33.48</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>25.74</x:v>
@@ -5208,7 +5208,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>27.76</x:v>
+        <x:v>27.16</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>15.05</x:v>
@@ -5243,7 +5243,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.47</x:v>
+        <x:v>15.55</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>16.65</x:v>
@@ -5278,7 +5278,7 @@
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>15.8</x:v>
+        <x:v>15.27</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>9.47</x:v>
@@ -5313,7 +5313,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>58.95</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>30.45</x:v>
@@ -5348,7 +5348,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.53</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5380,7 +5380,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>8.86</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>7.82</x:v>
@@ -5415,7 +5415,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>18.01</x:v>
+        <x:v>17.85</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>21.06</x:v>
@@ -5450,7 +5450,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>90.95</x:v>
+        <x:v>89.9</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>0</x:v>
@@ -5482,7 +5482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>510</x:v>
+        <x:v>484.5</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5514,7 +5514,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>235.5</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>154.36</x:v>
@@ -5549,7 +5549,7 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>76.85</x:v>
+        <x:v>78.65</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>14.81</x:v>
@@ -5584,7 +5584,7 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.82</x:v>
+        <x:v>7.77</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>33.08</x:v>
@@ -5619,13 +5619,13 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.24</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -5654,13 +5654,13 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.88</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -5689,13 +5689,13 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>560.5</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -5724,7 +5724,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>510</x:v>
+        <x:v>484.5</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>242.84</x:v>
@@ -5759,13 +5759,13 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>516.5</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>265.4</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -5794,7 +5794,7 @@
         <x:v>0.56</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>76.85</x:v>
+        <x:v>78.65</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>14.11</x:v>
@@ -5829,13 +5829,13 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>69.35</x:v>
+        <x:v>68.35</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
@@ -5864,13 +5864,13 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>61.5</x:v>
+        <x:v>67.65</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>21.86</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -5899,13 +5899,13 @@
         <x:v>3.07</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>446.75</x:v>
+        <x:v>402.25</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>32.31</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
@@ -5934,13 +5934,13 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>69.35</x:v>
+        <x:v>68.35</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>41.16</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5969,7 +5969,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.27</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.01</x:v>
@@ -6004,7 +6004,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.24</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>14.58</x:v>
@@ -6039,7 +6039,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>135.2</x:v>
@@ -6074,7 +6074,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.6</x:v>
+        <x:v>39.58</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>43.69</x:v>
@@ -6085,7 +6085,7 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>267</x:v>
@@ -6109,7 +6109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>141.7</x:v>
+        <x:v>140.6</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6117,7 +6117,7 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>269</x:v>
@@ -6141,13 +6141,13 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>26.64</x:v>
+        <x:v>26.1</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>17.59</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6176,7 +6176,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>763</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>488.11</x:v>
@@ -6187,7 +6187,7 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>272</x:v>
@@ -6211,7 +6211,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>11.89</x:v>
@@ -6246,7 +6246,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>52</x:v>
+        <x:v>50.8</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>42.47</x:v>
@@ -6281,13 +6281,13 @@
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.53</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -6316,7 +6316,7 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>76.85</x:v>
+        <x:v>78.65</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>11</x:v>
@@ -6351,13 +6351,13 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>59</x:v>
+        <x:v>58.75</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
@@ -6386,7 +6386,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>17.3</x:v>
+        <x:v>17.48</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>71.32</x:v>
@@ -6397,7 +6397,7 @@
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>282</x:v>
@@ -6421,7 +6421,7 @@
         <x:v>0.35</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>7.95</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>35.24</x:v>
@@ -6456,13 +6456,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -6491,7 +6491,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>2.91</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>1.6</x:v>
@@ -6526,7 +6526,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>19.21</x:v>
@@ -6561,7 +6561,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>22.1</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>21.49</x:v>
@@ -6596,7 +6596,7 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>8.91</x:v>
+        <x:v>9.02</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>7.44</x:v>
@@ -6631,7 +6631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>6.8</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>0</x:v>
@@ -6639,7 +6639,7 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>298</x:v>
@@ -6663,7 +6663,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>84</x:v>
+        <x:v>84.7</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>51.7</x:v>
@@ -6698,13 +6698,13 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -6733,7 +6733,7 @@
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>58.95</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>31.67</x:v>
@@ -6744,7 +6744,7 @@
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>304</x:v>
@@ -6768,7 +6768,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>39.4</x:v>
+        <x:v>39.68</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>66.95</x:v>
@@ -6779,7 +6779,7 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>306</x:v>
@@ -6803,7 +6803,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>92.4</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>96.34</x:v>
@@ -6838,7 +6838,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>52</x:v>
+        <x:v>50.8</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>41.84</x:v>
@@ -6873,18 +6873,18 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>259.5</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>136.8</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>310</x:v>
@@ -6908,7 +6908,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>225.5</x:v>
+        <x:v>235.2</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>57.32</x:v>
@@ -6943,7 +6943,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.49</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>1.16</x:v>
@@ -6954,7 +6954,7 @@
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>315</x:v>
@@ -6978,13 +6978,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>2.97</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -7013,7 +7013,7 @@
         <x:v>3.67</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.47</x:v>
+        <x:v>15.55</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>19.44</x:v>
@@ -7048,7 +7048,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.41</x:v>
+        <x:v>7.51</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>63.77</x:v>
@@ -7083,7 +7083,7 @@
         <x:v>3.63</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>133</x:v>
+        <x:v>135.1</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>68.86</x:v>
@@ -7118,7 +7118,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>5.88</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>11.75</x:v>
@@ -7153,13 +7153,13 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>11.64</x:v>
+        <x:v>11.71</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>12.91</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
@@ -7188,7 +7188,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>4.83</x:v>
+        <x:v>4.86</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>13.33</x:v>
@@ -7223,7 +7223,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>8.21</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>14.27</x:v>
@@ -7258,7 +7258,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>326.5</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>166.26</x:v>
@@ -7293,7 +7293,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>19.18</x:v>
+        <x:v>19.6</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,24 +49,39 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.04.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
     <x:t>31.03.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>EFOR</x:t>
   </x:si>
   <x:si>
     <x:t>25.03.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>GWIND</x:t>
   </x:si>
   <x:si>
@@ -103,546 +118,525 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>22.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUME</x:t>
   </x:si>
   <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
@@ -652,9 +646,6 @@
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
     <x:t>A1CAP</x:t>
   </x:si>
   <x:si>
@@ -745,12 +736,6 @@
     <x:t>01.08.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>11.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.02.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>MERKO</x:t>
   </x:si>
   <x:si>
@@ -769,42 +754,12 @@
     <x:t>30.01.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.01.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>02.01.2025</x:t>
   </x:si>
   <x:si>
     <x:t>07.01.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>13.12.2024</x:t>
   </x:si>
   <x:si>
@@ -814,60 +769,21 @@
     <x:t>22.11.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>05.11.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2024</x:t>
-  </x:si>
-  <x:si>
     <x:t>15.10.2024</x:t>
   </x:si>
   <x:si>
     <x:t>27.03.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2024</x:t>
+    <x:t>ERCB</x:t>
   </x:si>
   <x:si>
     <x:t>08.10.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>31.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.09.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.02.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>OYLUM</x:t>
   </x:si>
   <x:si>
@@ -904,12 +820,6 @@
     <x:t>29.05.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.07.2024</x:t>
-  </x:si>
-  <x:si>
     <x:t>25.06.2024</x:t>
   </x:si>
   <x:si>
@@ -922,51 +832,21 @@
     <x:t>13.06.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>12.06.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.01.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>04.06.2024</x:t>
   </x:si>
   <x:si>
     <x:t>02.08.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>29.05.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
     <x:t>17.05.2024</x:t>
   </x:si>
   <x:si>
     <x:t>28.01.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.03.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.11.2024</x:t>
-  </x:si>
-  <x:si>
     <x:t>08.03.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>06.03.2024</x:t>
-  </x:si>
-  <x:si>
     <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
@@ -976,18 +856,6 @@
     <x:t>12.09.2024</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.01.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.12.2023</x:t>
-  </x:si>
-  <x:si>
     <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
@@ -1019,6 +887,12 @@
   </x:si>
   <x:si>
     <x:t>24.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.12.2023</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1369,7 +1243,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K172"/>
+  <x:dimension ref="A1:K145"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1414,29 +1288,32 @@
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" s="0">
+        <x:v>7999148</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E2" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F2" s="0">
+        <x:v>168715651</x:v>
+      </x:c>
+      <x:c r="G2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="0">
+        <x:v>2.11</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>19.91</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="0">
-        <x:v>26398084</x:v>
-      </x:c>
-      <x:c r="E2" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>144.6</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -1444,675 +1321,666 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>1500000000</x:v>
+      </x:c>
       <x:c r="E3" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>127481195</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>11.61</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>820810</x:v>
+      <x:c r="C4" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>7300000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>225000000</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>23601918</x:v>
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>26.08</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>28.75</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>1001579</x:v>
+      <x:c r="C5" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>10000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F5" s="0">
-        <x:v>15106723</x:v>
+      <x:c r="F5" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>17.64</x:v>
+        <x:v>130.1</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>15.08</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>127481195</x:v>
+      </x:c>
+      <x:c r="G6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="0">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
+        <x:v>10.78</x:v>
+      </x:c>
+      <x:c r="J6" s="0">
+        <x:v>7.13</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E6" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="0">
-        <x:v>5.79</x:v>
-      </x:c>
-      <x:c r="J6" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>1897370</x:v>
+        <x:v>820810</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>40000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>44672185</x:v>
+        <x:v>23601918</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>2.52</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>23.44</x:v>
+        <x:v>28.86</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>23.54</x:v>
+        <x:v>28.75</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>16690506</x:v>
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>80000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>414733024</x:v>
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.64</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>28.3</x:v>
+        <x:v>17.09</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>24.85</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>7024156</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>80000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>93719334</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.67</x:v>
+        <x:v>5.73</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>13.34</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>3500000</x:v>
+        <x:v>1897370</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>49400000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>137144284</x:v>
+        <x:v>44672185</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0.71</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>39.86</x:v>
+        <x:v>23.04</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>39.18</x:v>
+        <x:v>23.54</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>3753472</x:v>
+        <x:v>17060506</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>6000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>432000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>224929072</x:v>
+        <x:v>424934524</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>60.3</x:v>
+        <x:v>27.18</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>59.93</x:v>
+        <x:v>24.91</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>3189049</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>4000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>154328962</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>7.77</x:v>
+        <x:v>13.32</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>48.39</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>35000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.29</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>0</x:v>
+        <x:v>39.18</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>875000</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>10000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>400000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>52471192</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.11</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>136.8</x:v>
+        <x:v>58.35</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>59.97</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>6248196</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>35000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>42144731</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>1.56</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>6.41</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>6.75</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>236122</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1700000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>110000000</x:v>
-      </x:c>
-      <x:c r="F16" s="0">
-        <x:v>14609667</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>82</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>61.87</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>1000000</x:v>
+        <x:v>875000</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E17" s="0">
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>21055375</x:v>
+        <x:v>52471192</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>22.52</x:v>
+        <x:v>126.9</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>21.06</x:v>
+        <x:v>59.97</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>6248196</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>2000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F18" s="0">
+        <x:v>42144731</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.77</x:v>
+        <x:v>6.66</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>0</x:v>
+        <x:v>6.75</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>84837201</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>200000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>834313382</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>9.24</x:v>
+        <x:v>79.25</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>9.83</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>16445115</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E20" s="0">
-        <x:v>500000000</x:v>
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>393919718</x:v>
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>53.5</x:v>
+        <x:v>21.76</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>23.95</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>1110000</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D21" s="0">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="F21" s="0">
-        <x:v>587039028</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>760</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>528.86</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24398659</x:v>
+        <x:v>84837201</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>40000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>850000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>590270273</x:v>
+        <x:v>834313382</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
@@ -2121,173 +1989,173 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>28.3</x:v>
+        <x:v>8.96</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>24.19</x:v>
+        <x:v>9.83</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>46563878</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>50000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>500007798</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.52</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.24</x:v>
+        <x:v>51.75</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>10.74</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="C24" s="0">
-        <x:v>226257</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>9000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>240000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>5447709</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>7.19</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>24.08</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>1969635</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="E25" s="0">
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>53800530</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>1.03</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>23</x:v>
+        <x:v>27.18</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>27.31</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>1000000</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>30000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>400000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>4455000</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.27</x:v>
+        <x:v>8.96</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>4.46</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>100000</x:v>
+        <x:v>226257</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>13760000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>300000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1308500</x:v>
+        <x:v>5447709</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>0</x:v>
@@ -2296,281 +2164,284 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.21</x:v>
+        <x:v>7.18</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>13.09</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>1969635</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E28" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F28" s="0">
+        <x:v>53800530</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>35</x:v>
+        <x:v>24.66</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>0</x:v>
+        <x:v>27.31</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>5831653</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>500000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>304086107</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>7.64</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>52.14</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>13000000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>79451200</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>510900616</x:v>
+        <x:v>1308500</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1.64</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>44.08</x:v>
+        <x:v>8.87</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>39.3</x:v>
+        <x:v>13.09</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>1120876</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2500000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>80000000</x:v>
-      </x:c>
-      <x:c r="F31" s="0">
-        <x:v>42676393</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>3.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>46.7</x:v>
+        <x:v>34.4</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>38.07</x:v>
-      </x:c>
-      <x:c r="K31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>1973951</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>135510760</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>3.75</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>2.47</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>84.7</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>68.65</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>15000000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>510900616</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0</x:v>
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>40.9</x:v>
+        <x:v>42.54</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>0</x:v>
+        <x:v>39.3</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>1973951</x:v>
+      </x:c>
+      <x:c r="D34" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E34" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>135510760</x:v>
+      </x:c>
+      <x:c r="G34" s="0">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="H34" s="0">
+        <x:v>2.47</x:v>
+      </x:c>
+      <x:c r="I34" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="J34" s="0">
+        <x:v>68.65</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>3337681</x:v>
-      </x:c>
-      <x:c r="D34" s="0">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="E34" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0">
-        <x:v>20505183</x:v>
-      </x:c>
-      <x:c r="G34" s="0">
-        <x:v>1.43</x:v>
-      </x:c>
-      <x:c r="H34" s="0">
-        <x:v>0.13</x:v>
-      </x:c>
-      <x:c r="I34" s="0">
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="J34" s="0">
-        <x:v>6.14</x:v>
-      </x:c>
-      <x:c r="K34" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>9275000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>950000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.68</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2581,63 +2452,63 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>1364000</x:v>
+        <x:v>3337681</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>23460000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>9000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>409075556</x:v>
+        <x:v>20505183</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.7</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>325</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>299.91</x:v>
+        <x:v>6.14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>380000000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>21.18</x:v>
+        <x:v>40.76</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2645,66 +2516,66 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>507440</x:v>
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>2500000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>100000000</x:v>
+        <x:v>9000000000</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>42117724</x:v>
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2.67</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>140.6</x:v>
+        <x:v>315.75</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>83</x:v>
+        <x:v>299.91</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>10000000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>36.4</x:v>
+        <x:v>20.7</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2712,480 +2583,480 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>2000000</x:v>
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>81947000</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>2</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>43.1</x:v>
+        <x:v>142.8</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>40.97</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>324474</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>5000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F41" s="0">
-        <x:v>1781383</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.73</x:v>
+        <x:v>35.72</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>5.49</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E42" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>14.75</x:v>
+        <x:v>41.5</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>0</x:v>
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>100000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>7.96</x:v>
+        <x:v>12.88</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>2000000</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E44" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F44" s="0">
-        <x:v>12245700</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>6.64</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>6.12</x:v>
-      </x:c>
-      <x:c r="K44" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C45" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F45" s="0">
-        <x:v>694527000</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.16</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K45" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>635229</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>11323561</x:v>
+        <x:v>12245700</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>23</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>17.83</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D47" s="0">
-        <x:v>3500000</x:v>
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>4947800</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>24.82</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>38.06</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D48" s="0">
-        <x:v>5000000</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>235.2</x:v>
+        <x:v>24.66</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>0</x:v>
+        <x:v>17.83</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>447761</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>3000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>120000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>18415143</x:v>
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>40.4</x:v>
+        <x:v>25.14</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>41.13</x:v>
+        <x:v>38.06</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>200000</x:v>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F50" s="0">
-        <x:v>4022593</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.24</x:v>
+        <x:v>236.5</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K50" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>575841</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>750000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>100000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>26128790</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.58</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>43.1</x:v>
+        <x:v>39.6</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>45.38</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>946718</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>37333519</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>7.55</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>79.3</x:v>
+        <x:v>18.02</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>39.43</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
+      <x:c r="C53" s="0">
+        <x:v>946718</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>37333519</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>7.55</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>81.4</x:v>
+      </x:c>
+      <x:c r="J53" s="0">
+        <x:v>39.43</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>18.49</x:v>
-      </x:c>
-      <x:c r="J53" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
@@ -3193,34 +3064,31 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D54" s="0">
-        <x:v>50000000</x:v>
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F54" s="0">
-        <x:v>49736990</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>21.48</x:v>
+        <x:v>18.55</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>16.34</x:v>
-      </x:c>
-      <x:c r="K54" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -3228,95 +3096,98 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>3043115</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>49736990</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>22.8</x:v>
+      </x:c>
+      <x:c r="J55" s="0">
+        <x:v>16.34</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E55" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>92635231</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="I55" s="0">
-        <x:v>92.9</x:v>
-      </x:c>
-      <x:c r="J55" s="0">
-        <x:v>38.88</x:v>
-      </x:c>
-      <x:c r="K55" s="0" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D56" s="0">
-        <x:v>4191000</x:v>
+      <x:c r="C56" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>92635231</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>61.25</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>0</x:v>
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>6950000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>125000000</x:v>
+        <x:v>160000000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>4.71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3327,28 +3198,28 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>1862500</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>75000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G58" s="0">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>38.32</x:v>
+        <x:v>5.66</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3356,37 +3227,34 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>310000</x:v>
+      <x:c r="C59" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F59" s="0">
-        <x:v>49980500</x:v>
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G59" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>9.95</x:v>
+        <x:v>38.9</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>161.23</x:v>
-      </x:c>
-      <x:c r="K59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -3394,104 +3262,104 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>2000000</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D60" s="0">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F60" s="0">
-        <x:v>31366572</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>18.59</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>15.68</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>1250000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>25000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F61" s="0">
-        <x:v>11187500</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G61" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.22</x:v>
+        <x:v>18.78</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>8.95</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>3077160</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>10000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>100000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>33590441</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G62" s="0">
-        <x:v>0.71</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>33.02</x:v>
+        <x:v>3.09</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>10.92</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -3526,7 +3394,7 @@
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -3555,7 +3423,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>114.3</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
@@ -3572,7 +3440,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D65" s="0">
         <x:v>150000000</x:v>
@@ -3581,7 +3449,7 @@
         <x:v>3000000000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>0</x:v>
@@ -3590,7 +3458,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.82</x:v>
+        <x:v>38.3</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3622,13 +3490,13 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -3657,7 +3525,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>58.45</x:v>
+        <x:v>56.55</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3668,7 +3536,7 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>150</x:v>
@@ -3692,18 +3560,18 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.3</x:v>
+        <x:v>19.91</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>150</x:v>
@@ -3727,18 +3595,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>22.2</x:v>
+        <x:v>22.04</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>150</x:v>
@@ -3762,21 +3630,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.88</x:v>
+        <x:v>7.72</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3797,21 +3665,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>50.2</x:v>
+        <x:v>53.8</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3832,24 +3700,24 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>71.2</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D73" s="0">
         <x:v>10000000</x:v>
@@ -3858,7 +3726,7 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>3.73</x:v>
@@ -3867,7 +3735,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>45.72</x:v>
+        <x:v>44.82</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3875,13 +3743,13 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D74" s="0">
         <x:v>50000000</x:v>
@@ -3890,7 +3758,7 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>5</x:v>
@@ -3899,7 +3767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.8</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3907,10 +3775,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3931,21 +3799,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.45</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3966,21 +3834,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.82</x:v>
+        <x:v>13.66</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -4001,21 +3869,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.32</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -4036,21 +3904,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.45</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -4071,21 +3939,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>250.5</x:v>
+        <x:v>244.7</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -4106,21 +3974,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>12.7</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4141,48 +4009,48 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>260.25</x:v>
+        <x:v>238.5</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>48000</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>5000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>1410107</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>1.05</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.01</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>36.4</x:v>
+        <x:v>26.14</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>29.38</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
@@ -4190,34 +4058,34 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>5100000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>9000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>200000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F83" s="0">
-        <x:v>90022686</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>7.6</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>4.31</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>26.1</x:v>
+        <x:v>14.62</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>17.65</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -4225,31 +4093,31 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>195050</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>3000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>155000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>12938342</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>1358</x:v>
+        <x:v>7.11</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>66.33</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
         <x:v>184</x:v>
@@ -4260,754 +4128,751 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C85" s="0">
-        <x:v>3228679</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0">
-        <x:v>51395842</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>15.17</x:v>
+        <x:v>17.81</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>15.92</x:v>
-      </x:c>
-      <x:c r="K85" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>150000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>6000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>240000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>6145450</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>7.1</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>40.97</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>1000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0">
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>18.46</x:v>
+        <x:v>130.1</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>0</x:v>
+        <x:v>31.92</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>366107</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>1200000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>6010300</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>19.76</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>16.42</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>120000</x:v>
+        <x:v>23682251</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>26398084</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>3830160</x:v>
+        <x:v>107041261</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.05</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>144.6</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>31.92</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>13050000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>13050000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>3</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>93</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>94.36</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>12182251</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>100000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>500000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>49483761</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>1.22</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4.97</x:v>
+        <x:v>4.36</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>4.06</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>4000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>429817200</x:v>
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.17</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>760</x:v>
+        <x:v>10.82</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>429.82</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C93" s="0">
-        <x:v>300000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>60000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>171000000</x:v>
-      </x:c>
-      <x:c r="F93" s="0">
-        <x:v>791000</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>4.38</x:v>
+        <x:v>3.67</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="K93" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>2175097</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>15000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>175000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F94" s="0">
-        <x:v>17901652</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>10</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>10.8</x:v>
+        <x:v>29.2</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>8.23</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C95" s="0">
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D95" s="0">
+        <x:v>11000000</x:v>
+      </x:c>
+      <x:c r="E95" s="0">
         <x:v>50000000</x:v>
       </x:c>
-      <x:c r="E95" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F95" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F95" s="0">
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.77</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>0</x:v>
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>43000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>200000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0">
-        <x:v>1024885</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>29.42</x:v>
+        <x:v>33.66</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>23.83</x:v>
-      </x:c>
-      <x:c r="K96" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>9937037</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>11000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>50000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F97" s="0">
-        <x:v>50001023</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.81</x:v>
+        <x:v>27.18</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>5.03</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C98" s="0">
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>5500000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F98" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F98" s="0">
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>33.96</x:v>
+        <x:v>8.96</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>0</x:v>
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C99" s="0">
-        <x:v>13064888</x:v>
-      </x:c>
-      <x:c r="D99" s="0">
-        <x:v>30000000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F99" s="0">
-        <x:v>268254173</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>28.3</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>20.53</x:v>
-      </x:c>
-      <x:c r="K99" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C100" s="0">
-        <x:v>111673026</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>150000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F100" s="0">
-        <x:v>500005947</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9.24</x:v>
+        <x:v>8.25</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>4.48</x:v>
-      </x:c>
-      <x:c r="K100" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C101" s="0">
+        <x:v>1100000</x:v>
+      </x:c>
+      <x:c r="D101" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F101" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F101" s="0">
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>4.57</x:v>
+        <x:v>112.3</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>0</x:v>
+        <x:v>50.97</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>5067479</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>19600000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>92000000</x:v>
-      </x:c>
-      <x:c r="F102" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F102" s="0">
+        <x:v>49864423</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>0</x:v>
+        <x:v>4.54</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>8.74</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>0</x:v>
+        <x:v>9.84</x:v>
+      </x:c>
+      <x:c r="K102" s="0" t="s">
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>1100000</x:v>
+        <x:v>1310000</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>2000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>100000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>56064346</x:v>
+        <x:v>49200625</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>2</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>114.1</x:v>
+        <x:v>39.94</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>50.97</x:v>
+        <x:v>37.56</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>4952647</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>11160000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>125000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>48332157</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>4.44</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>14.75</x:v>
+        <x:v>104.8</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>9.76</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C105" s="0">
-        <x:v>1210000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>2160000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="F105" s="0">
-        <x:v>45218625</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>39.98</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>37.37</x:v>
-      </x:c>
-      <x:c r="K105" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1989802</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>5000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>250000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F106" s="0">
-        <x:v>78711752</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2.94</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>105.3</x:v>
+        <x:v>14.18</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>39.56</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -5015,31 +4880,34 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C107" s="0">
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F107" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F107" s="0">
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>484.5</x:v>
+        <x:v>15.96</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>0</x:v>
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -5047,308 +4915,305 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>1000000</x:v>
+        <x:v>76908759</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>1000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>30000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>24034068</x:v>
+        <x:v>1979731803</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>1.34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>1.22</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.7</x:v>
+        <x:v>32.24</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>24.03</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>300000</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>67500000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>326000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>1369300</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>14.2</x:v>
+        <x:v>26.14</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>4.56</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>8291656</x:v>
+        <x:v>10994323</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>11000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>200000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>126004459</x:v>
+        <x:v>183002238</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1.9</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>17</x:v>
+        <x:v>14.95</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>15.2</x:v>
+        <x:v>16.65</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>76908759</x:v>
+        <x:v>25876543</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>250000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>245148287</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>0.78</x:v>
+        <x:v>1.33</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>33.48</x:v>
+        <x:v>15.15</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>25.74</x:v>
+        <x:v>9.47</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>2975773</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>6000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>150000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>44771095</x:v>
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>0</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>27.16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>15.05</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>10994323</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>21600000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F113" s="0">
-        <x:v>183002238</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>10</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>15.55</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>16.65</x:v>
-      </x:c>
-      <x:c r="K113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>25876543</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>195000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>245148287</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>15.27</x:v>
+        <x:v>8.82</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>9.47</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>5100000</x:v>
+        <x:v>590777</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>20000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>700000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F115" s="0">
-        <x:v>155318227</x:v>
+        <x:v>12439782</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>6.81</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0.93</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>58.5</x:v>
+        <x:v>17.79</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>30.45</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>300000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>700000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>6.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>2.53</x:v>
+        <x:v>86.3</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5356,311 +5221,314 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="C117" s="0">
-        <x:v>5000000</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F117" s="0">
-        <x:v>39090077</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>8.8</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="K117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>590777</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>21000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>500000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F118" s="0">
-        <x:v>12439782</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>17.85</x:v>
+        <x:v>231.6</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>21.06</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C119" s="0">
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>11700000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F119" s="0">
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0</x:v>
+        <x:v>1.88</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>89.9</x:v>
+        <x:v>14.55</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>0</x:v>
+        <x:v>14.81</x:v>
+      </x:c>
+      <x:c r="K119" s="0" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C120" s="0">
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F120" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>120000000</x:v>
+      </x:c>
+      <x:c r="F120" s="0">
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0</x:v>
+        <x:v>1.82</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>484.5</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>0</x:v>
+        <x:v>13.82</x:v>
+      </x:c>
+      <x:c r="K120" s="0" t="s">
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>53584</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>640000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>8271098</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G121" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>232.2</x:v>
+        <x:v>5.73</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>154.36</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>7550000</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>500000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>111777791</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>78.65</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>14.81</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>772649</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>230000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>25559231</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>4.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>7.77</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>33.08</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>246</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>2097716</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>10112561</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>120000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>28985167</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>10</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1.82</x:v>
+        <x:v>0.56</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.55</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>13.82</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>248</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>5185302</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>57000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>513000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>37061183</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>5.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0.26</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>5.9</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>7.15</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -5671,1635 +5539,693 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>669111</x:v>
+        <x:v>281228</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>1000000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>260000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F126" s="0">
-        <x:v>151220429</x:v>
+        <x:v>38021885</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>524</x:v>
+        <x:v>138.2</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>226</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="C127" s="0">
-        <x:v>38840</x:v>
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0">
-        <x:v>9431791</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>484.5</x:v>
+        <x:v>142.8</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>242.84</x:v>
-      </x:c>
-      <x:c r="K127" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>252</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>2146559</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>33400000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>569698174</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.64</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>533</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>265.4</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>2250000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>300000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F129" s="0">
-        <x:v>31750000</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0.56</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>78.65</x:v>
+        <x:v>56.55</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>14.11</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>109200</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>2000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>150000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F130" s="0">
-        <x:v>4494592</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>1.19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0.07</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>68.35</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>41.16</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>1127000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>2100000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>50000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>24638870</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G131" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>67.65</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>21.86</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>3435564</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>11200000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>336000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F132" s="0">
-        <x:v>111000901</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>3.07</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>402.25</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>32.31</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>109200</x:v>
+        <x:v>8578668</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>2000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>150000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>4494592</x:v>
+        <x:v>184312813</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>1.19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0.07</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>68.35</x:v>
+        <x:v>21.76</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>41.16</x:v>
+        <x:v>21.49</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>2550000</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>28000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>196000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>17871250</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>1.06</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>0.1</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>10.4</x:v>
+        <x:v>9.11</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>7.01</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>1500000</x:v>
-      </x:c>
-      <x:c r="D135" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>175000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>21870885</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>1.3</x:v>
+        <x:v>1.84</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.36</x:v>
+        <x:v>82.05</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>14.58</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>281228</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>8299326</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>600000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>38021885</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>140</x:v>
+        <x:v>2.89</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>135.2</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>12514496</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>18200000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>850000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F137" s="0">
-        <x:v>546809347</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>3.64</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>39.58</x:v>
+        <x:v>40.76</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>43.69</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C138" s="0">
+        <x:v>1060056</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>2500000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0">
+        <x:v>60762934</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>140.6</x:v>
+        <x:v>236.5</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>0</x:v>
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>2550028</x:v>
-      </x:c>
-      <x:c r="D139" s="0">
-        <x:v>5917500</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>45000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>44858986</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>2.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>26.1</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>17.59</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>2000000</x:v>
+        <x:v>373000</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>976212638</x:v>
+        <x:v>23786370</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>760</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>488.11</x:v>
+        <x:v>63.77</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>845945</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>250000000</x:v>
+        <x:v>140000000</x:v>
       </x:c>
       <x:c r="F141" s="0">
-        <x:v>10058606</x:v>
+        <x:v>133271568</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>2.64</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>11.89</x:v>
+        <x:v>13.33</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>280000</x:v>
+        <x:v>3081843</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>3469200</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>175000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>11890334</x:v>
+        <x:v>43986444</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>50.8</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>42.47</x:v>
+        <x:v>14.27</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>47311439</x:v>
+        <x:v>1348769</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>400000000</x:v>
+        <x:v>105000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>248829790</x:v>
+        <x:v>224239713</x:v>
       </x:c>
       <x:c r="G143" s="0">
-        <x:v>3.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>1.05</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.53</x:v>
+        <x:v>360.25</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>5.26</x:v>
+        <x:v>166.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>20000000</x:v>
+        <x:v>927506</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1488672430</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>300000000</x:v>
+        <x:v>411000000</x:v>
       </x:c>
       <x:c r="F144" s="0">
-        <x:v>219953800</x:v>
+        <x:v>19370508</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>4.98</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>78.65</x:v>
+        <x:v>18.98</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>11</x:v>
+        <x:v>20.88</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>21446</x:v>
+        <x:v>27739521</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>1000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>200000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F145" s="0">
-        <x:v>2015907</x:v>
+        <x:v>76729767</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>58.75</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>94</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:11">
-      <x:c r="A146" s="0" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="C146" s="0">
-        <x:v>19000</x:v>
-      </x:c>
-      <x:c r="D146" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E146" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0">
-        <x:v>1355100</x:v>
-      </x:c>
-      <x:c r="G146" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H146" s="0">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="I146" s="0">
-        <x:v>17.48</x:v>
-      </x:c>
-      <x:c r="J146" s="0">
-        <x:v>71.32</x:v>
-      </x:c>
-      <x:c r="K146" s="0" t="s">
-        <x:v>281</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:11">
-      <x:c r="A147" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="C147" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="D147" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E147" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F147" s="0">
-        <x:v>352389967</x:v>
-      </x:c>
-      <x:c r="G147" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H147" s="0">
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="I147" s="0">
-        <x:v>7.96</x:v>
-      </x:c>
-      <x:c r="J147" s="0">
-        <x:v>35.24</x:v>
-      </x:c>
-      <x:c r="K147" s="0" t="s">
-        <x:v>283</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:11">
-      <x:c r="A148" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="C148" s="0">
-        <x:v>850000</x:v>
-      </x:c>
-      <x:c r="D148" s="0">
-        <x:v>4250000</x:v>
-      </x:c>
-      <x:c r="E148" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F148" s="0">
-        <x:v>6548328</x:v>
-      </x:c>
-      <x:c r="G148" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H148" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I148" s="0">
-        <x:v>8.54</x:v>
-      </x:c>
-      <x:c r="J148" s="0">
-        <x:v>7.7</x:v>
-      </x:c>
-      <x:c r="K148" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:11">
-      <x:c r="A149" s="0" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="C149" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="D149" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="E149" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F149" s="0">
-        <x:v>23990000</x:v>
-      </x:c>
-      <x:c r="G149" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H149" s="0">
-        <x:v>0.22</x:v>
-      </x:c>
-      <x:c r="I149" s="0">
-        <x:v>3.05</x:v>
-      </x:c>
-      <x:c r="J149" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="K149" s="0" t="s">
-        <x:v>288</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:11">
-      <x:c r="A150" s="0" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="C150" s="0">
-        <x:v>6397124</x:v>
-      </x:c>
-      <x:c r="D150" s="0">
-        <x:v>35300000</x:v>
-      </x:c>
-      <x:c r="E150" s="0">
-        <x:v>1046645000</x:v>
-      </x:c>
-      <x:c r="F150" s="0">
-        <x:v>122892213</x:v>
-      </x:c>
-      <x:c r="G150" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H150" s="0">
-        <x:v>0.21</x:v>
-      </x:c>
-      <x:c r="I150" s="0">
-        <x:v>4.94</x:v>
-      </x:c>
-      <x:c r="J150" s="0">
-        <x:v>19.21</x:v>
-      </x:c>
-      <x:c r="K150" s="0" t="s">
-        <x:v>291</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:11">
-      <x:c r="A151" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="C151" s="0">
-        <x:v>8578668</x:v>
-      </x:c>
-      <x:c r="D151" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E151" s="0">
-        <x:v>525000000</x:v>
-      </x:c>
-      <x:c r="F151" s="0">
-        <x:v>184312813</x:v>
-      </x:c>
-      <x:c r="G151" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H151" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="I151" s="0">
-        <x:v>22.52</x:v>
-      </x:c>
-      <x:c r="J151" s="0">
-        <x:v>21.49</x:v>
-      </x:c>
-      <x:c r="K151" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:11">
-      <x:c r="A152" s="0" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="C152" s="0">
-        <x:v>9350000</x:v>
-      </x:c>
-      <x:c r="D152" s="0">
-        <x:v>14710247</x:v>
-      </x:c>
-      <x:c r="E152" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F152" s="0">
-        <x:v>69547091</x:v>
-      </x:c>
-      <x:c r="G152" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H152" s="0">
-        <x:v>3.18</x:v>
-      </x:c>
-      <x:c r="I152" s="0">
-        <x:v>9.02</x:v>
-      </x:c>
-      <x:c r="J152" s="0">
-        <x:v>7.44</x:v>
-      </x:c>
-      <x:c r="K152" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:11">
-      <x:c r="A153" s="0" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D153" s="0">
-        <x:v>6046875</x:v>
-      </x:c>
-      <x:c r="E153" s="0">
-        <x:v>98412890</x:v>
-      </x:c>
-      <x:c r="F153" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G153" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H153" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I153" s="0">
-        <x:v>6.89</x:v>
-      </x:c>
-      <x:c r="J153" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:11">
-      <x:c r="A154" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="C154" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E154" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F154" s="0">
-        <x:v>75911475</x:v>
-      </x:c>
-      <x:c r="G154" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H154" s="0">
-        <x:v>1.84</x:v>
-      </x:c>
-      <x:c r="I154" s="0">
-        <x:v>84.7</x:v>
-      </x:c>
-      <x:c r="J154" s="0">
-        <x:v>51.7</x:v>
-      </x:c>
-      <x:c r="K154" s="0" t="s">
-        <x:v>299</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:11">
-      <x:c r="A155" s="0" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="C155" s="0">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="D155" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E155" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F155" s="0">
-        <x:v>13401783</x:v>
-      </x:c>
-      <x:c r="G155" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H155" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="I155" s="0">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="J155" s="0">
-        <x:v>26.8</x:v>
-      </x:c>
-      <x:c r="K155" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" spans="1:11">
-      <x:c r="A156" s="0" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="C156" s="0">
-        <x:v>18900000</x:v>
-      </x:c>
-      <x:c r="D156" s="0">
-        <x:v>20000000</x:v>
-      </x:c>
-      <x:c r="E156" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F156" s="0">
-        <x:v>598621241</x:v>
-      </x:c>
-      <x:c r="G156" s="0">
-        <x:v>6.81</x:v>
-      </x:c>
-      <x:c r="H156" s="0">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="I156" s="0">
-        <x:v>58.5</x:v>
-      </x:c>
-      <x:c r="J156" s="0">
-        <x:v>31.67</x:v>
-      </x:c>
-      <x:c r="K156" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:11">
-      <x:c r="A157" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="C157" s="0">
-        <x:v>725000</x:v>
-      </x:c>
-      <x:c r="D157" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E157" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F157" s="0">
-        <x:v>48539975</x:v>
-      </x:c>
-      <x:c r="G157" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H157" s="0">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="I157" s="0">
-        <x:v>39.68</x:v>
-      </x:c>
-      <x:c r="J157" s="0">
-        <x:v>66.95</x:v>
-      </x:c>
-      <x:c r="K157" s="0" t="s">
-        <x:v>305</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:11">
-      <x:c r="A158" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="C158" s="0">
-        <x:v>4350000</x:v>
-      </x:c>
-      <x:c r="D158" s="0">
-        <x:v>4350000</x:v>
-      </x:c>
-      <x:c r="E158" s="0">
-        <x:v>550000000</x:v>
-      </x:c>
-      <x:c r="F158" s="0">
-        <x:v>419078527</x:v>
-      </x:c>
-      <x:c r="G158" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H158" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I158" s="0">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J158" s="0">
-        <x:v>96.34</x:v>
-      </x:c>
-      <x:c r="K158" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:11">
-      <x:c r="A159" s="0" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="C159" s="0">
-        <x:v>361000</x:v>
-      </x:c>
-      <x:c r="D159" s="0">
-        <x:v>3469200</x:v>
-      </x:c>
-      <x:c r="E159" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F159" s="0">
-        <x:v>15105974</x:v>
-      </x:c>
-      <x:c r="G159" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H159" s="0">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="I159" s="0">
-        <x:v>50.8</x:v>
-      </x:c>
-      <x:c r="J159" s="0">
-        <x:v>41.84</x:v>
-      </x:c>
-      <x:c r="K159" s="0" t="s">
-        <x:v>308</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:11">
-      <x:c r="A160" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="C160" s="0">
-        <x:v>226000</x:v>
-      </x:c>
-      <x:c r="D160" s="0">
-        <x:v>5500000</x:v>
-      </x:c>
-      <x:c r="E160" s="0">
-        <x:v>750000000</x:v>
-      </x:c>
-      <x:c r="F160" s="0">
-        <x:v>30917712</x:v>
-      </x:c>
-      <x:c r="G160" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H160" s="0">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="I160" s="0">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="J160" s="0">
-        <x:v>136.8</x:v>
-      </x:c>
-      <x:c r="K160" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:11">
-      <x:c r="A161" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="C161" s="0">
-        <x:v>1060056</x:v>
-      </x:c>
-      <x:c r="D161" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="E161" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0">
-        <x:v>60762934</x:v>
-      </x:c>
-      <x:c r="G161" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H161" s="0">
-        <x:v>0.44</x:v>
-      </x:c>
-      <x:c r="I161" s="0">
-        <x:v>235.2</x:v>
-      </x:c>
-      <x:c r="J161" s="0">
-        <x:v>57.32</x:v>
-      </x:c>
-      <x:c r="K161" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:11">
-      <x:c r="A162" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="C162" s="0">
-        <x:v>1725000</x:v>
-      </x:c>
-      <x:c r="D162" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="E162" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F162" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="G162" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H162" s="0">
-        <x:v>0.22</x:v>
-      </x:c>
-      <x:c r="I162" s="0">
-        <x:v>1.49</x:v>
-      </x:c>
-      <x:c r="J162" s="0">
-        <x:v>1.16</x:v>
-      </x:c>
-      <x:c r="K162" s="0" t="s">
-        <x:v>314</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:11">
-      <x:c r="A163" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="C163" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D163" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E163" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F163" s="0">
-        <x:v>565141750</x:v>
-      </x:c>
-      <x:c r="G163" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H163" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="I163" s="0">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="J163" s="0">
-        <x:v>4.26</x:v>
-      </x:c>
-      <x:c r="K163" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:11">
-      <x:c r="A164" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="C164" s="0">
-        <x:v>7921744</x:v>
-      </x:c>
-      <x:c r="D164" s="0">
-        <x:v>21600000</x:v>
-      </x:c>
-      <x:c r="E164" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F164" s="0">
-        <x:v>154033416</x:v>
-      </x:c>
-      <x:c r="G164" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H164" s="0">
-        <x:v>3.67</x:v>
-      </x:c>
-      <x:c r="I164" s="0">
-        <x:v>15.55</x:v>
-      </x:c>
-      <x:c r="J164" s="0">
-        <x:v>19.44</x:v>
-      </x:c>
-      <x:c r="K164" s="0" t="s">
-        <x:v>223</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:11">
-      <x:c r="A165" s="0" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="C165" s="0">
-        <x:v>373000</x:v>
-      </x:c>
-      <x:c r="D165" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E165" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="F165" s="0">
-        <x:v>23786370</x:v>
-      </x:c>
-      <x:c r="G165" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H165" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I165" s="0">
-        <x:v>7.51</x:v>
-      </x:c>
-      <x:c r="J165" s="0">
-        <x:v>63.77</x:v>
-      </x:c>
-      <x:c r="K165" s="0" t="s">
-        <x:v>319</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:11">
-      <x:c r="A166" s="0" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="C166" s="0">
-        <x:v>13430000</x:v>
-      </x:c>
-      <x:c r="D166" s="0">
-        <x:v>18500000</x:v>
-      </x:c>
-      <x:c r="E166" s="0">
-        <x:v>925000000</x:v>
-      </x:c>
-      <x:c r="F166" s="0">
-        <x:v>924841041</x:v>
-      </x:c>
-      <x:c r="G166" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H166" s="0">
-        <x:v>3.63</x:v>
-      </x:c>
-      <x:c r="I166" s="0">
-        <x:v>135.1</x:v>
-      </x:c>
-      <x:c r="J166" s="0">
-        <x:v>68.86</x:v>
-      </x:c>
-      <x:c r="K166" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:11">
-      <x:c r="A167" s="0" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="C167" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="D167" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E167" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F167" s="0">
-        <x:v>176217117</x:v>
-      </x:c>
-      <x:c r="G167" s="0">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="H167" s="0">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="I167" s="0">
-        <x:v>5.9</x:v>
-      </x:c>
-      <x:c r="J167" s="0">
-        <x:v>11.75</x:v>
-      </x:c>
-      <x:c r="K167" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:11">
-      <x:c r="A168" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="C168" s="0">
-        <x:v>10759347</x:v>
-      </x:c>
-      <x:c r="D168" s="0">
-        <x:v>21739600</x:v>
-      </x:c>
-      <x:c r="E168" s="0">
-        <x:v>350000000</x:v>
-      </x:c>
-      <x:c r="F168" s="0">
-        <x:v>138943650</x:v>
-      </x:c>
-      <x:c r="G168" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H168" s="0">
-        <x:v>0.99</x:v>
-      </x:c>
-      <x:c r="I168" s="0">
-        <x:v>11.71</x:v>
-      </x:c>
-      <x:c r="J168" s="0">
-        <x:v>12.91</x:v>
-      </x:c>
-      <x:c r="K168" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:11">
-      <x:c r="A169" s="0" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="C169" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="D169" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E169" s="0">
-        <x:v>140000000</x:v>
-      </x:c>
-      <x:c r="F169" s="0">
-        <x:v>133271568</x:v>
-      </x:c>
-      <x:c r="G169" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H169" s="0">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="I169" s="0">
-        <x:v>4.86</x:v>
-      </x:c>
-      <x:c r="J169" s="0">
-        <x:v>13.33</x:v>
-      </x:c>
-      <x:c r="K169" s="0" t="s">
-        <x:v>326</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:11">
-      <x:c r="A170" s="0" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="C170" s="0">
-        <x:v>3081843</x:v>
-      </x:c>
-      <x:c r="D170" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E170" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F170" s="0">
-        <x:v>43986444</x:v>
-      </x:c>
-      <x:c r="G170" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H170" s="0">
-        <x:v>0.66</x:v>
-      </x:c>
-      <x:c r="I170" s="0">
-        <x:v>8.61</x:v>
-      </x:c>
-      <x:c r="J170" s="0">
-        <x:v>14.27</x:v>
-      </x:c>
-      <x:c r="K170" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:11">
-      <x:c r="A171" s="0" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="C171" s="0">
-        <x:v>1348769</x:v>
-      </x:c>
-      <x:c r="D171" s="0">
-        <x:v>1500000</x:v>
-      </x:c>
-      <x:c r="E171" s="0">
-        <x:v>105000000</x:v>
-      </x:c>
-      <x:c r="F171" s="0">
-        <x:v>224239713</x:v>
-      </x:c>
-      <x:c r="G171" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H171" s="0">
-        <x:v>0.41</x:v>
-      </x:c>
-      <x:c r="I171" s="0">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="J171" s="0">
-        <x:v>166.26</x:v>
-      </x:c>
-      <x:c r="K171" s="0" t="s">
-        <x:v>331</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:11">
-      <x:c r="A172" s="0" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="C172" s="0">
-        <x:v>927506</x:v>
-      </x:c>
-      <x:c r="D172" s="0">
-        <x:v>1488672430</x:v>
-      </x:c>
-      <x:c r="E172" s="0">
-        <x:v>411000000</x:v>
-      </x:c>
-      <x:c r="F172" s="0">
-        <x:v>19370508</x:v>
-      </x:c>
-      <x:c r="G172" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H172" s="0">
-        <x:v>0.62</x:v>
-      </x:c>
-      <x:c r="I172" s="0">
-        <x:v>19.6</x:v>
-      </x:c>
-      <x:c r="J172" s="0">
-        <x:v>20.88</x:v>
-      </x:c>
-      <x:c r="K172" s="0" t="s">
-        <x:v>334</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -118,6 +118,9 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKFA</x:t>
   </x:si>
   <x:si>
@@ -199,616 +202,610 @@
     <x:t>06.10.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.12.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.11.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.11.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.10.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.10.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.09.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.07.2024</x:t>
+  </x:si>
+  <x:si>
     <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.11.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.11.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.07.2024</x:t>
   </x:si>
   <x:si>
     <x:t>FRIGO</x:t>
@@ -1307,7 +1304,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>19.91</x:v>
+        <x:v>19.86</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>21.09</x:v>
@@ -1342,7 +1339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.41</x:v>
+        <x:v>8.38</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1374,7 +1371,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>7.2</x:v>
+        <x:v>6.48</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1403,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>130.1</x:v>
+        <x:v>132.5</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1438,7 +1435,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>10.78</x:v>
+        <x:v>11.03</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>7.13</x:v>
@@ -1473,7 +1470,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>28.86</x:v>
+        <x:v>31.74</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>28.75</x:v>
@@ -1508,7 +1505,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>17.09</x:v>
+        <x:v>16.94</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>15.08</x:v>
@@ -1575,7 +1572,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>23.04</x:v>
+        <x:v>22.7</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>23.54</x:v>
@@ -1592,7 +1589,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>17060506</x:v>
+        <x:v>17641798</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>80000000</x:v>
@@ -1601,30 +1598,30 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>424934524</x:v>
+        <x:v>440645684</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.66</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>27.18</x:v>
+        <x:v>27.36</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>24.91</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>7024156</x:v>
@@ -1645,7 +1642,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>13.32</x:v>
+        <x:v>13.37</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>13.34</x:v>
@@ -1656,10 +1653,10 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>3500000</x:v>
@@ -1680,7 +1677,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>38.6</x:v>
+        <x:v>39.36</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>39.18</x:v>
@@ -1691,10 +1688,10 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>3753472</x:v>
@@ -1715,21 +1712,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>58.35</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.93</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>3189049</x:v>
@@ -1750,21 +1747,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>7.6</x:v>
+        <x:v>7.49</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>48.39</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>15</x:v>
@@ -1785,7 +1782,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.1</x:v>
+        <x:v>6.19</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>0</x:v>
@@ -1793,10 +1790,10 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>875000</x:v>
@@ -1817,21 +1814,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>126.9</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>59.97</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>6248196</x:v>
@@ -1852,21 +1849,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>6.66</x:v>
+        <x:v>6.59</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>236122</x:v>
@@ -1887,21 +1884,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>79.25</x:v>
+        <x:v>79.5</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>1000000</x:v>
@@ -1922,21 +1919,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.76</x:v>
+        <x:v>21.46</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>15</x:v>
@@ -1957,7 +1954,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>7.6</x:v>
+        <x:v>7.49</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>0</x:v>
@@ -1965,13 +1962,13 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>84837201</x:v>
+        <x:v>87187201</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>200000000</x:v>
@@ -1980,22 +1977,22 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>834313382</x:v>
+        <x:v>855385832</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.96</x:v>
+        <x:v>8.83</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>9.83</x:v>
+        <x:v>9.81</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -2024,7 +2021,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>51.75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>23.95</x:v>
@@ -2059,13 +2056,13 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>730</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>528.86</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -2094,7 +2091,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>27.18</x:v>
+        <x:v>27.36</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>24.19</x:v>
@@ -2105,7 +2102,7 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>67</x:v>
@@ -2129,7 +2126,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>8.96</x:v>
+        <x:v>8.83</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>10.74</x:v>
@@ -2164,7 +2161,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>7.18</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>24.08</x:v>
@@ -2199,7 +2196,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>24.66</x:v>
+        <x:v>23.94</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>27.31</x:v>
@@ -2234,7 +2231,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>4.46</x:v>
@@ -2269,7 +2266,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.87</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>13.09</x:v>
@@ -2304,7 +2301,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>34.4</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>0</x:v>
@@ -2336,7 +2333,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>6.3</x:v>
+        <x:v>6.93</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>52.14</x:v>
@@ -2353,7 +2350,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>13000000</x:v>
+        <x:v>13200000</x:v>
       </x:c>
       <x:c r="D33" s="0">
         <x:v>79451200</x:v>
@@ -2362,30 +2359,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>510900616</x:v>
+        <x:v>519420697</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1.64</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>42.54</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>39.3</x:v>
+        <x:v>39.35</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>1973951</x:v>
@@ -2406,21 +2403,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>82.05</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>15</x:v>
@@ -2441,7 +2438,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.62</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2449,10 +2446,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>3337681</x:v>
@@ -2473,21 +2470,21 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>6.14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>15</x:v>
@@ -2508,7 +2505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>40.76</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2516,10 +2513,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>1364000</x:v>
@@ -2540,21 +2537,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>315.75</x:v>
+        <x:v>314.5</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>15</x:v>
@@ -2575,7 +2572,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>20.7</x:v>
+        <x:v>20.18</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2583,10 +2580,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>507440</x:v>
@@ -2607,21 +2604,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>142.8</x:v>
+        <x:v>144.1</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>15</x:v>
@@ -2642,7 +2639,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>35.72</x:v>
+        <x:v>37.68</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>0</x:v>
@@ -2650,10 +2647,10 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>2000000</x:v>
@@ -2674,21 +2671,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>41.5</x:v>
+        <x:v>41.2</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>324474</x:v>
@@ -2709,22 +2706,22 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>12.88</x:v>
+        <x:v>13.58</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2744,7 +2741,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>13.01</x:v>
+        <x:v>12.73</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>0</x:v>
@@ -2752,10 +2749,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>15</x:v>
@@ -2784,10 +2781,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>2000000</x:v>
@@ -2808,7 +2805,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>6.6</x:v>
+        <x:v>6.59</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>6.12</x:v>
@@ -2819,10 +2816,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>174500000</x:v>
@@ -2843,13 +2840,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2857,7 +2854,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>635229</x:v>
@@ -2878,21 +2875,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>24.66</x:v>
+        <x:v>23.94</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>130000</x:v>
@@ -2913,21 +2910,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.14</x:v>
+        <x:v>24.46</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>15</x:v>
@@ -2948,7 +2945,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>236.5</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>0</x:v>
@@ -2956,10 +2953,10 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>447761</x:v>
@@ -2980,21 +2977,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>39.6</x:v>
+        <x:v>39.64</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>200000</x:v>
@@ -3015,21 +3012,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>18.02</x:v>
+        <x:v>16.22</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>946718</x:v>
@@ -3050,21 +3047,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>81.4</x:v>
+        <x:v>81.8</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>15</x:v>
@@ -3085,7 +3082,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>18.55</x:v>
+        <x:v>19.12</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>0</x:v>
@@ -3093,10 +3090,10 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>3043115</x:v>
@@ -3117,21 +3114,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>22.8</x:v>
+        <x:v>22.56</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>2382736</x:v>
@@ -3152,21 +3149,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>84.2</x:v>
+        <x:v>84.6</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>15</x:v>
@@ -3187,7 +3184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>61</x:v>
+        <x:v>62.6</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3195,10 +3192,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>15</x:v>
@@ -3219,7 +3216,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>5.66</x:v>
+        <x:v>5.69</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3227,10 +3224,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>15</x:v>
@@ -3251,7 +3248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>38.9</x:v>
+        <x:v>38.46</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3259,10 +3256,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>310000</x:v>
@@ -3283,21 +3280,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>9.67</x:v>
+        <x:v>9.51</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>2000000</x:v>
@@ -3318,7 +3315,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>18.78</x:v>
+        <x:v>18.4</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>15.68</x:v>
@@ -3329,10 +3326,10 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>1250000</x:v>
@@ -3353,21 +3350,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>3.09</x:v>
+        <x:v>3.07</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3388,21 +3385,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.16</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3423,21 +3420,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>113.8</x:v>
+        <x:v>112.1</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>15</x:v>
@@ -3458,7 +3455,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>38.3</x:v>
+        <x:v>37.5</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3466,10 +3463,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3490,21 +3487,21 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.84</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3525,13 +3522,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>56.55</x:v>
+        <x:v>56.65</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -3539,7 +3536,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3560,7 +3557,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.91</x:v>
+        <x:v>19.86</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3571,10 +3568,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3595,21 +3592,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>22.04</x:v>
+        <x:v>21.92</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3630,21 +3627,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.72</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3665,21 +3662,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>53.8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3700,21 +3697,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>70</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>15</x:v>
@@ -3735,7 +3732,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>44.82</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3743,10 +3740,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>15</x:v>
@@ -3767,7 +3764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.75</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3775,10 +3772,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3799,21 +3796,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.25</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3834,21 +3831,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.66</x:v>
+        <x:v>13.59</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -3869,21 +3866,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.25</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -3904,21 +3901,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.45</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -3939,21 +3936,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>244.7</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -3974,21 +3971,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>12.49</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4009,21 +4006,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>238.5</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>5100000</x:v>
@@ -4044,21 +4041,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>26.14</x:v>
+        <x:v>28.74</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>3228679</x:v>
@@ -4079,21 +4076,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>14.62</x:v>
+        <x:v>14.47</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>150000</x:v>
@@ -4114,21 +4111,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>7.11</x:v>
+        <x:v>7.03</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>15</x:v>
@@ -4149,7 +4146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>17.81</x:v>
+        <x:v>18.13</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>0</x:v>
@@ -4157,10 +4154,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>366107</x:v>
@@ -4181,13 +4178,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.5</x:v>
+        <x:v>18.33</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -4195,7 +4192,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>120000</x:v>
@@ -4216,21 +4213,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>130.1</x:v>
+        <x:v>132.5</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>13050000</x:v>
@@ -4248,24 +4245,24 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>3</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>96.1</x:v>
+        <x:v>97.15</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>23682251</x:v>
@@ -4286,7 +4283,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>5.03</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>4.52</x:v>
@@ -4300,7 +4297,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>1000000</x:v>
@@ -4321,21 +4318,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>730</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>300000</x:v>
@@ -4356,21 +4353,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4.36</x:v>
+        <x:v>4.27</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>2175097</x:v>
@@ -4391,21 +4388,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>10.82</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>15</x:v>
@@ -4426,7 +4423,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>3.67</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>0</x:v>
@@ -4434,10 +4431,10 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>43000</x:v>
@@ -4458,21 +4455,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>29.2</x:v>
+        <x:v>29.32</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>9937037</x:v>
@@ -4493,21 +4490,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.77</x:v>
+        <x:v>3.76</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>15</x:v>
@@ -4528,7 +4525,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>33.66</x:v>
+        <x:v>34.52</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>0</x:v>
@@ -4539,7 +4536,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>13064888</x:v>
@@ -4560,21 +4557,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>27.18</x:v>
+        <x:v>27.36</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>111673026</x:v>
@@ -4595,21 +4592,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>8.96</x:v>
+        <x:v>8.83</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>15</x:v>
@@ -4630,7 +4627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>4.46</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>0</x:v>
@@ -4638,10 +4635,10 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>15</x:v>
@@ -4662,7 +4659,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>8.25</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4670,10 +4667,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>1100000</x:v>
@@ -4694,21 +4691,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>112.3</x:v>
+        <x:v>123.5</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>5067479</x:v>
@@ -4729,24 +4726,24 @@
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>13.01</x:v>
+        <x:v>12.73</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>9.84</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>1310000</x:v>
+        <x:v>1460000</x:v>
       </x:c>
       <x:c r="D103" s="0">
         <x:v>2160000</x:v>
@@ -4755,30 +4752,30 @@
         <x:v>35000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>49200625</x:v>
+        <x:v>55050600</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0.75</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>39.94</x:v>
+        <x:v>38.98</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>37.56</x:v>
+        <x:v>37.71</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1989802</x:v>
@@ -4799,21 +4796,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>104.8</x:v>
+        <x:v>105.2</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>15</x:v>
@@ -4834,7 +4831,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>0</x:v>
@@ -4842,10 +4839,10 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>300000</x:v>
@@ -4866,21 +4863,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>14.18</x:v>
+        <x:v>13.86</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>8291656</x:v>
@@ -4901,21 +4898,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>15.96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>76908759</x:v>
@@ -4936,21 +4933,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>32.24</x:v>
+        <x:v>31.34</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>2975773</x:v>
@@ -4971,21 +4968,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>26.14</x:v>
+        <x:v>26.12</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>15.05</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>10994323</x:v>
@@ -5006,24 +5003,24 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>14.95</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>220</x:v>
-      </x:c>
       <x:c r="C111" s="0">
-        <x:v>25876543</x:v>
+        <x:v>26126543</x:v>
       </x:c>
       <x:c r="D111" s="0">
         <x:v>195000000</x:v>
@@ -5032,30 +5029,30 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>245148287</x:v>
+        <x:v>248960787</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1.33</x:v>
+        <x:v>1.34</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.15</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>9.47</x:v>
+        <x:v>9.53</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>5100000</x:v>
@@ -5082,15 +5079,15 @@
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>15</x:v>
@@ -5111,7 +5108,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5119,10 +5116,10 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>5000000</x:v>
@@ -5143,21 +5140,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.87</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>590777</x:v>
@@ -5178,21 +5175,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>17.79</x:v>
+        <x:v>17.56</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>15</x:v>
@@ -5213,7 +5210,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>86.3</x:v>
+        <x:v>83.8</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5221,10 +5218,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>15</x:v>
@@ -5245,7 +5242,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5253,10 +5250,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>53584</x:v>
@@ -5277,7 +5274,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>231.6</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>154.36</x:v>
@@ -5288,10 +5285,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>7550000</x:v>
@@ -5309,24 +5306,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1.88</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>14.55</x:v>
+        <x:v>14.83</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>2097716</x:v>
@@ -5347,21 +5344,21 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>15.8</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>5185302</x:v>
@@ -5382,21 +5379,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>5.73</x:v>
+        <x:v>5.77</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>669111</x:v>
@@ -5417,21 +5414,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>538</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>38840</x:v>
@@ -5452,21 +5449,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2250000</x:v>
@@ -5484,24 +5481,24 @@
         <x:v>4.98</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.56</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.55</x:v>
+        <x:v>14.83</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>1500000</x:v>
@@ -5522,21 +5519,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>15.8</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>281228</x:v>
@@ -5557,7 +5554,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>138.2</x:v>
+        <x:v>141.2</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>135.2</x:v>
@@ -5568,10 +5565,10 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>15</x:v>
@@ -5592,7 +5589,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>142.8</x:v>
+        <x:v>144.1</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>0</x:v>
@@ -5600,10 +5597,10 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>845945</x:v>
@@ -5624,21 +5621,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>21446</x:v>
@@ -5659,21 +5656,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>56.55</x:v>
+        <x:v>57.5</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>850000</x:v>
@@ -5694,21 +5691,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>8.3</x:v>
+        <x:v>8.52</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>15000000</x:v>
@@ -5729,21 +5726,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3.25</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>6397124</x:v>
@@ -5764,21 +5761,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>4.73</x:v>
+        <x:v>4.69</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>8578668</x:v>
@@ -5799,21 +5796,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>21.76</x:v>
+        <x:v>21.46</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>9350000</x:v>
@@ -5834,21 +5831,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>9.11</x:v>
+        <x:v>9.2</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1468255</x:v>
@@ -5869,21 +5866,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>82.05</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>500000</x:v>
@@ -5904,21 +5901,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>2.89</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>725000</x:v>
@@ -5939,21 +5936,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>40.76</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>1060056</x:v>
@@ -5974,21 +5971,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>236.5</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>132750000</x:v>
@@ -6009,21 +6006,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>278</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>373000</x:v>
@@ -6044,21 +6041,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>10000000</x:v>
@@ -6079,21 +6076,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>5.44</x:v>
+        <x:v>5.67</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>3081843</x:v>
@@ -6114,21 +6111,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.55</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>1348769</x:v>
@@ -6149,21 +6146,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>360.25</x:v>
+        <x:v>324.25</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>927506</x:v>
@@ -6184,13 +6181,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>18.98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -6198,7 +6195,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>27739521</x:v>
@@ -6219,13 +6216,13 @@
         <x:v>1.11</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>8.41</x:v>
+        <x:v>8.38</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>2.77</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -118,90 +118,90 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>28.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
@@ -625,13 +625,7 @@
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -1304,7 +1298,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>19.86</x:v>
+        <x:v>19.91</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>21.09</x:v>
@@ -1339,7 +1333,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.38</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1371,7 +1365,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>6.48</x:v>
+        <x:v>6.49</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1403,7 +1397,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>132.5</x:v>
+        <x:v>131.8</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1435,7 +1429,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>11.03</x:v>
+        <x:v>11.55</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>7.13</x:v>
@@ -1470,7 +1464,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>31.74</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>28.75</x:v>
@@ -1505,7 +1499,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>16.94</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>15.08</x:v>
@@ -1540,7 +1534,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>5.73</x:v>
+        <x:v>5.83</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>0</x:v>
@@ -1572,7 +1566,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.7</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>23.54</x:v>
@@ -1589,7 +1583,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>17641798</x:v>
+        <x:v>18217299</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>80000000</x:v>
@@ -1598,19 +1592,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>440645684</x:v>
+        <x:v>456298736</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.68</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>27.36</x:v>
+        <x:v>27.48</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>24.98</x:v>
+        <x:v>25.05</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>34</x:v>
@@ -1677,7 +1671,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>39.36</x:v>
+        <x:v>39.96</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>39.18</x:v>
@@ -1712,7 +1706,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>58.2</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.93</x:v>
@@ -1747,7 +1741,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>7.49</x:v>
+        <x:v>7.52</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>48.39</x:v>
@@ -1782,7 +1776,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.19</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>0</x:v>
@@ -1796,7 +1790,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>875000</x:v>
+        <x:v>925000</x:v>
       </x:c>
       <x:c r="D17" s="0">
         <x:v>10000000</x:v>
@@ -1805,7 +1799,7 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>52471192</x:v>
+        <x:v>58446192</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
@@ -1817,18 +1811,18 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>59.97</x:v>
+        <x:v>63.19</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>6248196</x:v>
@@ -1849,21 +1843,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>6.59</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>236122</x:v>
@@ -1884,21 +1878,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>79.5</x:v>
+        <x:v>87.45</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>1000000</x:v>
@@ -1919,13 +1913,13 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.46</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1933,7 +1927,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>15</x:v>
@@ -1954,7 +1948,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>7.49</x:v>
+        <x:v>7.52</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>0</x:v>
@@ -1962,10 +1956,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>87187201</x:v>
@@ -1986,13 +1980,13 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.83</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -2021,7 +2015,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>53</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>23.95</x:v>
@@ -2056,7 +2050,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>727</x:v>
+        <x:v>741.5</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>528.86</x:v>
@@ -2091,7 +2085,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>27.36</x:v>
+        <x:v>27.48</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>24.19</x:v>
@@ -2102,7 +2096,7 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>67</x:v>
@@ -2126,7 +2120,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>8.83</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>10.74</x:v>
@@ -2161,7 +2155,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>7.2</x:v>
+        <x:v>7.16</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>24.08</x:v>
@@ -2196,7 +2190,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.94</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>27.31</x:v>
@@ -2231,7 +2225,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>3.18</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>4.46</x:v>
@@ -2266,7 +2260,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.61</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>13.09</x:v>
@@ -2301,7 +2295,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>36.44</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>0</x:v>
@@ -2333,7 +2327,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>6.93</x:v>
+        <x:v>7.62</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>52.14</x:v>
@@ -2368,13 +2362,13 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>43</x:v>
+        <x:v>43.32</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>39.35</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -2403,7 +2397,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>83.2</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>68.65</x:v>
@@ -2438,7 +2432,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.8</x:v>
+        <x:v>39.5</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2470,7 +2464,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>2.56</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>6.14</x:v>
@@ -2505,7 +2499,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>41.02</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2537,7 +2531,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>314.5</x:v>
+        <x:v>308.25</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>299.91</x:v>
@@ -2572,7 +2566,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>20.18</x:v>
+        <x:v>20.58</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2604,7 +2598,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>144.1</x:v>
+        <x:v>149.6</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>83</x:v>
@@ -2639,7 +2633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>37.68</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>0</x:v>
@@ -2671,7 +2665,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>41.2</x:v>
+        <x:v>41.42</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>40.97</x:v>
@@ -2706,7 +2700,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>13.58</x:v>
+        <x:v>13.36</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>5.49</x:v>
@@ -2741,7 +2735,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.73</x:v>
+        <x:v>12.76</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>0</x:v>
@@ -2773,7 +2767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>7.9</x:v>
+        <x:v>8.25</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2805,7 +2799,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>6.59</x:v>
+        <x:v>6.55</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>6.12</x:v>
@@ -2840,7 +2834,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>3.98</x:v>
@@ -2875,7 +2869,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.94</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>17.83</x:v>
@@ -2910,7 +2904,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.46</x:v>
+        <x:v>25.06</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>38.06</x:v>
@@ -2977,7 +2971,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>39.64</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>41.13</x:v>
@@ -3012,7 +3006,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>16.22</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>20.11</x:v>
@@ -3047,7 +3041,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>81.8</x:v>
+        <x:v>81.05</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>39.43</x:v>
@@ -3082,7 +3076,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>19.12</x:v>
+        <x:v>20.1</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>0</x:v>
@@ -3114,7 +3108,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>22.56</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>16.34</x:v>
@@ -3149,7 +3143,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>84.6</x:v>
+        <x:v>83.1</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>38.88</x:v>
@@ -3184,7 +3178,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>62.6</x:v>
+        <x:v>65.85</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3216,7 +3210,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>5.69</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3248,7 +3242,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>38.46</x:v>
+        <x:v>38.98</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3280,7 +3274,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>9.51</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>161.23</x:v>
@@ -3315,7 +3309,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>18.4</x:v>
+        <x:v>19.09</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>15.68</x:v>
@@ -3385,7 +3379,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.15</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
@@ -3455,7 +3449,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>37.5</x:v>
+        <x:v>37.84</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3487,7 +3481,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3522,7 +3516,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>56.65</x:v>
+        <x:v>56.75</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
@@ -3557,7 +3551,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.86</x:v>
+        <x:v>19.91</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3592,7 +3586,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>21.92</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3627,7 +3621,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.6</x:v>
+        <x:v>7.62</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
@@ -3662,7 +3656,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>52</x:v>
+        <x:v>55.4</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
@@ -3697,7 +3691,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>70.5</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
@@ -3732,7 +3726,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>44.02</x:v>
+        <x:v>44.52</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3764,7 +3758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.63</x:v>
+        <x:v>7.62</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3796,7 +3790,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.8</x:v>
+        <x:v>7.51</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
@@ -3831,7 +3825,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.59</x:v>
+        <x:v>13.53</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
@@ -3866,7 +3860,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>11.33</x:v>
+        <x:v>12.46</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
@@ -3901,7 +3895,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.15</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
@@ -3936,7 +3930,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>254</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
@@ -3971,7 +3965,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>12.19</x:v>
+        <x:v>12.34</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
@@ -4006,7 +4000,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
@@ -4041,7 +4035,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>28.74</x:v>
+        <x:v>29.18</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>17.65</x:v>
@@ -4076,13 +4070,13 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>14.47</x:v>
+        <x:v>14.65</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -4111,7 +4105,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>7.03</x:v>
+        <x:v>7.02</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>40.97</x:v>
@@ -4178,7 +4172,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.33</x:v>
+        <x:v>18.45</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>16.42</x:v>
@@ -4213,7 +4207,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>132.5</x:v>
+        <x:v>131.8</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>31.92</x:v>
@@ -4248,7 +4242,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>97.15</x:v>
+        <x:v>95.65</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>94.36</x:v>
@@ -4283,7 +4277,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>5</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>4.52</x:v>
@@ -4318,7 +4312,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>727</x:v>
+        <x:v>741.5</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>429.82</x:v>
@@ -4353,7 +4347,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4.27</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>2.64</x:v>
@@ -4388,7 +4382,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>11.9</x:v>
+        <x:v>13.09</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>8.23</x:v>
@@ -4423,7 +4417,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.32</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>0</x:v>
@@ -4455,7 +4449,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>29.32</x:v>
+        <x:v>29.64</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>23.83</x:v>
@@ -4490,7 +4484,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.76</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>5.03</x:v>
@@ -4525,7 +4519,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>34.52</x:v>
+        <x:v>37.96</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>0</x:v>
@@ -4557,7 +4551,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>27.36</x:v>
+        <x:v>27.48</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>20.53</x:v>
@@ -4568,7 +4562,7 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>186</x:v>
@@ -4592,7 +4586,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>8.83</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>4.48</x:v>
@@ -4627,7 +4621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>4.43</x:v>
+        <x:v>4.47</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>0</x:v>
@@ -4659,7 +4653,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>8.4</x:v>
+        <x:v>7.86</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4691,7 +4685,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>123.5</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>50.97</x:v>
@@ -4708,7 +4702,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>5067479</x:v>
+        <x:v>5267479</x:v>
       </x:c>
       <x:c r="D102" s="0">
         <x:v>11160000</x:v>
@@ -4717,27 +4711,27 @@
         <x:v>125000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>49864423</x:v>
+        <x:v>52505825</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>4.54</x:v>
+        <x:v>4.72</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>12.73</x:v>
+        <x:v>12.76</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>9.84</x:v>
+        <x:v>9.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>186</x:v>
@@ -4761,18 +4755,18 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>38.98</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>37.71</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>186</x:v>
@@ -4796,18 +4790,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>105.2</x:v>
+        <x:v>106.3</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>186</x:v>
@@ -4831,7 +4825,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>489</x:v>
+        <x:v>500.5</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>0</x:v>
@@ -4839,7 +4833,7 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>186</x:v>
@@ -4863,7 +4857,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>13.86</x:v>
+        <x:v>12.48</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>4.56</x:v>
@@ -4874,7 +4868,7 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>186</x:v>
@@ -4898,7 +4892,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>16</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>15.2</x:v>
@@ -4909,7 +4903,7 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>186</x:v>
@@ -4933,21 +4927,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.34</x:v>
+        <x:v>31.66</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>2975773</x:v>
@@ -4968,7 +4962,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>26.12</x:v>
+        <x:v>26.46</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>15.05</x:v>
@@ -4979,10 +4973,10 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>10994323</x:v>
@@ -5003,24 +4997,24 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>15.03</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>26126543</x:v>
+        <x:v>26626543</x:v>
       </x:c>
       <x:c r="D111" s="0">
         <x:v>195000000</x:v>
@@ -5029,19 +5023,19 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>248960787</x:v>
+        <x:v>256460787</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1.34</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.05</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>9.53</x:v>
+        <x:v>9.63</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
         <x:v>34</x:v>
@@ -5049,10 +5043,10 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>5100000</x:v>
@@ -5073,21 +5067,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>60</x:v>
+        <x:v>59.7</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>15</x:v>
@@ -5108,7 +5102,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>2.51</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5116,10 +5110,10 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>5000000</x:v>
@@ -5140,21 +5134,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>8.87</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>590777</x:v>
@@ -5175,21 +5169,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>17.56</x:v>
+        <x:v>17.67</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>15</x:v>
@@ -5210,7 +5204,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>83.8</x:v>
+        <x:v>85.9</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5218,10 +5212,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>15</x:v>
@@ -5242,7 +5236,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>489</x:v>
+        <x:v>500.5</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5250,10 +5244,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>53584</x:v>
@@ -5274,7 +5268,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>229</x:v>
+        <x:v>240.9</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>154.36</x:v>
@@ -5285,10 +5279,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>7550000</x:v>
@@ -5309,21 +5303,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>14.83</x:v>
+        <x:v>13.35</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>2097716</x:v>
@@ -5344,7 +5338,7 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>15.6</x:v>
+        <x:v>15.46</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>13.82</x:v>
@@ -5355,10 +5349,10 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>5185302</x:v>
@@ -5379,7 +5373,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>5.77</x:v>
+        <x:v>5.71</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>7.15</x:v>
@@ -5390,10 +5384,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>669111</x:v>
@@ -5414,7 +5408,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>541</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>226</x:v>
@@ -5425,10 +5419,10 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>38840</x:v>
@@ -5449,21 +5443,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>489</x:v>
+        <x:v>500.5</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2250000</x:v>
@@ -5484,21 +5478,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.83</x:v>
+        <x:v>13.35</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>1500000</x:v>
@@ -5519,21 +5513,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>15.6</x:v>
+        <x:v>15.46</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>281228</x:v>
@@ -5554,7 +5548,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>141.2</x:v>
+        <x:v>143.6</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>135.2</x:v>
@@ -5568,7 +5562,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>15</x:v>
@@ -5589,7 +5583,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>144.1</x:v>
+        <x:v>149.6</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>0</x:v>
@@ -5600,7 +5594,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>845945</x:v>
@@ -5621,21 +5615,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.56</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>21446</x:v>
@@ -5656,7 +5650,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>57.5</x:v>
+        <x:v>58.15</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>94</x:v>
@@ -5667,10 +5661,10 @@
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>850000</x:v>
@@ -5691,7 +5685,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>8.52</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>7.7</x:v>
@@ -5702,10 +5696,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>15000000</x:v>
@@ -5726,21 +5720,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3.01</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>6397124</x:v>
@@ -5761,21 +5755,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>4.69</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>8578668</x:v>
@@ -5796,21 +5790,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>21.46</x:v>
+        <x:v>21.58</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>9350000</x:v>
@@ -5831,13 +5825,13 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>9.2</x:v>
+        <x:v>9.23</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
@@ -5845,7 +5839,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1468255</x:v>
@@ -5866,21 +5860,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>83.2</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>500000</x:v>
@@ -5901,7 +5895,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>26.8</x:v>
@@ -5915,7 +5909,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>725000</x:v>
@@ -5936,13 +5930,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>41.02</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -5950,7 +5944,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>1060056</x:v>
@@ -5977,7 +5971,7 @@
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -5985,7 +5979,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>132750000</x:v>
@@ -6006,7 +6000,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>4.26</x:v>
@@ -6017,10 +6011,10 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>373000</x:v>
@@ -6041,21 +6035,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>7.38</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>10000000</x:v>
@@ -6076,21 +6070,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>5.67</x:v>
+        <x:v>5.59</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>3081843</x:v>
@@ -6111,21 +6105,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.53</x:v>
+        <x:v>7.57</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>1348769</x:v>
@@ -6146,21 +6140,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>324.25</x:v>
+        <x:v>336.5</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>927506</x:v>
@@ -6181,13 +6175,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>19</x:v>
+        <x:v>19.18</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -6195,7 +6189,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>27739521</x:v>
@@ -6216,13 +6210,13 @@
         <x:v>1.11</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>8.38</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>2.77</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -118,51 +118,54 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>29.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>DAGI</x:t>
   </x:si>
   <x:si>
@@ -878,12 +881,6 @@
   </x:si>
   <x:si>
     <x:t>24.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.12.2023</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1234,7 +1231,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K145"/>
+  <x:dimension ref="A1:K144"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1298,7 +1295,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>19.91</x:v>
+        <x:v>19.38</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>21.09</x:v>
@@ -1333,7 +1330,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.41</x:v>
+        <x:v>8.31</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1365,7 +1362,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>6.49</x:v>
+        <x:v>6.39</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1397,7 +1394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>131.8</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1429,7 +1426,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>7.13</x:v>
@@ -1464,7 +1461,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>30.2</x:v>
+        <x:v>30.46</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>28.75</x:v>
@@ -1499,7 +1496,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>16.9</x:v>
+        <x:v>16.2</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>15.08</x:v>
@@ -1534,7 +1531,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>5.83</x:v>
+        <x:v>5.75</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>0</x:v>
@@ -1566,7 +1563,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.2</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>23.54</x:v>
@@ -1583,7 +1580,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>18217299</x:v>
+        <x:v>18393155</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>80000000</x:v>
@@ -1592,19 +1589,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>456298736</x:v>
+        <x:v>461119653</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>27.48</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>25.05</x:v>
+        <x:v>25.07</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>34</x:v>
@@ -1636,7 +1633,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>13.37</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>13.34</x:v>
@@ -1671,7 +1668,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>39.96</x:v>
+        <x:v>39.08</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>39.18</x:v>
@@ -1706,7 +1703,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>58.95</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.93</x:v>
@@ -1741,7 +1738,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>7.52</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>48.39</x:v>
@@ -1776,7 +1773,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.22</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>0</x:v>
@@ -1808,21 +1805,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>119</x:v>
+        <x:v>112.2</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>63.19</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>6248196</x:v>
@@ -1843,21 +1840,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>6.65</x:v>
+        <x:v>6.71</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>236122</x:v>
@@ -1878,21 +1875,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>87.45</x:v>
+        <x:v>83.4</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>1000000</x:v>
@@ -1913,13 +1910,13 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.36</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1927,7 +1924,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>15</x:v>
@@ -1948,7 +1945,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>7.52</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>0</x:v>
@@ -1956,10 +1953,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>87187201</x:v>
@@ -1980,21 +1977,21 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>16445115</x:v>
@@ -2015,21 +2012,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>52.15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>1110000</x:v>
@@ -2050,7 +2047,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>741.5</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>528.86</x:v>
@@ -2064,7 +2061,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>24398659</x:v>
@@ -2085,21 +2082,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>27.48</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>46563878</x:v>
@@ -2120,21 +2117,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>226257</x:v>
@@ -2155,21 +2152,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>7.16</x:v>
+        <x:v>7.33</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>1969635</x:v>
@@ -2190,21 +2187,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.8</x:v>
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1000000</x:v>
@@ -2225,21 +2222,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.22</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100000</x:v>
@@ -2260,21 +2257,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.6</x:v>
+        <x:v>8.62</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>15</x:v>
@@ -2295,7 +2292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>36.64</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>0</x:v>
@@ -2303,10 +2300,10 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>5831653</x:v>
@@ -2327,21 +2324,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>7.62</x:v>
+        <x:v>8.38</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>13200000</x:v>
@@ -2362,21 +2359,21 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>43.32</x:v>
+        <x:v>44.1</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>39.35</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>1973951</x:v>
@@ -2397,21 +2394,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>85.5</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>15</x:v>
@@ -2432,7 +2429,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.5</x:v>
+        <x:v>39.74</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2440,10 +2437,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>3337681</x:v>
@@ -2464,7 +2461,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>6.14</x:v>
@@ -2475,10 +2472,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>15</x:v>
@@ -2499,7 +2496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>41.22</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2507,10 +2504,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>1364000</x:v>
@@ -2531,21 +2528,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>308.25</x:v>
+        <x:v>300.75</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>15</x:v>
@@ -2566,7 +2563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>20.58</x:v>
+        <x:v>19.77</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2574,10 +2571,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>507440</x:v>
@@ -2598,21 +2595,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>149.6</x:v>
+        <x:v>156.8</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>15</x:v>
@@ -2633,7 +2630,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>38.34</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>0</x:v>
@@ -2641,10 +2638,10 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>2000000</x:v>
@@ -2665,21 +2662,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>41.42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>324474</x:v>
@@ -2700,21 +2697,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>13.36</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>15</x:v>
@@ -2735,7 +2732,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.76</x:v>
+        <x:v>12.54</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>0</x:v>
@@ -2743,10 +2740,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>15</x:v>
@@ -2767,7 +2764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>8.25</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2775,10 +2772,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>2000000</x:v>
@@ -2799,7 +2796,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>6.55</x:v>
+        <x:v>6.43</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>6.12</x:v>
@@ -2810,10 +2807,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>174500000</x:v>
@@ -2834,21 +2831,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>3.14</x:v>
+        <x:v>3.12</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>635229</x:v>
@@ -2869,21 +2866,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.8</x:v>
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>130000</x:v>
@@ -2904,21 +2901,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.06</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>15</x:v>
@@ -2939,7 +2936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>240</x:v>
+        <x:v>225.3</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>0</x:v>
@@ -2947,10 +2944,10 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>447761</x:v>
@@ -2971,21 +2968,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>39.62</x:v>
+        <x:v>39.48</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>200000</x:v>
@@ -3006,21 +3003,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>14.6</x:v>
+        <x:v>13.14</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>946718</x:v>
@@ -3041,21 +3038,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>81.05</x:v>
+        <x:v>82.7</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>15</x:v>
@@ -3076,7 +3073,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>20.1</x:v>
+        <x:v>20.26</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>0</x:v>
@@ -3084,10 +3081,10 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>3043115</x:v>
@@ -3108,21 +3105,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>22.74</x:v>
+        <x:v>23.42</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>2382736</x:v>
@@ -3143,21 +3140,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>83.1</x:v>
+        <x:v>82.05</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>15</x:v>
@@ -3178,7 +3175,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>65.85</x:v>
+        <x:v>64.55</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3186,10 +3183,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>15</x:v>
@@ -3210,7 +3207,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>5.68</x:v>
+        <x:v>6.24</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3218,10 +3215,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>15</x:v>
@@ -3242,7 +3239,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>38.98</x:v>
+        <x:v>38.3</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3250,10 +3247,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>310000</x:v>
@@ -3274,21 +3271,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>9.26</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>2000000</x:v>
@@ -3309,7 +3306,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>19.09</x:v>
+        <x:v>18.98</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>15.68</x:v>
@@ -3320,10 +3317,10 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>1250000</x:v>
@@ -3344,21 +3341,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>3.07</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3379,21 +3376,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.19</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3414,21 +3411,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>112.1</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>15</x:v>
@@ -3449,7 +3446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>37.84</x:v>
+        <x:v>36.48</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3457,10 +3454,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3481,7 +3478,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.9</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3492,10 +3489,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3516,13 +3513,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>56.75</x:v>
+        <x:v>55.75</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -3530,7 +3527,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3551,7 +3548,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.91</x:v>
+        <x:v>19.38</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3562,10 +3559,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3586,7 +3583,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>22.26</x:v>
+        <x:v>23.18</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3597,10 +3594,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3621,21 +3618,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.62</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3656,21 +3653,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>55.4</x:v>
+        <x:v>57.5</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3691,21 +3688,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>74.6</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>15</x:v>
@@ -3726,7 +3723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>44.52</x:v>
+        <x:v>44.32</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3734,10 +3731,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>15</x:v>
@@ -3758,7 +3755,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.62</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3766,10 +3763,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3790,21 +3787,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.51</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3825,21 +3822,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.53</x:v>
+        <x:v>13.32</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -3860,21 +3857,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>12.46</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -3895,21 +3892,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.11</x:v>
+        <x:v>4.17</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -3930,21 +3927,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>258</x:v>
+        <x:v>247.4</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -3965,21 +3962,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>12.34</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -4000,21 +3997,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>241</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>5100000</x:v>
@@ -4035,21 +4032,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>29.18</x:v>
+        <x:v>28.66</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>3228679</x:v>
@@ -4070,21 +4067,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>14.65</x:v>
+        <x:v>14.52</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>150000</x:v>
@@ -4105,21 +4102,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>7.02</x:v>
+        <x:v>6.92</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>15</x:v>
@@ -4140,7 +4137,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>18.13</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>0</x:v>
@@ -4148,10 +4145,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>366107</x:v>
@@ -4172,13 +4169,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.45</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -4186,7 +4183,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>120000</x:v>
@@ -4207,21 +4204,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>131.8</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>13050000</x:v>
@@ -4242,21 +4239,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>95.65</x:v>
+        <x:v>93.4</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>23682251</x:v>
@@ -4277,7 +4274,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>5.27</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>4.52</x:v>
@@ -4288,10 +4285,10 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>1000000</x:v>
@@ -4312,21 +4309,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>741.5</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>300000</x:v>
@@ -4347,21 +4344,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>3.98</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>2175097</x:v>
@@ -4382,21 +4379,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>13.09</x:v>
+        <x:v>14.39</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>15</x:v>
@@ -4417,7 +4414,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>3.32</x:v>
+        <x:v>3.24</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>0</x:v>
@@ -4425,10 +4422,10 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>43000</x:v>
@@ -4449,21 +4446,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>29.64</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>9937037</x:v>
@@ -4484,21 +4481,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.7</x:v>
+        <x:v>3.71</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>15</x:v>
@@ -4519,7 +4516,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>37.96</x:v>
+        <x:v>41.74</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>0</x:v>
@@ -4530,7 +4527,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>13064888</x:v>
@@ -4551,21 +4548,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>27.48</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>111673026</x:v>
@@ -4586,21 +4583,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>15</x:v>
@@ -4621,7 +4618,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>4.47</x:v>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>0</x:v>
@@ -4629,10 +4626,10 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>15</x:v>
@@ -4653,7 +4650,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>7.86</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4661,10 +4658,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>1100000</x:v>
@@ -4685,21 +4682,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>120</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>5267479</x:v>
@@ -4720,21 +4717,21 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>12.76</x:v>
+        <x:v>12.54</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1460000</x:v>
@@ -4755,21 +4752,21 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>40</x:v>
+        <x:v>42.54</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>37.71</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1989802</x:v>
@@ -4790,21 +4787,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>106.3</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>15</x:v>
@@ -4825,7 +4822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>500.5</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>0</x:v>
@@ -4833,10 +4830,10 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>300000</x:v>
@@ -4857,21 +4854,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>12.48</x:v>
+        <x:v>11.87</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>8291656</x:v>
@@ -4892,21 +4889,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>15.68</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>76908759</x:v>
@@ -4927,21 +4924,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>31.66</x:v>
+        <x:v>30.54</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>2975773</x:v>
@@ -4962,7 +4959,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>26.46</x:v>
+        <x:v>26.24</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>15.05</x:v>
@@ -4973,10 +4970,10 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>10994323</x:v>
@@ -4997,21 +4994,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>15.12</x:v>
+        <x:v>14.82</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>26626543</x:v>
@@ -5032,21 +5029,21 @@
         <x:v>1.37</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.3</x:v>
+        <x:v>15.41</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>9.63</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>5100000</x:v>
@@ -5067,21 +5064,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>59.7</x:v>
+        <x:v>58.85</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>15</x:v>
@@ -5102,7 +5099,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>2.56</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5110,10 +5107,10 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>5000000</x:v>
@@ -5134,21 +5131,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>8.95</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>590777</x:v>
@@ -5169,21 +5166,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>17.67</x:v>
+        <x:v>17.23</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>15</x:v>
@@ -5204,7 +5201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>85.9</x:v>
+        <x:v>83.5</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5212,10 +5209,10 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>15</x:v>
@@ -5236,7 +5233,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>500.5</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5244,10 +5241,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>53584</x:v>
@@ -5268,7 +5265,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>240.9</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>154.36</x:v>
@@ -5279,10 +5276,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>7550000</x:v>
@@ -5303,21 +5300,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>13.35</x:v>
+        <x:v>12.02</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>2097716</x:v>
@@ -5338,21 +5335,21 @@
         <x:v>1.82</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>15.46</x:v>
+        <x:v>15.45</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>5185302</x:v>
@@ -5373,21 +5370,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>5.71</x:v>
+        <x:v>5.51</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>669111</x:v>
@@ -5408,21 +5405,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>551</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>38840</x:v>
@@ -5443,21 +5440,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>500.5</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>2250000</x:v>
@@ -5478,21 +5475,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>13.35</x:v>
+        <x:v>12.02</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>1500000</x:v>
@@ -5513,21 +5510,21 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>15.46</x:v>
+        <x:v>15.45</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>281228</x:v>
@@ -5548,7 +5545,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>143.6</x:v>
+        <x:v>148.5</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>135.2</x:v>
@@ -5559,10 +5556,10 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>15</x:v>
@@ -5583,7 +5580,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>149.6</x:v>
+        <x:v>156.8</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>0</x:v>
@@ -5591,10 +5588,10 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>845945</x:v>
@@ -5615,21 +5612,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>21446</x:v>
@@ -5650,21 +5647,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>58.15</x:v>
+        <x:v>57.6</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>850000</x:v>
@@ -5685,21 +5682,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>8.4</x:v>
+        <x:v>8.06</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>15000000</x:v>
@@ -5720,21 +5717,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3</x:v>
+        <x:v>2.93</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>6397124</x:v>
@@ -5761,15 +5758,15 @@
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>8578668</x:v>
@@ -5790,21 +5787,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>21.58</x:v>
+        <x:v>21.36</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>9350000</x:v>
@@ -5825,21 +5822,21 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>1468255</x:v>
@@ -5860,21 +5857,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>85.5</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>500000</x:v>
@@ -5895,21 +5892,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>2.82</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>725000</x:v>
@@ -5930,21 +5927,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>41.22</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>1060056</x:v>
@@ -5965,21 +5962,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>240</x:v>
+        <x:v>225.3</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>132750000</x:v>
@@ -6000,21 +5997,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>3.14</x:v>
+        <x:v>3.12</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>373000</x:v>
@@ -6035,21 +6032,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>7.63</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>10000000</x:v>
@@ -6070,21 +6067,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>5.59</x:v>
+        <x:v>5.67</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>3081843</x:v>
@@ -6105,21 +6102,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.57</x:v>
+        <x:v>7.09</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>1348769</x:v>
@@ -6140,21 +6137,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>336.5</x:v>
+        <x:v>354.5</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>927506</x:v>
@@ -6175,48 +6172,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>19.18</x:v>
+        <x:v>19.02</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:11">
-      <x:c r="A145" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="C145" s="0">
-        <x:v>27739521</x:v>
-      </x:c>
-      <x:c r="D145" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="E145" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F145" s="0">
-        <x:v>76729767</x:v>
-      </x:c>
-      <x:c r="G145" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H145" s="0">
-        <x:v>1.11</x:v>
-      </x:c>
-      <x:c r="I145" s="0">
-        <x:v>8.41</x:v>
-      </x:c>
-      <x:c r="J145" s="0">
-        <x:v>2.77</x:v>
-      </x:c>
-      <x:c r="K145" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -118,7 +118,7 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>30.04.2026</x:t>
+    <x:t>04.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
@@ -163,472 +163,472 @@
     <x:t>27.11.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
     <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
   </x:si>
   <x:si>
     <x:t>TCKRC</x:t>
@@ -1295,7 +1295,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>19.38</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>21.09</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.31</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1362,7 +1362,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>6.39</x:v>
+        <x:v>6.43</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1394,7 +1394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1426,7 +1426,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>12.7</x:v>
+        <x:v>11.81</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>7.13</x:v>
@@ -1461,7 +1461,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>30.46</x:v>
+        <x:v>28.98</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>28.75</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16.15</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>15.08</x:v>
@@ -1531,7 +1531,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>5.75</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>0</x:v>
@@ -1563,7 +1563,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.5</x:v>
+        <x:v>22.62</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>23.54</x:v>
@@ -1580,7 +1580,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>18393155</x:v>
+        <x:v>18620446</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>80000000</x:v>
@@ -1589,19 +1589,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>461119653</x:v>
+        <x:v>467253782</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>27</x:v>
+        <x:v>27.86</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>25.07</x:v>
+        <x:v>25.09</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>34</x:v>
@@ -1633,7 +1633,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>13.5</x:v>
+        <x:v>13.63</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>13.34</x:v>
@@ -1668,7 +1668,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>39.08</x:v>
+        <x:v>40.8</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>39.18</x:v>
@@ -1703,7 +1703,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>58.25</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>59.93</x:v>
@@ -1738,7 +1738,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.42</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>48.39</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.05</x:v>
+        <x:v>6.33</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>0</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>925000</x:v>
+        <x:v>950000</x:v>
       </x:c>
       <x:c r="D17" s="0">
         <x:v>10000000</x:v>
@@ -1796,30 +1796,30 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>58446192</x:v>
+        <x:v>61251192</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.11</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>112.2</x:v>
+        <x:v>105.7</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>63.19</x:v>
+        <x:v>64.47</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>6248196</x:v>
@@ -1840,21 +1840,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>6.71</x:v>
+        <x:v>7.16</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>236122</x:v>
@@ -1875,21 +1875,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>83.4</x:v>
+        <x:v>81.4</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>1000000</x:v>
@@ -1910,13 +1910,13 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.36</x:v>
+        <x:v>21.38</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1924,7 +1924,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>15</x:v>
@@ -1945,7 +1945,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>7.32</x:v>
+        <x:v>7.42</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>0</x:v>
@@ -1953,10 +1953,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>87187201</x:v>
@@ -1977,21 +1977,21 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.97</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>16445115</x:v>
@@ -2012,21 +2012,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>1110000</x:v>
@@ -2047,7 +2047,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>730</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>528.86</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>24398659</x:v>
@@ -2082,21 +2082,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>27</x:v>
+        <x:v>27.86</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>46563878</x:v>
@@ -2117,21 +2117,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>8.97</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>226257</x:v>
@@ -2152,21 +2152,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>7.33</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>1969635</x:v>
@@ -2187,21 +2187,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.1</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1000000</x:v>
@@ -2222,21 +2222,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>3.22</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100000</x:v>
@@ -2257,21 +2257,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.62</x:v>
+        <x:v>8.69</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>15</x:v>
@@ -2292,7 +2292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>35.8</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>0</x:v>
@@ -2300,10 +2300,10 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>5831653</x:v>
@@ -2324,21 +2324,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>8.38</x:v>
+        <x:v>8.81</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>13200000</x:v>
@@ -2359,21 +2359,21 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>44.1</x:v>
+        <x:v>44.48</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>39.35</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>1973951</x:v>
@@ -2394,21 +2394,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>82.35</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>15</x:v>
@@ -2429,7 +2429,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>39.74</x:v>
+        <x:v>40.22</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>0</x:v>
@@ -2437,10 +2437,10 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>3337681</x:v>
@@ -2461,7 +2461,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>6.14</x:v>
@@ -2472,10 +2472,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>15</x:v>
@@ -2496,7 +2496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>40.94</x:v>
+        <x:v>41.58</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>0</x:v>
@@ -2504,10 +2504,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>1364000</x:v>
@@ -2528,21 +2528,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>300.75</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>15</x:v>
@@ -2563,7 +2563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>19.77</x:v>
+        <x:v>20.26</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>0</x:v>
@@ -2571,10 +2571,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>507440</x:v>
@@ -2595,21 +2595,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>156.8</x:v>
+        <x:v>162.3</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>15</x:v>
@@ -2630,7 +2630,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>38.82</x:v>
+        <x:v>38.32</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>0</x:v>
@@ -2638,10 +2638,10 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>2000000</x:v>
@@ -2662,21 +2662,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>41</x:v>
+        <x:v>43.26</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>324474</x:v>
@@ -2697,22 +2697,22 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>12.66</x:v>
+        <x:v>12.31</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2732,7 +2732,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.54</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>0</x:v>
@@ -2740,10 +2740,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>15</x:v>
@@ -2764,7 +2764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>8.45</x:v>
+        <x:v>8.74</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2772,10 +2772,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>2000000</x:v>
@@ -2796,7 +2796,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>6.43</x:v>
+        <x:v>6.39</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>6.12</x:v>
@@ -2807,10 +2807,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>174500000</x:v>
@@ -2831,21 +2831,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>3.12</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>635229</x:v>
@@ -2866,21 +2866,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>23.1</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>130000</x:v>
@@ -2901,21 +2901,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>26.96</x:v>
+        <x:v>27.3</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>15</x:v>
@@ -2936,7 +2936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>225.3</x:v>
+        <x:v>231.2</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>0</x:v>
@@ -2944,10 +2944,10 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>447761</x:v>
@@ -2968,21 +2968,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>39.48</x:v>
+        <x:v>40.22</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>200000</x:v>
@@ -3003,21 +3003,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>13.14</x:v>
+        <x:v>12.54</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>946718</x:v>
@@ -3038,21 +3038,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>82.7</x:v>
+        <x:v>85.8</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>15</x:v>
@@ -3073,7 +3073,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>20.26</x:v>
+        <x:v>21.3</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>0</x:v>
@@ -3081,10 +3081,10 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>3043115</x:v>
@@ -3105,21 +3105,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.42</x:v>
+        <x:v>23.52</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>2382736</x:v>
@@ -3140,21 +3140,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>82.05</x:v>
+        <x:v>82.5</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>15</x:v>
@@ -3175,7 +3175,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>64.55</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>0</x:v>
@@ -3183,10 +3183,10 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>15</x:v>
@@ -3207,7 +3207,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>6.24</x:v>
+        <x:v>6.07</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3215,10 +3215,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>15</x:v>
@@ -3239,7 +3239,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>38.3</x:v>
+        <x:v>38.42</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3247,10 +3247,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>310000</x:v>
@@ -3271,21 +3271,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>2000000</x:v>
@@ -3306,7 +3306,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>18.98</x:v>
+        <x:v>19.39</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>15.68</x:v>
@@ -3317,10 +3317,10 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>1250000</x:v>
@@ -3341,21 +3341,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>3.03</x:v>
+        <x:v>3.04</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>12500000</x:v>
@@ -3376,21 +3376,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.16</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>2093944</x:v>
@@ -3411,21 +3411,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>111</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>15</x:v>
@@ -3446,7 +3446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>36.48</x:v>
+        <x:v>36.46</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>0</x:v>
@@ -3454,10 +3454,10 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>51245979</x:v>
@@ -3478,7 +3478,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.9</x:v>
+        <x:v>2.92</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.45</x:v>
@@ -3489,10 +3489,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>1584837</x:v>
@@ -3513,13 +3513,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>55.75</x:v>
+        <x:v>56.1</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -3527,7 +3527,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>7999148</x:v>
@@ -3548,7 +3548,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.38</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>21.09</x:v>
@@ -3559,10 +3559,10 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>14000000</x:v>
@@ -3583,7 +3583,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>23.18</x:v>
+        <x:v>23.28</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>16.87</x:v>
@@ -3594,10 +3594,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>1700005</x:v>
@@ -3618,21 +3618,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.59</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>6000000</x:v>
@@ -3653,21 +3653,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>57.5</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>1675000</x:v>
@@ -3688,21 +3688,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>77.7</x:v>
+        <x:v>80.4</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>15</x:v>
@@ -3723,7 +3723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>44.32</x:v>
+        <x:v>45.16</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>0</x:v>
@@ -3731,10 +3731,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>15</x:v>
@@ -3755,7 +3755,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.38</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3763,10 +3763,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>1000000</x:v>
@@ -3787,21 +3787,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.5</x:v>
+        <x:v>7.52</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>98551</x:v>
@@ -3822,21 +3822,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>13.32</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>6049315</x:v>
@@ -3857,21 +3857,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>12.77</x:v>
+        <x:v>12.36</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>37225000</x:v>
@@ -3892,21 +3892,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.17</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1000000</x:v>
@@ -3927,21 +3927,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>247.4</x:v>
+        <x:v>245.2</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>600000</x:v>
@@ -3962,21 +3962,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>11.36</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>11703083</x:v>
@@ -3997,21 +3997,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>235</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>5100000</x:v>
@@ -4032,21 +4032,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>28.66</x:v>
+        <x:v>30.46</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>3228679</x:v>
@@ -4067,21 +4067,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>14.52</x:v>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>150000</x:v>
@@ -4102,21 +4102,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>6.92</x:v>
+        <x:v>6.95</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>15</x:v>
@@ -4137,7 +4137,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>18.32</x:v>
+        <x:v>18.08</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>0</x:v>
@@ -4145,10 +4145,10 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>366107</x:v>
@@ -4169,13 +4169,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>17.6</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -4183,7 +4183,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>120000</x:v>
@@ -4204,21 +4204,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>13050000</x:v>
@@ -4239,21 +4239,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>93.4</x:v>
+        <x:v>94.65</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>23682251</x:v>
@@ -4274,7 +4274,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>5.43</x:v>
+        <x:v>5.47</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>4.52</x:v>
@@ -4285,10 +4285,10 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>1000000</x:v>
@@ -4309,21 +4309,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>730</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>300000</x:v>
@@ -4344,21 +4344,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>2175097</x:v>
@@ -4379,21 +4379,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>14.39</x:v>
+        <x:v>15.82</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>15</x:v>
@@ -4414,7 +4414,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>3.24</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>0</x:v>
@@ -4422,10 +4422,10 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>43000</x:v>
@@ -4446,21 +4446,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>30.2</x:v>
+        <x:v>31.02</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>9937037</x:v>
@@ -4481,21 +4481,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.71</x:v>
+        <x:v>3.68</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>15</x:v>
@@ -4516,7 +4516,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>41.74</x:v>
+        <x:v>42.48</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>0</x:v>
@@ -4527,7 +4527,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>13064888</x:v>
@@ -4548,21 +4548,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>27</x:v>
+        <x:v>27.86</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>111673026</x:v>
@@ -4583,21 +4583,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>8.97</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>15</x:v>
@@ -4618,7 +4618,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>4.55</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>0</x:v>
@@ -4626,10 +4626,10 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>15</x:v>
@@ -4650,7 +4650,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4658,10 +4658,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>1100000</x:v>
@@ -4682,21 +4682,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>132</x:v>
+        <x:v>124.4</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>5267479</x:v>
@@ -4717,21 +4717,21 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>12.54</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>1460000</x:v>
@@ -4752,13 +4752,13 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>42.54</x:v>
+        <x:v>43.26</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>37.71</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4766,7 +4766,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1989802</x:v>
@@ -4787,7 +4787,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>111.8</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>39.56</x:v>
@@ -4801,7 +4801,7 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>15</x:v>
@@ -4822,7 +4822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>0</x:v>
@@ -4833,7 +4833,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>300000</x:v>
@@ -4854,13 +4854,13 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>11.87</x:v>
+        <x:v>11.47</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -4868,7 +4868,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>8291656</x:v>
@@ -4889,13 +4889,13 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>15.7</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -4903,7 +4903,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>76908759</x:v>
@@ -4924,7 +4924,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>30.54</x:v>
+        <x:v>30.86</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>25.74</x:v>
@@ -4959,7 +4959,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>26.24</x:v>
+        <x:v>26.58</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>15.05</x:v>
@@ -4994,7 +4994,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>14.82</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>16.65</x:v>
@@ -5029,13 +5029,13 @@
         <x:v>1.37</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.41</x:v>
+        <x:v>15.49</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>9.63</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -5064,7 +5064,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>58.85</x:v>
+        <x:v>59.8</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>30.45</x:v>
@@ -5099,7 +5099,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5131,7 +5131,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>8.97</x:v>
+        <x:v>9.04</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>7.82</x:v>
@@ -5166,7 +5166,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>17.23</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>21.06</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>83.5</x:v>
+        <x:v>83.75</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>0</x:v>
@@ -5233,7 +5233,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5265,7 +5265,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>239</x:v>
+        <x:v>236.3</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>154.36</x:v>
@@ -5300,7 +5300,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>12.02</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>14.81</x:v>
@@ -5332,16 +5332,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>1.82</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>15.45</x:v>
+        <x:v>2.14</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
@@ -5370,13 +5370,13 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>5.51</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -5405,13 +5405,13 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>561</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5440,7 +5440,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>242.84</x:v>
@@ -5475,7 +5475,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>12.02</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>14.11</x:v>
@@ -5507,10 +5507,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1.3</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>15.45</x:v>
+        <x:v>2.14</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.58</x:v>
@@ -5545,7 +5545,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>148.5</x:v>
+        <x:v>153.1</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>135.2</x:v>
@@ -5556,7 +5556,7 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>248</x:v>
@@ -5580,7 +5580,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>156.8</x:v>
+        <x:v>162.3</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>0</x:v>
@@ -5588,7 +5588,7 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>249</x:v>
@@ -5612,7 +5612,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>11.89</x:v>
@@ -5647,13 +5647,13 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>57.6</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
@@ -5682,13 +5682,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>8.06</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
@@ -5717,7 +5717,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>2.93</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>1.6</x:v>
@@ -5752,7 +5752,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>4.73</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>19.21</x:v>
@@ -5763,7 +5763,7 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>261</x:v>
@@ -5787,7 +5787,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>21.36</x:v>
+        <x:v>21.38</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>21.49</x:v>
@@ -5822,7 +5822,7 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>9.25</x:v>
+        <x:v>9.19</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>7.44</x:v>
@@ -5833,7 +5833,7 @@
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>266</x:v>
@@ -5857,7 +5857,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>82.35</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>51.7</x:v>
@@ -5892,18 +5892,18 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.63</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>270</x:v>
@@ -5927,7 +5927,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>40.94</x:v>
+        <x:v>41.58</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>66.95</x:v>
@@ -5938,7 +5938,7 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>272</x:v>
@@ -5962,7 +5962,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>225.3</x:v>
+        <x:v>231.2</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>57.32</x:v>
@@ -5973,7 +5973,7 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>274</x:v>
@@ -5997,13 +5997,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>3.12</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6032,7 +6032,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>7.88</x:v>
+        <x:v>8.36</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>63.77</x:v>
@@ -6067,7 +6067,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>5.67</x:v>
+        <x:v>6.23</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>13.33</x:v>
@@ -6102,7 +6102,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.09</x:v>
+        <x:v>6.94</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>14.27</x:v>
@@ -6137,7 +6137,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>354.5</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>166.26</x:v>
@@ -6172,7 +6172,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>19.02</x:v>
+        <x:v>19.59</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,6 +49,15 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>BOBET</x:t>
   </x:si>
   <x:si>
@@ -88,6 +97,9 @@
     <x:t>24.03.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>KONKA</x:t>
   </x:si>
   <x:si>
@@ -118,9 +130,6 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>04.05.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKFA</x:t>
   </x:si>
   <x:si>
@@ -337,13 +346,7 @@
     <x:t>13.06.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
     <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
   </x:si>
   <x:si>
     <x:t>AVGYO</x:t>
@@ -1231,7 +1234,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K144"/>
+  <x:dimension ref="A1:K145"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1277,28 +1280,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>7999148</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>15000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>300000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>168715651</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>19.43</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J2" s="0">
-        <x:v>21.09</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>13</x:v>
@@ -1309,51 +1312,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="C3" s="0">
+        <x:v>7999148</x:v>
+      </x:c>
       <x:c r="D3" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>8.39</x:v>
+        <x:v>19.74</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>0</x:v>
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>0</x:v>
@@ -1362,7 +1368,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>6.43</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1370,346 +1376,346 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>26398084</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>3215000</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>129</x:v>
+        <x:v>6.62</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>0</x:v>
+        <x:v>6.43</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>127481195</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>11.81</x:v>
+        <x:v>131.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>820810</x:v>
-      </x:c>
-      <x:c r="D7" s="0">
-        <x:v>7300000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>225000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>23601918</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>28.98</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>28.75</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>1001579</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>10000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>100000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>15106723</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>16.15</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>15.08</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>40000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F9" s="0">
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>6</x:v>
+        <x:v>16.39</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>0</x:v>
+        <x:v>15.08</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>1897370</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>2000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F10" s="0">
-        <x:v>44672185</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>2.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>22.62</x:v>
+        <x:v>6.11</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>23.54</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>18620446</x:v>
+        <x:v>1897370</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>80000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>467253782</x:v>
+        <x:v>44672185</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.72</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>27.86</x:v>
+        <x:v>22.62</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>25.09</x:v>
+        <x:v>23.54</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>7024156</x:v>
+        <x:v>18620446</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>93719334</x:v>
+        <x:v>467253782</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>13.63</x:v>
+        <x:v>27.94</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>13.34</x:v>
+        <x:v>25.09</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>3500000</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>49400000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>137144284</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>40.8</x:v>
+        <x:v>13.7</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>39.18</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>3753472</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>6000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>432000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>224929072</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>57.75</x:v>
+        <x:v>43.54</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>59.93</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1720,28 +1726,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>3189049</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>4000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>400000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>154328962</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>7.42</x:v>
+        <x:v>58.9</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>48.39</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
         <x:v>44</x:v>
@@ -1754,99 +1760,99 @@
       <x:c r="B16" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C16" s="0">
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>35000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F16" s="0">
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.63</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.33</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>0</x:v>
+        <x:v>48.39</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>950000</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>10000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F17" s="0">
-        <x:v>61251192</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>105.7</x:v>
+        <x:v>6.49</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>64.47</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>6248196</x:v>
+        <x:v>950000</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>35000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>42144731</x:v>
+        <x:v>61251192</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>1.56</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>7.16</x:v>
+        <x:v>108.1</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>6.75</x:v>
+        <x:v>64.47</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1857,28 +1863,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>236122</x:v>
+        <x:v>6248196</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>1700000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>110000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>14609667</x:v>
+        <x:v>42144731</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>81.4</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>61.87</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>54</x:v>
@@ -1892,28 +1898,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>1000000</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>1700000</x:v>
+      </x:c>
+      <x:c r="E20" s="0">
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>21055375</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>21.38</x:v>
+        <x:v>82.4</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>21.06</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
         <x:v>57</x:v>
@@ -1921,69 +1927,69 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E21" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F21" s="0">
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>7.42</x:v>
+        <x:v>21.94</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>0</x:v>
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>87187201</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D22" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E22" s="0">
         <x:v>200000000</x:v>
       </x:c>
-      <x:c r="E22" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F22" s="0">
-        <x:v>855385832</x:v>
+      <x:c r="F22" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>9.01</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>9.81</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -1994,28 +2000,28 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>16445115</x:v>
+        <x:v>87187201</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>25000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>393919718</x:v>
+        <x:v>855385832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>23.95</x:v>
+        <x:v>9.81</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>64</x:v>
@@ -2029,133 +2035,133 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>1110000</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>2000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>1100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>587039028</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.19</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>747</x:v>
+        <x:v>55.7</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>528.86</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>24398659</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>40000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>850000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>590270273</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>27.86</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>24.19</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>46563878</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>50000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>500000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>500007798</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>9.01</x:v>
+        <x:v>27.94</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>10.74</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="C27" s="0">
-        <x:v>226257</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>9000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>240000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>5447709</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>7.95</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>24.08</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
         <x:v>72</x:v>
@@ -2169,28 +2175,28 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>1969635</x:v>
+        <x:v>226257</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E28" s="0">
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>53800530</x:v>
+        <x:v>5447709</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1.03</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>23.7</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>27.31</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
         <x:v>75</x:v>
@@ -2204,28 +2210,28 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1969635</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E29" s="0">
-        <x:v>400000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4455000</x:v>
+        <x:v>53800530</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>3.25</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>4.46</x:v>
+        <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
         <x:v>78</x:v>
@@ -2239,28 +2245,28 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>100000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>13760000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1308500</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.69</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>13.09</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
         <x:v>81</x:v>
@@ -2273,64 +2279,64 @@
       <x:c r="B31" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C31" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>30000000</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F31" s="0">
+        <x:v>1308500</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>36.4</x:v>
+        <x:v>8.92</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>0</x:v>
+        <x:v>13.09</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>5831653</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F32" s="0">
-        <x:v>304086107</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>8.81</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>52.14</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -2341,66 +2347,66 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>13200000</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>79451200</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>519420697</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>44.48</x:v>
+        <x:v>7.93</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>39.35</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>1973951</x:v>
+        <x:v>13200000</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>3000000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>135510760</x:v>
+        <x:v>519420697</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2.47</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>81.7</x:v>
+        <x:v>43.86</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>68.65</x:v>
+        <x:v>39.35</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2410,131 +2416,131 @@
       <x:c r="B35" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C35" s="0">
+        <x:v>1973951</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>15000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F35" s="0">
+        <x:v>135510760</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>5.49</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0</x:v>
+        <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>40.22</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>0</x:v>
+        <x:v>68.65</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>3337681</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F36" s="0">
-        <x:v>20505183</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.43</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>2.67</x:v>
+        <x:v>40.74</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>6.14</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>3337681</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>9275000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>950000000</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F37" s="0">
+        <x:v>20505183</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>41.58</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>0</x:v>
+        <x:v>6.14</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>1364000</x:v>
+      <x:c r="C38" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>23460000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>9000000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0">
-        <x:v>409075556</x:v>
+        <x:v>950000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>301</x:v>
+        <x:v>42.9</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>299.91</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -2544,163 +2550,163 @@
       <x:c r="B39" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C39" s="0">
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>380000000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="F39" s="0">
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>10</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>20.26</x:v>
+        <x:v>309.75</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>0</x:v>
+        <x:v>299.91</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>507440</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2500000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F40" s="0">
-        <x:v>42117724</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>162.3</x:v>
+        <x:v>21.22</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F41" s="0">
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.63</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>38.32</x:v>
+        <x:v>159.5</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>2000000</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>2000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>81947000</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>43.26</x:v>
+        <x:v>38.26</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>40.97</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="C43" s="0">
-        <x:v>324474</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1781383</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0.08</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>12.31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>5.49</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
         <x:v>109</x:v>
@@ -2708,63 +2714,66 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C44" s="0">
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.57</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D45" s="0">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="E45" s="0">
-        <x:v>7000000</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>8.74</x:v>
+        <x:v>12.91</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2772,413 +2781,413 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C46" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F46" s="0">
-        <x:v>12245700</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>6.39</x:v>
+        <x:v>8.44</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>6.12</x:v>
-      </x:c>
-      <x:c r="K46" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="C47" s="0">
-        <x:v>174500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>694527000</x:v>
+        <x:v>12245700</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>2.99</x:v>
+        <x:v>6.48</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>3.98</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>694527000</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>3.08</x:v>
+      </x:c>
+      <x:c r="J48" s="0">
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>635229</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E48" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F48" s="0">
-        <x:v>11323561</x:v>
-      </x:c>
-      <x:c r="G48" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="0">
-        <x:v>0.33</x:v>
-      </x:c>
-      <x:c r="I48" s="0">
-        <x:v>23.7</x:v>
-      </x:c>
-      <x:c r="J48" s="0">
-        <x:v>17.83</x:v>
-      </x:c>
-      <x:c r="K48" s="0" t="s">
-        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D49" s="0">
-        <x:v>3500000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>4947800</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>27.3</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>38.06</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C50" s="0">
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>5000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>231.2</x:v>
+        <x:v>27.8</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>0</x:v>
+        <x:v>38.06</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>447761</x:v>
+      <x:c r="C51" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>18415143</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>40.22</x:v>
+        <x:v>240.4</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>41.13</x:v>
-      </x:c>
-      <x:c r="K51" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>447761</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>120000000</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>18415143</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>0.86</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>39.76</x:v>
+      </x:c>
+      <x:c r="J52" s="0">
+        <x:v>41.13</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E52" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>4022593</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>12.54</x:v>
-      </x:c>
-      <x:c r="J52" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K52" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>4022593</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>1.71</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>13.79</x:v>
+      </x:c>
+      <x:c r="J53" s="0">
+        <x:v>20.11</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>946718</x:v>
-      </x:c>
-      <x:c r="D53" s="0">
-        <x:v>20000000</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>37333519</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>7.55</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>0.36</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>85.8</x:v>
-      </x:c>
-      <x:c r="J53" s="0">
-        <x:v>39.43</x:v>
-      </x:c>
-      <x:c r="K53" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>946718</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>37333519</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>7.55</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>85.2</x:v>
+      </x:c>
+      <x:c r="J54" s="0">
+        <x:v>39.43</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E54" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F54" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G54" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I54" s="0">
-        <x:v>21.3</x:v>
-      </x:c>
-      <x:c r="J54" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D55" s="0">
-        <x:v>50000000</x:v>
+      <x:c r="C55" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>49736990</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>23.52</x:v>
+        <x:v>21.52</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>16.34</x:v>
-      </x:c>
-      <x:c r="K55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>3043115</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>49736990</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>24.64</x:v>
+      </x:c>
+      <x:c r="J56" s="0">
+        <x:v>16.34</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D56" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E56" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>92635231</x:v>
-      </x:c>
-      <x:c r="G56" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="I56" s="0">
-        <x:v>82.5</x:v>
-      </x:c>
-      <x:c r="J56" s="0">
-        <x:v>38.88</x:v>
-      </x:c>
-      <x:c r="K56" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E57" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F57" s="0">
+        <x:v>92635231</x:v>
+      </x:c>
+      <x:c r="G57" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I57" s="0">
+        <x:v>86.6</x:v>
+      </x:c>
+      <x:c r="J57" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D57" s="0">
-        <x:v>4191000</x:v>
-      </x:c>
-      <x:c r="E57" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G57" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I57" s="0">
-        <x:v>63.3</x:v>
-      </x:c>
-      <x:c r="J57" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -3186,28 +3195,28 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>6950000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>125000000</x:v>
+        <x:v>160000000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G58" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>6.07</x:v>
+        <x:v>63.45</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3215,31 +3224,31 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>1862500</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>75000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G59" s="0">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>38.42</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3250,69 +3259,66 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>310000</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F60" s="0">
-        <x:v>49980500</x:v>
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>8.88</x:v>
+        <x:v>38.92</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>161.23</x:v>
-      </x:c>
-      <x:c r="K60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>2000000</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D61" s="0">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F61" s="0">
-        <x:v>31366572</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G61" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>19.39</x:v>
+        <x:v>8.86</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>15.68</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -3320,34 +3326,34 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>1250000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>25000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>11187500</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G62" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>3.04</x:v>
+        <x:v>19.57</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>8.95</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -3355,101 +3361,104 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>12500000</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>12500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>60000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>61582393</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>5</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.21</x:v>
+        <x:v>3.07</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>4.93</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
       <x:c r="C64" s="0">
-        <x:v>2093944</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>220000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>200139168</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>115.2</x:v>
+        <x:v>2.27</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>95.58</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>2093944</x:v>
+      </x:c>
+      <x:c r="D65" s="0">
+        <x:v>220000000</x:v>
+      </x:c>
+      <x:c r="E65" s="0">
+        <x:v>8500000000</x:v>
+      </x:c>
+      <x:c r="F65" s="0">
+        <x:v>200139168</x:v>
+      </x:c>
+      <x:c r="G65" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I65" s="0">
+        <x:v>117.7</x:v>
+      </x:c>
+      <x:c r="J65" s="0">
+        <x:v>95.58</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D65" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="E65" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F65" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G65" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I65" s="0">
-        <x:v>36.46</x:v>
-      </x:c>
-      <x:c r="J65" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -3457,34 +3466,31 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C66" s="0">
-        <x:v>51245979</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>85000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F66" s="0">
-        <x:v>125342407</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G66" s="0">
-        <x:v>2.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>2.92</x:v>
+        <x:v>38.12</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K66" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -3492,104 +3498,104 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>1584837</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>2500000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>92450176</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>0</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>1.08</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>56.1</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>58.33</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>7999148</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>11000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>168715651</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>19.43</x:v>
+        <x:v>59.2</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>21.09</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>14000000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>10000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>236130680</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>1.17</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>23.28</x:v>
+        <x:v>19.74</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>16.87</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -3597,136 +3603,139 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>1700005</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>95000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>20390731</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G70" s="0">
-        <x:v>10</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>7.65</x:v>
+        <x:v>23.42</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>11.99</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>1700005</x:v>
+      </x:c>
+      <x:c r="D71" s="0">
+        <x:v>95000000</x:v>
+      </x:c>
+      <x:c r="E71" s="0">
+        <x:v>1425000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0">
+        <x:v>20390731</x:v>
+      </x:c>
+      <x:c r="G71" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H71" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I71" s="0">
+        <x:v>7.74</x:v>
+      </x:c>
+      <x:c r="J71" s="0">
+        <x:v>11.99</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="D71" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E71" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0">
-        <x:v>132286928</x:v>
-      </x:c>
-      <x:c r="G71" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="H71" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="I71" s="0">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="J71" s="0">
-        <x:v>22.05</x:v>
-      </x:c>
-      <x:c r="K71" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="D72" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E72" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F72" s="0">
+        <x:v>132286928</x:v>
+      </x:c>
+      <x:c r="G72" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="H72" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="I72" s="0">
+        <x:v>54.7</x:v>
+      </x:c>
+      <x:c r="J72" s="0">
+        <x:v>22.05</x:v>
+      </x:c>
+      <x:c r="K72" s="0" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C72" s="0">
-        <x:v>1675000</x:v>
-      </x:c>
-      <x:c r="D72" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E72" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F72" s="0">
-        <x:v>114158717</x:v>
-      </x:c>
-      <x:c r="G72" s="0">
-        <x:v>7.81</x:v>
-      </x:c>
-      <x:c r="H72" s="0">
-        <x:v>1.45</x:v>
-      </x:c>
-      <x:c r="I72" s="0">
-        <x:v>80.4</x:v>
-      </x:c>
-      <x:c r="J72" s="0">
-        <x:v>68.15</x:v>
-      </x:c>
-      <x:c r="K72" s="0" t="s">
-        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C73" s="0">
+        <x:v>1675000</x:v>
+      </x:c>
+      <x:c r="D73" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E73" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F73" s="0">
+        <x:v>114158717</x:v>
+      </x:c>
+      <x:c r="G73" s="0">
+        <x:v>7.81</x:v>
+      </x:c>
+      <x:c r="H73" s="0">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="I73" s="0">
+        <x:v>81.7</x:v>
+      </x:c>
+      <x:c r="J73" s="0">
+        <x:v>68.15</x:v>
+      </x:c>
+      <x:c r="K73" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D73" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E73" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F73" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G73" s="0">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="H73" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I73" s="0">
-        <x:v>45.16</x:v>
-      </x:c>
-      <x:c r="J73" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -3734,28 +3743,28 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>5</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H74" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>7.3</x:v>
+        <x:v>45.56</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3766,69 +3775,66 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>1000000</x:v>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0">
-        <x:v>19787700</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G75" s="0">
-        <x:v>0.67</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.52</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>19.79</x:v>
-      </x:c>
-      <x:c r="K75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D76" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E76" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F76" s="0">
+        <x:v>19787700</x:v>
+      </x:c>
+      <x:c r="G76" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="H76" s="0">
+        <x:v>0.27</x:v>
+      </x:c>
+      <x:c r="I76" s="0">
+        <x:v>7.58</x:v>
+      </x:c>
+      <x:c r="J76" s="0">
+        <x:v>19.79</x:v>
+      </x:c>
+      <x:c r="K76" s="0" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>98551</x:v>
-      </x:c>
-      <x:c r="D76" s="0">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="E76" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F76" s="0">
-        <x:v>1295684</x:v>
-      </x:c>
-      <x:c r="G76" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="0">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="I76" s="0">
-        <x:v>13.6</x:v>
-      </x:c>
-      <x:c r="J76" s="0">
-        <x:v>13.15</x:v>
-      </x:c>
-      <x:c r="K76" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -3836,69 +3842,69 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>6049315</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>15000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F77" s="0">
-        <x:v>66439559</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>12.36</x:v>
+        <x:v>13.94</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>10.98</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>37225000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E78" s="0">
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>149982056</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>6.89</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.1</x:v>
+        <x:v>12.18</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>4.03</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -3906,241 +3912,244 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>1000000</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>1000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>350000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>284578907</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>0.8</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>0.8</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>245.2</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>284.58</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D80" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E80" s="0">
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F80" s="0">
+        <x:v>284578907</x:v>
+      </x:c>
+      <x:c r="G80" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H80" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I80" s="0">
+        <x:v>246.1</x:v>
+      </x:c>
+      <x:c r="J80" s="0">
+        <x:v>284.58</x:v>
+      </x:c>
+      <x:c r="K80" s="0" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C80" s="0">
-        <x:v>600000</x:v>
-      </x:c>
-      <x:c r="D80" s="0">
-        <x:v>600000</x:v>
-      </x:c>
-      <x:c r="E80" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="F80" s="0">
-        <x:v>22814140</x:v>
-      </x:c>
-      <x:c r="G80" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H80" s="0">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="I80" s="0">
-        <x:v>12.49</x:v>
-      </x:c>
-      <x:c r="J80" s="0">
-        <x:v>38.02</x:v>
-      </x:c>
-      <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C81" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D81" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E81" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F81" s="0">
+        <x:v>22814140</x:v>
+      </x:c>
+      <x:c r="G81" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I81" s="0">
+        <x:v>12.6</x:v>
+      </x:c>
+      <x:c r="J81" s="0">
+        <x:v>38.02</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C81" s="0">
-        <x:v>11703083</x:v>
-      </x:c>
-      <x:c r="D81" s="0">
-        <x:v>16000000</x:v>
-      </x:c>
-      <x:c r="E81" s="0">
-        <x:v>720000000</x:v>
-      </x:c>
-      <x:c r="F81" s="0">
-        <x:v>978644023</x:v>
-      </x:c>
-      <x:c r="G81" s="0">
-        <x:v>10.16</x:v>
-      </x:c>
-      <x:c r="H81" s="0">
-        <x:v>1.67</x:v>
-      </x:c>
-      <x:c r="I81" s="0">
-        <x:v>241.4</x:v>
-      </x:c>
-      <x:c r="J81" s="0">
-        <x:v>83.62</x:v>
-      </x:c>
-      <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>11703083</x:v>
+      </x:c>
+      <x:c r="D82" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="E82" s="0">
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F82" s="0">
+        <x:v>978644023</x:v>
+      </x:c>
+      <x:c r="G82" s="0">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="H82" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="I82" s="0">
+        <x:v>241.3</x:v>
+      </x:c>
+      <x:c r="J82" s="0">
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C82" s="0">
-        <x:v>5100000</x:v>
-      </x:c>
-      <x:c r="D82" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E82" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F82" s="0">
-        <x:v>90022686</x:v>
-      </x:c>
-      <x:c r="G82" s="0">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="H82" s="0">
-        <x:v>4.31</x:v>
-      </x:c>
-      <x:c r="I82" s="0">
-        <x:v>30.46</x:v>
-      </x:c>
-      <x:c r="J82" s="0">
-        <x:v>17.65</x:v>
-      </x:c>
-      <x:c r="K82" s="0" t="s">
-        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>5100000</x:v>
+      </x:c>
+      <x:c r="D83" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E83" s="0">
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F83" s="0">
+        <x:v>90022686</x:v>
+      </x:c>
+      <x:c r="G83" s="0">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="H83" s="0">
+        <x:v>4.31</x:v>
+      </x:c>
+      <x:c r="I83" s="0">
+        <x:v>30.68</x:v>
+      </x:c>
+      <x:c r="J83" s="0">
+        <x:v>17.65</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C83" s="0">
-        <x:v>3228679</x:v>
-      </x:c>
-      <x:c r="D83" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E83" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0">
-        <x:v>51395842</x:v>
-      </x:c>
-      <x:c r="G83" s="0">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="H83" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="I83" s="0">
-        <x:v>14.4</x:v>
-      </x:c>
-      <x:c r="J83" s="0">
-        <x:v>15.92</x:v>
-      </x:c>
-      <x:c r="K83" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
       <x:c r="C84" s="0">
-        <x:v>150000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>6000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>240000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>6145450</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>6.95</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>40.97</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="D85" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E85" s="0">
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0">
+        <x:v>6145450</x:v>
+      </x:c>
+      <x:c r="G85" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I85" s="0">
+        <x:v>7.01</x:v>
+      </x:c>
+      <x:c r="J85" s="0">
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K85" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D85" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E85" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I85" s="0">
-        <x:v>18.08</x:v>
-      </x:c>
-      <x:c r="J85" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -4148,209 +4157,206 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C86" s="0">
-        <x:v>366107</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>1200000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F86" s="0">
-        <x:v>6010300</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>17.2</x:v>
+        <x:v>18.92</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>16.42</x:v>
-      </x:c>
-      <x:c r="K86" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>120000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F87" s="0">
-        <x:v>3830160</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>129</x:v>
+        <x:v>17.12</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>31.92</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="C88" s="0">
-        <x:v>13050000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>13050000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>94.65</x:v>
+        <x:v>131.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>94.36</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="D89" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="E89" s="0">
+        <x:v>1305000000</x:v>
+      </x:c>
+      <x:c r="F89" s="0">
+        <x:v>1231340857</x:v>
+      </x:c>
+      <x:c r="G89" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H89" s="0">
+        <x:v>3.13</x:v>
+      </x:c>
+      <x:c r="I89" s="0">
+        <x:v>100.3</x:v>
+      </x:c>
+      <x:c r="J89" s="0">
+        <x:v>94.36</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>23682251</x:v>
-      </x:c>
-      <x:c r="D89" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E89" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F89" s="0">
-        <x:v>107041261</x:v>
-      </x:c>
-      <x:c r="G89" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H89" s="0">
-        <x:v>2.37</x:v>
-      </x:c>
-      <x:c r="I89" s="0">
-        <x:v>5.47</x:v>
-      </x:c>
-      <x:c r="J89" s="0">
-        <x:v>4.52</x:v>
-      </x:c>
-      <x:c r="K89" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>1000000</x:v>
+        <x:v>23682251</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>4000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>429817200</x:v>
+        <x:v>107041261</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0.17</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>747</x:v>
+        <x:v>5.86</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>429.82</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>300000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>60000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>171000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>791000</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>4.09</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>2.64</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -4358,34 +4364,34 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>2175097</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>15000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>175000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>17901652</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>15.82</x:v>
+        <x:v>4.07</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>8.23</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -4393,31 +4399,34 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F93" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F93" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>3.25</x:v>
+        <x:v>17.4</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K93" s="0" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -4425,168 +4434,165 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>43000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>200000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="F94" s="0">
-        <x:v>1024885</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>31.02</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>23.83</x:v>
-      </x:c>
-      <x:c r="K94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C95" s="0">
+        <x:v>43000</x:v>
+      </x:c>
+      <x:c r="D95" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="E95" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="F95" s="0">
+        <x:v>1024885</x:v>
+      </x:c>
+      <x:c r="G95" s="0">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H95" s="0">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I95" s="0">
+        <x:v>34.12</x:v>
+      </x:c>
+      <x:c r="J95" s="0">
+        <x:v>23.83</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C95" s="0">
-        <x:v>9937037</x:v>
-      </x:c>
-      <x:c r="D95" s="0">
-        <x:v>11000000</x:v>
-      </x:c>
-      <x:c r="E95" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F95" s="0">
-        <x:v>50001023</x:v>
-      </x:c>
-      <x:c r="G95" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H95" s="0">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="I95" s="0">
-        <x:v>3.68</x:v>
-      </x:c>
-      <x:c r="J95" s="0">
-        <x:v>5.03</x:v>
-      </x:c>
-      <x:c r="K95" s="0" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>9937037</x:v>
+      </x:c>
+      <x:c r="D96" s="0">
+        <x:v>11000000</x:v>
+      </x:c>
+      <x:c r="E96" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0">
+        <x:v>50001023</x:v>
+      </x:c>
+      <x:c r="G96" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I96" s="0">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="J96" s="0">
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D96" s="0">
-        <x:v>5500000</x:v>
-      </x:c>
-      <x:c r="E96" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G96" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H96" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I96" s="0">
-        <x:v>42.48</x:v>
-      </x:c>
-      <x:c r="J96" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>13064888</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>30000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0">
-        <x:v>268254173</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>27.86</x:v>
+        <x:v>40.26</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>20.53</x:v>
-      </x:c>
-      <x:c r="K97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>111673026</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>500000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>500005947</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>9.01</x:v>
+        <x:v>27.94</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>4.48</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
         <x:v>199</x:v>
@@ -4594,34 +4600,37 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C99" s="0">
+        <x:v>111673026</x:v>
+      </x:c>
+      <x:c r="D99" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="E99" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F99" s="0">
+        <x:v>500005947</x:v>
+      </x:c>
+      <x:c r="G99" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="0">
+        <x:v>1.24</x:v>
+      </x:c>
+      <x:c r="I99" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J99" s="0">
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E99" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F99" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G99" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H99" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I99" s="0">
-        <x:v>4.63</x:v>
-      </x:c>
-      <x:c r="J99" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -4629,28 +4638,28 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D100" s="0">
-        <x:v>19600000</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>92000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>8.5</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4661,171 +4670,171 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C101" s="0">
-        <x:v>1100000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>2000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F101" s="0">
-        <x:v>56064346</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>124.4</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K101" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>5267479</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>11160000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>125000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>52505825</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>4.72</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>12.57</x:v>
+        <x:v>123.5</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>9.97</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>1460000</x:v>
+        <x:v>5267479</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>2160000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>35000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>55050600</x:v>
+        <x:v>52505825</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0.84</x:v>
+        <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>43.26</x:v>
+        <x:v>12.91</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>37.71</x:v>
+        <x:v>9.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C104" s="0">
+        <x:v>1460000</x:v>
+      </x:c>
+      <x:c r="D104" s="0">
+        <x:v>2160000</x:v>
+      </x:c>
+      <x:c r="E104" s="0">
+        <x:v>35000000</x:v>
+      </x:c>
+      <x:c r="F104" s="0">
+        <x:v>55050600</x:v>
+      </x:c>
+      <x:c r="G104" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="0">
+        <x:v>0.84</x:v>
+      </x:c>
+      <x:c r="I104" s="0">
+        <x:v>42.64</x:v>
+      </x:c>
+      <x:c r="J104" s="0">
+        <x:v>37.71</x:v>
+      </x:c>
+      <x:c r="K104" s="0" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C104" s="0">
-        <x:v>1989802</x:v>
-      </x:c>
-      <x:c r="D104" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E104" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F104" s="0">
-        <x:v>78711752</x:v>
-      </x:c>
-      <x:c r="G104" s="0">
-        <x:v>2.94</x:v>
-      </x:c>
-      <x:c r="H104" s="0">
-        <x:v>1.17</x:v>
-      </x:c>
-      <x:c r="I104" s="0">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J104" s="0">
-        <x:v>39.56</x:v>
-      </x:c>
-      <x:c r="K104" s="0" t="s">
-        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>1989802</x:v>
+      </x:c>
+      <x:c r="D105" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E105" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0">
+        <x:v>78711752</x:v>
+      </x:c>
+      <x:c r="G105" s="0">
+        <x:v>2.94</x:v>
+      </x:c>
+      <x:c r="H105" s="0">
+        <x:v>1.17</x:v>
+      </x:c>
+      <x:c r="I105" s="0">
+        <x:v>108.1</x:v>
+      </x:c>
+      <x:c r="J105" s="0">
+        <x:v>39.56</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D105" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E105" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F105" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G105" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H105" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I105" s="0">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="J105" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -4833,34 +4842,31 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>300000</x:v>
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>67500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>326000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0">
-        <x:v>1369300</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>11.47</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>4.56</x:v>
-      </x:c>
-      <x:c r="K106" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -4868,34 +4874,34 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>8291656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>11000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>200000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>126004459</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>16.18</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>15.2</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -4903,328 +4909,331 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>76908759</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>250000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0.78</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>30.86</x:v>
+        <x:v>16.63</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>25.74</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C109" s="0">
+        <x:v>76908759</x:v>
+      </x:c>
+      <x:c r="D109" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="E109" s="0">
+        <x:v>12000000000</x:v>
+      </x:c>
+      <x:c r="F109" s="0">
+        <x:v>1979731803</x:v>
+      </x:c>
+      <x:c r="G109" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H109" s="0">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I109" s="0">
+        <x:v>31.46</x:v>
+      </x:c>
+      <x:c r="J109" s="0">
+        <x:v>25.74</x:v>
+      </x:c>
+      <x:c r="K109" s="0" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="C109" s="0">
-        <x:v>2975773</x:v>
-      </x:c>
-      <x:c r="D109" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E109" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F109" s="0">
-        <x:v>44771095</x:v>
-      </x:c>
-      <x:c r="G109" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H109" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="I109" s="0">
-        <x:v>26.58</x:v>
-      </x:c>
-      <x:c r="J109" s="0">
-        <x:v>15.05</x:v>
-      </x:c>
-      <x:c r="K109" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
       <x:c r="C110" s="0">
-        <x:v>10994323</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>21600000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>183002238</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>15.19</x:v>
+        <x:v>27.72</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>16.65</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>26626543</x:v>
+        <x:v>10994323</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>195000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>256460787</x:v>
+        <x:v>183002238</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1.37</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.49</x:v>
+        <x:v>15.42</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>9.63</x:v>
+        <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="C112" s="0">
-        <x:v>5100000</x:v>
+        <x:v>26626543</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>20000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>700000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>155318227</x:v>
+        <x:v>256460787</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>6.81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0.93</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>59.8</x:v>
+        <x:v>15.61</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>30.45</x:v>
+        <x:v>9.63</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>300000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
         <x:v>700000000</x:v>
       </x:c>
-      <x:c r="F113" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="F113" s="0">
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>0</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>2.52</x:v>
+        <x:v>60.4</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>0</x:v>
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="C114" s="0">
-        <x:v>5000000</x:v>
+      <x:c r="C114" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>5000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F114" s="0">
-        <x:v>39090077</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>9.04</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="K114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="D115" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E115" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0">
+        <x:v>39090077</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="0">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I115" s="0">
+        <x:v>9.4</x:v>
+      </x:c>
+      <x:c r="J115" s="0">
+        <x:v>7.82</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="C115" s="0">
-        <x:v>590777</x:v>
-      </x:c>
-      <x:c r="D115" s="0">
-        <x:v>21000000</x:v>
-      </x:c>
-      <x:c r="E115" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0">
-        <x:v>12439782</x:v>
-      </x:c>
-      <x:c r="G115" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H115" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="I115" s="0">
-        <x:v>17.3</x:v>
-      </x:c>
-      <x:c r="J115" s="0">
-        <x:v>21.06</x:v>
-      </x:c>
-      <x:c r="K115" s="0" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C116" s="0">
+        <x:v>590777</x:v>
+      </x:c>
+      <x:c r="D116" s="0">
+        <x:v>21000000</x:v>
+      </x:c>
+      <x:c r="E116" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F116" s="0">
+        <x:v>12439782</x:v>
+      </x:c>
+      <x:c r="G116" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H116" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I116" s="0">
+        <x:v>17.53</x:v>
+      </x:c>
+      <x:c r="J116" s="0">
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K116" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D116" s="0">
-        <x:v>11700000</x:v>
-      </x:c>
-      <x:c r="E116" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F116" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G116" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H116" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I116" s="0">
-        <x:v>83.75</x:v>
-      </x:c>
-      <x:c r="J116" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>231</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>270000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
@@ -5233,7 +5242,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>510</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5241,174 +5250,171 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C118" s="0">
-        <x:v>53584</x:v>
+      <x:c r="C118" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>640000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0">
-        <x:v>8271098</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>236.3</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>154.36</x:v>
-      </x:c>
-      <x:c r="K118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>235</x:v>
-      </x:c>
       <x:c r="C119" s="0">
-        <x:v>7550000</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>500000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F119" s="0">
-        <x:v>111777791</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>12.4</x:v>
+        <x:v>245.7</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>14.81</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C120" s="0">
+        <x:v>7550000</x:v>
+      </x:c>
+      <x:c r="D120" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="E120" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F120" s="0">
+        <x:v>111777791</x:v>
+      </x:c>
+      <x:c r="G120" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H120" s="0">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="I120" s="0">
+        <x:v>12.55</x:v>
+      </x:c>
+      <x:c r="J120" s="0">
+        <x:v>14.81</x:v>
+      </x:c>
+      <x:c r="K120" s="0" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="C120" s="0">
-        <x:v>2097716</x:v>
-      </x:c>
-      <x:c r="D120" s="0">
-        <x:v>10112561</x:v>
-      </x:c>
-      <x:c r="E120" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F120" s="0">
-        <x:v>28985167</x:v>
-      </x:c>
-      <x:c r="G120" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H120" s="0">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="I120" s="0">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="J120" s="0">
-        <x:v>13.82</x:v>
-      </x:c>
-      <x:c r="K120" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="C121" s="0">
-        <x:v>5185302</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>57000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>513000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>37061183</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G121" s="0">
-        <x:v>5.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>5.5</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>7.15</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>242</x:v>
-      </x:c>
       <x:c r="C122" s="0">
-        <x:v>669111</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>1000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>260000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>151220429</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>566</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>226</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
         <x:v>199</x:v>
@@ -5416,229 +5422,229 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>38840</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D123" s="0">
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>270000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>9431791</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>510</x:v>
+        <x:v>574.5</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>242.84</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>243</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>2250000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>300000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>31750000</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>12.4</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>14.11</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>2250000</x:v>
+      </x:c>
+      <x:c r="D125" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E125" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F125" s="0">
+        <x:v>31750000</x:v>
+      </x:c>
+      <x:c r="G125" s="0">
+        <x:v>4.98</x:v>
+      </x:c>
+      <x:c r="H125" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I125" s="0">
+        <x:v>12.55</x:v>
+      </x:c>
+      <x:c r="J125" s="0">
+        <x:v>14.11</x:v>
+      </x:c>
+      <x:c r="K125" s="0" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>1500000</x:v>
-      </x:c>
-      <x:c r="D125" s="0">
-        <x:v>10112561</x:v>
-      </x:c>
-      <x:c r="E125" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F125" s="0">
-        <x:v>21870885</x:v>
-      </x:c>
-      <x:c r="G125" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H125" s="0">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="I125" s="0">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="J125" s="0">
-        <x:v>14.58</x:v>
-      </x:c>
-      <x:c r="K125" s="0" t="s">
-        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>247</x:v>
-      </x:c>
       <x:c r="C126" s="0">
-        <x:v>281228</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>8299326</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>600000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F126" s="0">
-        <x:v>38021885</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>153.1</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>135.2</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="C127" s="0">
+        <x:v>281228</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>2500000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0">
+        <x:v>38021885</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>162.3</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>0</x:v>
+        <x:v>135.2</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C128" s="0">
-        <x:v>845945</x:v>
+      <x:c r="C128" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F128" s="0">
-        <x:v>10058606</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.67</x:v>
+        <x:v>159.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>11.89</x:v>
-      </x:c>
-      <x:c r="K128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>21446</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>1000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F129" s="0">
-        <x:v>2015907</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>0</x:v>
@@ -5647,538 +5653,573 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>58</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>94</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>254</x:v>
-      </x:c>
       <x:c r="C130" s="0">
-        <x:v>850000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>4250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>40000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F130" s="0">
-        <x:v>6548328</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>1</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>8.1</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>7.7</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>256</x:v>
-      </x:c>
       <x:c r="C131" s="0">
-        <x:v>15000000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>300000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>600000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>23990000</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G131" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3</x:v>
+        <x:v>8.91</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>1.6</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C132" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="D132" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="E132" s="0">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F132" s="0">
+        <x:v>23990000</x:v>
+      </x:c>
+      <x:c r="G132" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H132" s="0">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="I132" s="0">
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="J132" s="0">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="K132" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="C132" s="0">
-        <x:v>6397124</x:v>
-      </x:c>
-      <x:c r="D132" s="0">
-        <x:v>35300000</x:v>
-      </x:c>
-      <x:c r="E132" s="0">
-        <x:v>1046645000</x:v>
-      </x:c>
-      <x:c r="F132" s="0">
-        <x:v>122892213</x:v>
-      </x:c>
-      <x:c r="G132" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H132" s="0">
-        <x:v>0.21</x:v>
-      </x:c>
-      <x:c r="I132" s="0">
-        <x:v>4.76</x:v>
-      </x:c>
-      <x:c r="J132" s="0">
-        <x:v>19.21</x:v>
-      </x:c>
-      <x:c r="K132" s="0" t="s">
-        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C133" s="0">
+        <x:v>6397124</x:v>
+      </x:c>
+      <x:c r="D133" s="0">
+        <x:v>35300000</x:v>
+      </x:c>
+      <x:c r="E133" s="0">
+        <x:v>1046645000</x:v>
+      </x:c>
+      <x:c r="F133" s="0">
+        <x:v>122892213</x:v>
+      </x:c>
+      <x:c r="G133" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H133" s="0">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I133" s="0">
+        <x:v>5.12</x:v>
+      </x:c>
+      <x:c r="J133" s="0">
+        <x:v>19.21</x:v>
+      </x:c>
+      <x:c r="K133" s="0" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="C133" s="0">
-        <x:v>8578668</x:v>
-      </x:c>
-      <x:c r="D133" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E133" s="0">
-        <x:v>525000000</x:v>
-      </x:c>
-      <x:c r="F133" s="0">
-        <x:v>184312813</x:v>
-      </x:c>
-      <x:c r="G133" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H133" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="I133" s="0">
-        <x:v>21.38</x:v>
-      </x:c>
-      <x:c r="J133" s="0">
-        <x:v>21.49</x:v>
-      </x:c>
-      <x:c r="K133" s="0" t="s">
-        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>8578668</x:v>
+      </x:c>
+      <x:c r="D134" s="0">
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E134" s="0">
+        <x:v>525000000</x:v>
+      </x:c>
+      <x:c r="F134" s="0">
+        <x:v>184312813</x:v>
+      </x:c>
+      <x:c r="G134" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H134" s="0">
+        <x:v>2.45</x:v>
+      </x:c>
+      <x:c r="I134" s="0">
+        <x:v>21.94</x:v>
+      </x:c>
+      <x:c r="J134" s="0">
+        <x:v>21.49</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C134" s="0">
-        <x:v>9350000</x:v>
-      </x:c>
-      <x:c r="D134" s="0">
-        <x:v>14710247</x:v>
-      </x:c>
-      <x:c r="E134" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F134" s="0">
-        <x:v>69547091</x:v>
-      </x:c>
-      <x:c r="G134" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H134" s="0">
-        <x:v>3.18</x:v>
-      </x:c>
-      <x:c r="I134" s="0">
-        <x:v>9.19</x:v>
-      </x:c>
-      <x:c r="J134" s="0">
-        <x:v>7.44</x:v>
-      </x:c>
-      <x:c r="K134" s="0" t="s">
-        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C135" s="0">
+        <x:v>9350000</x:v>
+      </x:c>
+      <x:c r="D135" s="0">
+        <x:v>14710247</x:v>
+      </x:c>
+      <x:c r="E135" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F135" s="0">
+        <x:v>69547091</x:v>
+      </x:c>
+      <x:c r="G135" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H135" s="0">
+        <x:v>3.18</x:v>
+      </x:c>
+      <x:c r="I135" s="0">
+        <x:v>9.44</x:v>
+      </x:c>
+      <x:c r="J135" s="0">
+        <x:v>7.44</x:v>
+      </x:c>
+      <x:c r="K135" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="C135" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E135" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F135" s="0">
-        <x:v>75911475</x:v>
-      </x:c>
-      <x:c r="G135" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H135" s="0">
-        <x:v>1.84</x:v>
-      </x:c>
-      <x:c r="I135" s="0">
-        <x:v>81.7</x:v>
-      </x:c>
-      <x:c r="J135" s="0">
-        <x:v>51.7</x:v>
-      </x:c>
-      <x:c r="K135" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C136" s="0">
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E136" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F136" s="0">
+        <x:v>75911475</x:v>
+      </x:c>
+      <x:c r="G136" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H136" s="0">
+        <x:v>1.84</x:v>
+      </x:c>
+      <x:c r="I136" s="0">
+        <x:v>83.6</x:v>
+      </x:c>
+      <x:c r="J136" s="0">
+        <x:v>51.7</x:v>
+      </x:c>
+      <x:c r="K136" s="0" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="C136" s="0">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="D136" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E136" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F136" s="0">
-        <x:v>13401783</x:v>
-      </x:c>
-      <x:c r="G136" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H136" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="I136" s="0">
-        <x:v>2.63</x:v>
-      </x:c>
-      <x:c r="J136" s="0">
-        <x:v>26.8</x:v>
-      </x:c>
-      <x:c r="K136" s="0" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>270</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>725000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F137" s="0">
-        <x:v>48539975</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>41.58</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>66.95</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C138" s="0">
+        <x:v>725000</x:v>
+      </x:c>
+      <x:c r="D138" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E138" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0">
+        <x:v>48539975</x:v>
+      </x:c>
+      <x:c r="G138" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H138" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I138" s="0">
+        <x:v>42.9</x:v>
+      </x:c>
+      <x:c r="J138" s="0">
+        <x:v>66.95</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="C138" s="0">
-        <x:v>1060056</x:v>
-      </x:c>
-      <x:c r="D138" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="E138" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0">
-        <x:v>60762934</x:v>
-      </x:c>
-      <x:c r="G138" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H138" s="0">
-        <x:v>0.44</x:v>
-      </x:c>
-      <x:c r="I138" s="0">
-        <x:v>231.2</x:v>
-      </x:c>
-      <x:c r="J138" s="0">
-        <x:v>57.32</x:v>
-      </x:c>
-      <x:c r="K138" s="0" t="s">
-        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D139" s="0">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="E139" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F139" s="0">
+        <x:v>60762934</x:v>
+      </x:c>
+      <x:c r="G139" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H139" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I139" s="0">
+        <x:v>240.4</x:v>
+      </x:c>
+      <x:c r="J139" s="0">
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K139" s="0" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="C139" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E139" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F139" s="0">
-        <x:v>565141750</x:v>
-      </x:c>
-      <x:c r="G139" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H139" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="I139" s="0">
-        <x:v>2.99</x:v>
-      </x:c>
-      <x:c r="J139" s="0">
-        <x:v>4.26</x:v>
-      </x:c>
-      <x:c r="K139" s="0" t="s">
-        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>276</x:v>
-      </x:c>
       <x:c r="C140" s="0">
-        <x:v>373000</x:v>
-      </x:c>
-      <x:c r="D140" s="0">
-        <x:v>1000000</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>75000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>23786370</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>8.36</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>63.77</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C141" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D141" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E141" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F141" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G141" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H141" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I141" s="0">
+        <x:v>8.41</x:v>
+      </x:c>
+      <x:c r="J141" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K141" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="C141" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="D141" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E141" s="0">
-        <x:v>140000000</x:v>
-      </x:c>
-      <x:c r="F141" s="0">
-        <x:v>133271568</x:v>
-      </x:c>
-      <x:c r="G141" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H141" s="0">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="I141" s="0">
-        <x:v>6.23</x:v>
-      </x:c>
-      <x:c r="J141" s="0">
-        <x:v>13.33</x:v>
-      </x:c>
-      <x:c r="K141" s="0" t="s">
-        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C142" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D142" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E142" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F142" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G142" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H142" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I142" s="0">
+        <x:v>6.85</x:v>
+      </x:c>
+      <x:c r="J142" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K142" s="0" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="C142" s="0">
-        <x:v>3081843</x:v>
-      </x:c>
-      <x:c r="D142" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E142" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F142" s="0">
-        <x:v>43986444</x:v>
-      </x:c>
-      <x:c r="G142" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H142" s="0">
-        <x:v>0.66</x:v>
-      </x:c>
-      <x:c r="I142" s="0">
-        <x:v>6.94</x:v>
-      </x:c>
-      <x:c r="J142" s="0">
-        <x:v>14.27</x:v>
-      </x:c>
-      <x:c r="K142" s="0" t="s">
-        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
       <x:c r="C143" s="0">
-        <x:v>1348769</x:v>
+        <x:v>3081843</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>1500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>105000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>224239713</x:v>
+        <x:v>43986444</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>0.41</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>382</x:v>
+        <x:v>6.88</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>166.26</x:v>
+        <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C144" s="0">
+        <x:v>1348769</x:v>
+      </x:c>
+      <x:c r="D144" s="0">
+        <x:v>1500000</x:v>
+      </x:c>
+      <x:c r="E144" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="F144" s="0">
+        <x:v>224239713</x:v>
+      </x:c>
+      <x:c r="G144" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H144" s="0">
+        <x:v>0.41</x:v>
+      </x:c>
+      <x:c r="I144" s="0">
+        <x:v>371.25</x:v>
+      </x:c>
+      <x:c r="J144" s="0">
+        <x:v>166.26</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="B144" s="0" t="s">
+    </x:row>
+    <x:row r="145" spans="1:11">
+      <x:c r="A145" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C144" s="0">
+      <x:c r="B145" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C145" s="0">
         <x:v>927506</x:v>
       </x:c>
-      <x:c r="D144" s="0">
+      <x:c r="D145" s="0">
         <x:v>1488672430</x:v>
       </x:c>
-      <x:c r="E144" s="0">
+      <x:c r="E145" s="0">
         <x:v>411000000</x:v>
       </x:c>
-      <x:c r="F144" s="0">
+      <x:c r="F145" s="0">
         <x:v>19370508</x:v>
       </x:c>
-      <x:c r="G144" s="0">
+      <x:c r="G145" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H144" s="0">
+      <x:c r="H145" s="0">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="I144" s="0">
-        <x:v>19.59</x:v>
-      </x:c>
-      <x:c r="J144" s="0">
+      <x:c r="I145" s="0">
+        <x:v>20.28</x:v>
+      </x:c>
+      <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
-      <x:c r="K144" s="0" t="s">
-        <x:v>288</x:v>
+      <x:c r="K145" s="0" t="s">
+        <x:v>289</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,6 +130,9 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKFA</x:t>
   </x:si>
   <x:si>
@@ -631,49 +634,52 @@
     <x:t>BLUME</x:t>
   </x:si>
   <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.03.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.03.2025</x:t>
   </x:si>
   <x:si>
     <x:t>ADGYO</x:t>
@@ -1298,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>12.49</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1333,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>19.74</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1368,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.77</x:v>
+        <x:v>8.92</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1400,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.62</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1435,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>131.5</x:v>
+        <x:v>131.7</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1467,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.1</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1502,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>28.5</x:v>
+        <x:v>29.06</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1537,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>16.39</x:v>
+        <x:v>16.77</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1572,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>6.11</x:v>
+        <x:v>6.16</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1604,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.62</x:v>
+        <x:v>22.44</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1621,7 +1627,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>18620446</x:v>
+        <x:v>18820446</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1630,7 +1636,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>467253782</x:v>
+        <x:v>472925782</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
@@ -1639,21 +1645,21 @@
         <x:v>0.72</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>27.94</x:v>
+        <x:v>27.98</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.09</x:v>
+        <x:v>25.13</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>7024156</x:v>
@@ -1674,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>13.7</x:v>
+        <x:v>14.29</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1685,10 +1691,10 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>3500000</x:v>
@@ -1709,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>43.54</x:v>
+        <x:v>47.88</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1720,10 +1726,10 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>3753472</x:v>
@@ -1744,21 +1750,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>58.9</x:v>
+        <x:v>60.5</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>3189049</x:v>
@@ -1779,21 +1785,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7.46</x:v>
+        <x:v>7.58</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>18</x:v>
@@ -1814,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.49</x:v>
+        <x:v>6.45</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1822,10 +1828,10 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>950000</x:v>
@@ -1846,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>108.1</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1857,10 +1863,10 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>6248196</x:v>
@@ -1881,21 +1887,21 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>7.4</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>236122</x:v>
@@ -1916,21 +1922,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>82.4</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>1000000</x:v>
@@ -1951,21 +1957,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>21.94</x:v>
+        <x:v>22.16</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>18</x:v>
@@ -1986,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7.46</x:v>
+        <x:v>7.58</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -1994,10 +2000,10 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>87187201</x:v>
@@ -2018,21 +2024,21 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>16445115</x:v>
@@ -2053,21 +2059,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>55.7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1110000</x:v>
@@ -2088,13 +2094,13 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>781</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -2102,7 +2108,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>24398659</x:v>
@@ -2123,21 +2129,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>27.94</x:v>
+        <x:v>27.98</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>46563878</x:v>
@@ -2158,21 +2164,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>226257</x:v>
@@ -2193,21 +2199,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.38</x:v>
+        <x:v>7.28</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1969635</x:v>
@@ -2228,21 +2234,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>24.08</x:v>
+        <x:v>25.38</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>1000000</x:v>
@@ -2263,21 +2269,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100000</x:v>
@@ -2298,21 +2304,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.92</x:v>
+        <x:v>9.1</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>18</x:v>
@@ -2333,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>38.88</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2341,10 +2347,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>5831653</x:v>
@@ -2365,21 +2371,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>7.93</x:v>
+        <x:v>7.14</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>13200000</x:v>
@@ -2400,21 +2406,21 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>43.86</x:v>
+        <x:v>45.66</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.35</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>1973951</x:v>
@@ -2435,21 +2441,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>83.6</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>18</x:v>
@@ -2470,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>40.74</x:v>
+        <x:v>41.52</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2478,10 +2484,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>3337681</x:v>
@@ -2502,21 +2508,21 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>18</x:v>
@@ -2537,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>42.9</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2545,10 +2551,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>1364000</x:v>
@@ -2569,21 +2575,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>309.75</x:v>
+        <x:v>312.5</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>18</x:v>
@@ -2604,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.22</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2612,10 +2618,10 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>507440</x:v>
@@ -2636,21 +2642,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>159.5</x:v>
+        <x:v>163.8</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>18</x:v>
@@ -2671,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>38.26</x:v>
+        <x:v>39.2</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2679,10 +2685,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>2000000</x:v>
@@ -2703,13 +2709,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44</x:v>
+        <x:v>44.2</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2717,7 +2723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>324474</x:v>
@@ -2738,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.49</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2749,10 +2755,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>18</x:v>
@@ -2773,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>12.91</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2781,10 +2787,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>18</x:v>
@@ -2805,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.44</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2813,10 +2819,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>2000000</x:v>
@@ -2837,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.48</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2848,10 +2854,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>174500000</x:v>
@@ -2872,21 +2878,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.33</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>635229</x:v>
@@ -2907,21 +2913,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>24.08</x:v>
+        <x:v>25.38</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>130000</x:v>
@@ -2942,21 +2948,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>27.8</x:v>
+        <x:v>29.24</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -2977,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>240.4</x:v>
+        <x:v>240.5</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -2985,10 +2991,10 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>447761</x:v>
@@ -3009,21 +3015,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>39.76</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>200000</x:v>
@@ -3044,21 +3050,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>13.79</x:v>
+        <x:v>12.42</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>946718</x:v>
@@ -3079,21 +3085,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>85.2</x:v>
+        <x:v>86.05</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>18</x:v>
@@ -3114,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.52</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3122,10 +3128,10 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>3043115</x:v>
@@ -3146,21 +3152,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>24.64</x:v>
+        <x:v>24.48</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2382736</x:v>
@@ -3181,21 +3187,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>86.6</x:v>
+        <x:v>87.5</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>18</x:v>
@@ -3216,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>63.45</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3224,10 +3230,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>18</x:v>
@@ -3248,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.3</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3256,10 +3262,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>18</x:v>
@@ -3280,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>38.92</x:v>
+        <x:v>40.12</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3288,10 +3294,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>310000</x:v>
@@ -3312,21 +3318,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.86</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>2000000</x:v>
@@ -3347,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>19.57</x:v>
+        <x:v>19.89</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3358,10 +3364,10 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>1250000</x:v>
@@ -3382,21 +3388,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.07</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>12500000</x:v>
@@ -3417,21 +3423,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.27</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>2093944</x:v>
@@ -3452,21 +3458,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>117.7</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>18</x:v>
@@ -3487,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>38.12</x:v>
+        <x:v>40.32</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3495,10 +3501,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>51245979</x:v>
@@ -3519,21 +3525,21 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>3.01</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1584837</x:v>
@@ -3554,13 +3560,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>59.2</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3568,7 +3574,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>7999148</x:v>
@@ -3589,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>19.74</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3600,10 +3606,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>14000000</x:v>
@@ -3624,21 +3630,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>23.42</x:v>
+        <x:v>23.28</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>1700005</x:v>
@@ -3659,21 +3665,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>6000000</x:v>
@@ -3694,21 +3700,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>54.7</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>1675000</x:v>
@@ -3729,21 +3735,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>81.7</x:v>
+        <x:v>80.25</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>18</x:v>
@@ -3764,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>45.56</x:v>
+        <x:v>46.68</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3772,10 +3778,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>18</x:v>
@@ -3796,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.5</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3804,10 +3810,10 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1000000</x:v>
@@ -3828,21 +3834,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.58</x:v>
+        <x:v>7.79</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>98551</x:v>
@@ -3863,21 +3869,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.94</x:v>
+        <x:v>14.33</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>6049315</x:v>
@@ -3898,21 +3904,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.18</x:v>
+        <x:v>12.46</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>37225000</x:v>
@@ -3933,21 +3939,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.09</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1000000</x:v>
@@ -3968,21 +3974,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>246.1</x:v>
+        <x:v>250.5</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>600000</x:v>
@@ -4003,21 +4009,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.6</x:v>
+        <x:v>12.68</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>11703083</x:v>
@@ -4038,21 +4044,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>241.3</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4073,21 +4079,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>30.68</x:v>
+        <x:v>32.48</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>3228679</x:v>
@@ -4108,21 +4114,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.58</x:v>
+        <x:v>14.91</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>150000</x:v>
@@ -4143,21 +4149,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.01</x:v>
+        <x:v>7.14</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>18</x:v>
@@ -4178,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.92</x:v>
+        <x:v>18.69</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4186,10 +4192,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>366107</x:v>
@@ -4210,13 +4216,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.12</x:v>
+        <x:v>17.66</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -4224,7 +4230,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>120000</x:v>
@@ -4245,21 +4251,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>131.5</x:v>
+        <x:v>131.7</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>13050000</x:v>
@@ -4280,21 +4286,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>100.3</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>23682251</x:v>
@@ -4315,7 +4321,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.86</x:v>
+        <x:v>5.62</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.52</x:v>
@@ -4326,10 +4332,10 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>1000000</x:v>
@@ -4350,21 +4356,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>781</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>300000</x:v>
@@ -4385,21 +4391,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>4.07</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>2175097</x:v>
@@ -4420,21 +4426,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>17.4</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>18</x:v>
@@ -4455,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4463,10 +4469,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>43000</x:v>
@@ -4487,21 +4493,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>34.12</x:v>
+        <x:v>32.94</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>9937037</x:v>
@@ -4522,21 +4528,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>3.79</x:v>
+        <x:v>3.87</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
@@ -4557,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>40.26</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4568,7 +4574,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>13064888</x:v>
@@ -4589,21 +4595,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>27.94</x:v>
+        <x:v>27.98</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>111673026</x:v>
@@ -4624,21 +4630,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>9</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4659,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.89</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4667,10 +4673,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
@@ -4691,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>9.3</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4699,10 +4705,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>1100000</x:v>
@@ -4723,21 +4729,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>123.5</x:v>
+        <x:v>122.6</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>5267479</x:v>
@@ -4758,24 +4764,24 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>12.91</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>1460000</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D104" s="0">
         <x:v>2160000</x:v>
@@ -4784,30 +4790,30 @@
         <x:v>35000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>55050600</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>42.64</x:v>
+        <x:v>42.92</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>37.71</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1989802</x:v>
@@ -4828,21 +4834,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>108.1</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>18</x:v>
@@ -4863,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>509</x:v>
+        <x:v>512.5</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4871,10 +4877,10 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>300000</x:v>
@@ -4895,21 +4901,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.5</x:v>
+        <x:v>11.51</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>8291656</x:v>
@@ -4930,21 +4936,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>16.63</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>76908759</x:v>
@@ -4965,21 +4971,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>31.46</x:v>
+        <x:v>32.06</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5000,21 +5006,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>27.72</x:v>
+        <x:v>28.12</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5035,21 +5041,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.42</x:v>
+        <x:v>16.15</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>26626543</x:v>
@@ -5070,21 +5076,21 @@
         <x:v>1.37</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>15.61</x:v>
+        <x:v>15.99</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>9.63</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5105,21 +5111,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>60.4</x:v>
+        <x:v>62.3</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5140,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.55</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5148,10 +5154,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5172,21 +5178,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.4</x:v>
+        <x:v>9.78</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5207,21 +5213,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>17.53</x:v>
+        <x:v>17.79</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5242,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>87</x:v>
+        <x:v>88.35</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5250,10 +5256,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5274,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>509</x:v>
+        <x:v>512.5</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5282,10 +5288,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5306,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>245.7</x:v>
+        <x:v>248.9</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5317,10 +5323,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5341,21 +5347,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>12.55</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5376,21 +5382,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.35</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5411,21 +5417,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.68</x:v>
+        <x:v>5.73</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5446,21 +5452,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>574.5</x:v>
+        <x:v>572.5</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5481,21 +5487,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>509</x:v>
+        <x:v>512.5</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5516,21 +5522,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>12.55</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5551,21 +5557,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.35</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>281228</x:v>
@@ -5586,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>155</x:v>
+        <x:v>155.9</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5597,10 +5603,10 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5621,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>159.5</x:v>
+        <x:v>163.8</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5629,10 +5635,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5653,21 +5659,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5688,21 +5694,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>60</x:v>
+        <x:v>60.45</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5723,21 +5729,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.91</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5758,21 +5764,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.05</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5793,21 +5799,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>5.12</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>8578668</x:v>
@@ -5828,21 +5834,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>21.94</x:v>
+        <x:v>22.16</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5869,15 +5875,15 @@
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5898,21 +5904,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>83.6</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5933,21 +5939,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5968,21 +5974,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>42.9</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6003,21 +6009,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>240.4</x:v>
+        <x:v>240.5</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6038,21 +6044,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.33</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6073,21 +6079,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>8.41</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6108,21 +6114,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>6.85</x:v>
+        <x:v>7.52</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6143,21 +6149,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.88</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6178,21 +6184,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>371.25</x:v>
+        <x:v>385.75</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6213,13 +6219,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>20.28</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -1304,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>12.57</x:v>
+        <x:v>12.53</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.92</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.83</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>131.7</x:v>
+        <x:v>132.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.4</x:v>
+        <x:v>13.57</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>29.06</x:v>
+        <x:v>29.56</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>16.77</x:v>
+        <x:v>16.55</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>6.16</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>0.72</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>27.98</x:v>
+        <x:v>28.04</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>25.13</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>14.29</x:v>
+        <x:v>13.75</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>47.88</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>60.5</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7.58</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.45</x:v>
+        <x:v>6.39</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>112</x:v>
+        <x:v>115.6</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>7.47</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>84</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.16</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7.58</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.98</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.81</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>55</x:v>
+        <x:v>54.05</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>784</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>27.98</x:v>
+        <x:v>28.04</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.98</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.28</x:v>
+        <x:v>7.31</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>25.38</x:v>
+        <x:v>25.44</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>9.1</x:v>
+        <x:v>9.02</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>37.8</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>7.14</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2406,7 +2406,7 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>45.66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.35</x:v>
@@ -2441,7 +2441,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>84.2</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>41.52</x:v>
+        <x:v>41.1</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2508,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>43.74</x:v>
+        <x:v>46.44</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>312.5</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.7</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2642,7 +2642,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>163.8</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>39.2</x:v>
+        <x:v>39.5</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.2</x:v>
+        <x:v>44.5</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.57</x:v>
+        <x:v>12.53</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>13.04</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.45</x:v>
+        <x:v>8.63</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2843,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.6</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2878,7 +2878,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.33</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.38</x:v>
+        <x:v>25.44</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2948,7 +2948,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>29.24</x:v>
+        <x:v>26.72</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>240.5</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>40.1</x:v>
+        <x:v>40.74</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>12.42</x:v>
+        <x:v>11.18</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>86.05</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>21.6</x:v>
+        <x:v>20.42</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>24.48</x:v>
+        <x:v>24.5</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>87.5</x:v>
+        <x:v>87.8</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3222,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>64</x:v>
+        <x:v>63.6</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.89</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>40.12</x:v>
+        <x:v>40.72</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.59</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>19.89</x:v>
+        <x:v>19.61</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.15</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3423,7 +3423,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.35</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3458,7 +3458,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>118.6</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>40.32</x:v>
+        <x:v>39.76</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>3.05</x:v>
+        <x:v>3.06</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>65.1</x:v>
+        <x:v>67.8</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>23.28</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>8</x:v>
+        <x:v>7.86</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>53</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>80.25</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>46.68</x:v>
+        <x:v>45.82</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.76</x:v>
+        <x:v>8.01</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.79</x:v>
+        <x:v>7.56</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3869,7 +3869,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>14.33</x:v>
+        <x:v>14.45</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.46</x:v>
+        <x:v>12.45</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.13</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3974,7 +3974,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>250.5</x:v>
+        <x:v>253.5</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.68</x:v>
+        <x:v>12.95</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>246</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.48</x:v>
+        <x:v>31.8</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4114,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.91</x:v>
+        <x:v>14.86</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4149,7 +4149,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.14</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.69</x:v>
+        <x:v>18.81</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4216,7 +4216,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.66</x:v>
+        <x:v>17.48</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4251,7 +4251,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>131.7</x:v>
+        <x:v>132.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>99.95</x:v>
+        <x:v>99.15</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4321,7 +4321,7 @@
         <x:v>2.37</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.62</x:v>
+        <x:v>5.57</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.52</x:v>
@@ -4356,7 +4356,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>784</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4391,7 +4391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4426,7 +4426,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>16.7</x:v>
+        <x:v>15.52</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>3.64</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>32.94</x:v>
+        <x:v>34.28</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4528,7 +4528,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>3.87</x:v>
+        <x:v>3.92</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>40</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4595,7 +4595,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>27.98</x:v>
+        <x:v>28.04</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4630,7 +4630,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.98</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.97</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>8.9</x:v>
+        <x:v>9.28</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4729,7 +4729,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>122.6</x:v>
+        <x:v>119.1</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4764,7 +4764,7 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>13.04</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
@@ -4799,7 +4799,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>42.92</x:v>
+        <x:v>42.42</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4834,7 +4834,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>111.8</x:v>
+        <x:v>111.7</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>512.5</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4901,7 +4901,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.51</x:v>
+        <x:v>11.54</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4936,7 +4936,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>16.6</x:v>
+        <x:v>17.4</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4971,7 +4971,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32.06</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>28.12</x:v>
+        <x:v>28.26</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>16.15</x:v>
+        <x:v>16.21</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5076,7 +5076,7 @@
         <x:v>1.37</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>15.99</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>9.63</x:v>
@@ -5111,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>62.3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5146,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.61</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5178,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.78</x:v>
+        <x:v>9.37</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5213,7 +5213,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>17.79</x:v>
+        <x:v>17.9</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>88.35</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>512.5</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>248.9</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5347,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.1</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5417,7 +5417,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.73</x:v>
+        <x:v>5.78</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5452,7 +5452,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>572.5</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>512.5</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5522,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.1</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5557,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5592,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>155.9</x:v>
+        <x:v>162.9</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>163.8</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5659,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5694,7 +5694,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>60.45</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5729,7 +5729,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.73</x:v>
+        <x:v>8.74</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5764,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.99</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5834,7 +5834,7 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22.16</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.49</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>9.44</x:v>
+        <x:v>9.36</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>84.2</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
@@ -5939,7 +5939,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5974,7 +5974,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>43.74</x:v>
+        <x:v>46.44</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>240.5</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
@@ -6044,7 +6044,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.33</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6079,7 +6079,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>8.8</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
@@ -6114,7 +6114,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.52</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
@@ -6149,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.8</x:v>
+        <x:v>6.76</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6184,7 +6184,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>385.75</x:v>
+        <x:v>386.25</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>21.4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,513 +130,513 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
     <x:t>06.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
@@ -677,9 +677,6 @@
   </x:si>
   <x:si>
     <x:t>14.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>ADGYO</x:t>
@@ -1304,7 +1301,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>12.53</x:v>
+        <x:v>11.63</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1336,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>20.2</x:v>
+        <x:v>20.44</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1371,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.95</x:v>
+        <x:v>8.79</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1403,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.1</x:v>
+        <x:v>6.85</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1438,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>132.5</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1470,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>13.57</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1505,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>29.56</x:v>
+        <x:v>30.32</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1540,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>16.55</x:v>
+        <x:v>16.72</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1575,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>6.12</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1607,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23</x:v>
+        <x:v>23.9</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1627,7 +1624,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>18820446</x:v>
+        <x:v>19020446</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1636,19 +1633,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>472925782</x:v>
+        <x:v>478523782</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.72</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>28.04</x:v>
+        <x:v>28.86</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.13</x:v>
+        <x:v>25.16</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1680,7 +1677,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>13.75</x:v>
+        <x:v>13.62</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1712,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>49.6</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1747,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>63.15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1782,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.39</x:v>
+        <x:v>6.35</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1849,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>115.6</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1884,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.75</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1919,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>82.6</x:v>
+        <x:v>84.35</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1954,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.24</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1989,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2006,7 +2003,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>87187201</x:v>
+        <x:v>87387201</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>200000000</x:v>
@@ -2015,7 +2012,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>855385832</x:v>
+        <x:v>857184832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
@@ -2024,21 +2021,21 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>9.01</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>16445115</x:v>
@@ -2059,21 +2056,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>54.05</x:v>
+        <x:v>53.1</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1110000</x:v>
@@ -2094,7 +2091,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>790</x:v>
+        <x:v>774.5</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2108,7 +2105,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>24398659</x:v>
@@ -2129,13 +2126,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>28.04</x:v>
+        <x:v>28.86</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2143,7 +2140,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>46563878</x:v>
@@ -2164,21 +2161,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.01</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>226257</x:v>
@@ -2199,21 +2196,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.31</x:v>
+        <x:v>7.23</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1969635</x:v>
@@ -2234,21 +2231,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>25.44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>1000000</x:v>
@@ -2269,21 +2266,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.52</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100000</x:v>
@@ -2304,21 +2301,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>9.02</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>18</x:v>
@@ -2339,7 +2336,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>37.6</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2347,10 +2344,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>5831653</x:v>
@@ -2371,21 +2368,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>7.01</x:v>
+        <x:v>6.85</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>13200000</x:v>
@@ -2406,13 +2403,13 @@
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>45</x:v>
+        <x:v>44.86</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.35</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2441,7 +2438,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>86.5</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2476,7 +2473,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>41.1</x:v>
+        <x:v>41.14</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2508,7 +2505,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2543,7 +2540,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>46.44</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2575,7 +2572,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>311</x:v>
+        <x:v>308.5</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2610,7 +2607,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>22</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2642,7 +2639,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
@@ -2677,7 +2674,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>39.5</x:v>
+        <x:v>38.98</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2709,7 +2706,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.5</x:v>
+        <x:v>44.54</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2744,7 +2741,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>12.53</x:v>
+        <x:v>11.63</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2779,7 +2776,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>13.82</x:v>
+        <x:v>13.22</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2811,7 +2808,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.63</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2843,7 +2840,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.73</x:v>
+        <x:v>6.64</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2878,7 +2875,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.52</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2889,7 +2886,7 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>120</x:v>
@@ -2913,7 +2910,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2948,7 +2945,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.72</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2983,7 +2980,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3015,7 +3012,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>40.74</x:v>
+        <x:v>41.06</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3050,7 +3047,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>11.18</x:v>
+        <x:v>10.07</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3085,7 +3082,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>86.8</x:v>
+        <x:v>93.25</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3120,7 +3117,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>20.42</x:v>
+        <x:v>19.83</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3187,7 +3184,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>87.8</x:v>
+        <x:v>89.5</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3222,7 +3219,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>63.6</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3254,7 +3251,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.3</x:v>
+        <x:v>6.11</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3286,7 +3283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>40.72</x:v>
+        <x:v>41.3</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3318,7 +3315,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.6</x:v>
+        <x:v>9.46</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3353,7 +3350,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>19.61</x:v>
+        <x:v>19.6</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3388,7 +3385,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3423,7 +3420,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.42</x:v>
+        <x:v>2.47</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3458,7 +3455,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>120</x:v>
+        <x:v>121.9</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3493,7 +3490,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>39.76</x:v>
+        <x:v>40.8</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3525,7 +3522,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>3.06</x:v>
+        <x:v>3.04</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3560,7 +3557,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>67.8</x:v>
+        <x:v>63.8</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3595,7 +3592,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>20.2</x:v>
+        <x:v>20.44</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3630,7 +3627,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>23.5</x:v>
+        <x:v>24.94</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3665,7 +3662,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.86</x:v>
+        <x:v>8.05</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3700,7 +3697,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>55.8</x:v>
+        <x:v>57.5</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3735,7 +3732,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>76.85</x:v>
+        <x:v>76.5</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3770,7 +3767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>45.82</x:v>
+        <x:v>46.28</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3802,7 +3799,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.01</x:v>
+        <x:v>8.06</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3834,7 +3831,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.56</x:v>
+        <x:v>7.58</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3869,7 +3866,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>14.45</x:v>
+        <x:v>14.48</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3904,7 +3901,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.45</x:v>
+        <x:v>12.73</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3939,7 +3936,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.1</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3974,7 +3971,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>253.5</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4009,7 +4006,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.95</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4044,7 +4041,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>258</x:v>
+        <x:v>256.25</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4079,7 +4076,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>31.8</x:v>
+        <x:v>32.86</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4114,7 +4111,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.86</x:v>
+        <x:v>14.93</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4149,7 +4146,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.13</x:v>
+        <x:v>7.19</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4184,7 +4181,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.81</x:v>
+        <x:v>19.8</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4216,7 +4213,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.48</x:v>
+        <x:v>17.45</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4251,7 +4248,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>132.5</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4286,7 +4283,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>99.15</x:v>
+        <x:v>100.9</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4332,7 +4329,7 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>188</x:v>
@@ -4356,7 +4353,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>790</x:v>
+        <x:v>774.5</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4391,7 +4388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>4.31</x:v>
+        <x:v>4.34</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4426,7 +4423,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>15.52</x:v>
+        <x:v>14.91</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4461,7 +4458,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4493,7 +4490,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>34.28</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4528,7 +4525,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>3.92</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4563,7 +4560,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.52</x:v>
+        <x:v>3.87</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4595,7 +4592,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>28.04</x:v>
+        <x:v>28.86</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4630,7 +4627,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>9.01</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4665,7 +4662,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.89</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4697,7 +4694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>9.28</x:v>
+        <x:v>9.1</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4729,7 +4726,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>119.1</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4764,13 +4761,13 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>13.82</x:v>
+        <x:v>13.22</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4799,7 +4796,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>42.42</x:v>
+        <x:v>41.84</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4834,7 +4831,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>111.7</x:v>
+        <x:v>117.3</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4869,7 +4866,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4901,7 +4898,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.54</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4936,7 +4933,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>17.4</x:v>
+        <x:v>16.91</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4971,7 +4968,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32</x:v>
+        <x:v>32.42</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5006,7 +5003,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>28.26</x:v>
+        <x:v>29.24</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5041,7 +5038,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>16.21</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5058,7 +5055,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>26626543</x:v>
+        <x:v>27956143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5067,27 +5064,27 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>256460787</x:v>
+        <x:v>277049643</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.37</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.11</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>9.63</x:v>
+        <x:v>9.91</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>220</x:v>
@@ -5111,21 +5108,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>62</x:v>
+        <x:v>60.6</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5146,7 +5143,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5154,10 +5151,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5184,15 +5181,15 @@
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5213,21 +5210,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>17.9</x:v>
+        <x:v>18.27</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5248,7 +5245,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>90.75</x:v>
+        <x:v>88.5</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5259,7 +5256,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5280,7 +5277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5288,10 +5285,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5312,7 +5309,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>248</x:v>
+        <x:v>249.5</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5323,10 +5320,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5347,21 +5344,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>12.6</x:v>
+        <x:v>13.27</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5382,7 +5379,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.3</x:v>
+        <x:v>2.27</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5393,10 +5390,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5417,7 +5414,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.78</x:v>
+        <x:v>5.92</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5428,10 +5425,10 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5452,7 +5449,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>573</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5466,7 +5463,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5487,21 +5484,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5522,21 +5519,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>12.6</x:v>
+        <x:v>13.27</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5557,21 +5554,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.3</x:v>
+        <x:v>2.27</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>281228</x:v>
@@ -5592,7 +5589,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>162.9</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5606,7 +5603,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5627,7 +5624,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5638,7 +5635,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5659,21 +5656,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5694,7 +5691,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>59.85</x:v>
+        <x:v>62.15</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5705,10 +5702,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5729,7 +5726,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.74</x:v>
+        <x:v>8.62</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5740,10 +5737,10 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5764,21 +5761,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5799,13 +5796,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.94</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5813,7 +5810,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>8578668</x:v>
@@ -5834,21 +5831,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22.24</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5869,13 +5866,13 @@
         <x:v>3.18</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>9.36</x:v>
+        <x:v>9.63</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -5883,7 +5880,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5904,21 +5901,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>86.5</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5939,7 +5936,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5953,7 +5950,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5974,13 +5971,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>46.44</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -5988,7 +5985,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6009,13 +6006,13 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6023,7 +6020,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6044,7 +6041,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.52</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6055,10 +6052,10 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6079,21 +6076,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>9.68</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>282</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6120,15 +6117,15 @@
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6149,21 +6146,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.76</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6184,21 +6181,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>386.25</x:v>
+        <x:v>387.75</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6219,13 +6216,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>22</x:v>
+        <x:v>21.74</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,87 +130,90 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>08.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
@@ -292,345 +295,345 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>28.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BLUME</x:t>
   </x:si>
   <x:si>
@@ -677,6 +680,9 @@
   </x:si>
   <x:si>
     <x:t>14.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>ADGYO</x:t>
@@ -1301,7 +1307,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>11.63</x:v>
+        <x:v>11.31</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1336,7 +1342,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>20.44</x:v>
+        <x:v>19.52</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1371,7 +1377,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.79</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1403,7 +1409,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.85</x:v>
+        <x:v>7.16</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1438,7 +1444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>135</x:v>
+        <x:v>133.8</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1470,7 +1476,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>13.04</x:v>
+        <x:v>12.82</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1505,7 +1511,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>30.32</x:v>
+        <x:v>29.28</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1540,7 +1546,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>16.72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1575,7 +1581,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.9</x:v>
+        <x:v>5.93</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1607,7 +1613,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.9</x:v>
+        <x:v>23.28</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1624,7 +1630,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>19020446</x:v>
+        <x:v>19270446</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1633,19 +1639,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>478523782</x:v>
+        <x:v>486418782</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.74</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>28.86</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.16</x:v>
+        <x:v>25.24</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1677,7 +1683,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>13.62</x:v>
+        <x:v>13.33</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1712,7 +1718,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>48.5</x:v>
+        <x:v>46.8</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1747,7 +1753,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>66</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1782,7 +1788,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7.69</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1817,7 +1823,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.35</x:v>
+        <x:v>6.32</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1849,7 +1855,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>120</x:v>
+        <x:v>121.6</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1884,7 +1890,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.73</x:v>
+        <x:v>6.46</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1919,7 +1925,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>84.35</x:v>
+        <x:v>83.4</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1954,7 +1960,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.16</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1989,7 +1995,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7.69</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2021,21 +2027,21 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.94</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.81</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>16445115</x:v>
@@ -2056,21 +2062,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>53.1</x:v>
+        <x:v>52.35</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1110000</x:v>
@@ -2091,7 +2097,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>774.5</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2105,7 +2111,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>24398659</x:v>
@@ -2126,13 +2132,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>28.86</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2140,7 +2146,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>46563878</x:v>
@@ -2161,21 +2167,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.94</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>226257</x:v>
@@ -2196,21 +2202,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.23</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1969635</x:v>
@@ -2231,21 +2237,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>25</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>1000000</x:v>
@@ -2266,21 +2272,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100000</x:v>
@@ -2301,21 +2307,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.94</x:v>
+        <x:v>8.49</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>18</x:v>
@@ -2336,7 +2342,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>40</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2344,10 +2350,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>5831653</x:v>
@@ -2368,24 +2374,24 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>6.85</x:v>
+        <x:v>6.34</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>13200000</x:v>
+        <x:v>13512000</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>79451200</x:v>
@@ -2394,22 +2400,22 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>519420697</x:v>
+        <x:v>533126017</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1.66</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>44.86</x:v>
+        <x:v>43.84</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>39.35</x:v>
+        <x:v>39.46</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2438,7 +2444,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>86.55</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2473,7 +2479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>41.14</x:v>
+        <x:v>40.54</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2505,7 +2511,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2540,7 +2546,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>51.05</x:v>
+        <x:v>50.25</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2572,7 +2578,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>308.5</x:v>
+        <x:v>305.75</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2607,7 +2613,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>22.24</x:v>
+        <x:v>20.64</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2639,7 +2645,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>171</x:v>
+        <x:v>188.1</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
@@ -2674,7 +2680,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>38.98</x:v>
+        <x:v>37.94</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2706,7 +2712,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.54</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2741,7 +2747,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>11.63</x:v>
+        <x:v>11.31</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2776,7 +2782,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>13.22</x:v>
+        <x:v>13.28</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2808,7 +2814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.61</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2875,7 +2881,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.54</x:v>
+        <x:v>3.23</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2886,7 +2892,7 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>120</x:v>
@@ -2910,7 +2916,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2945,7 +2951,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.96</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2980,7 +2986,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>239</x:v>
+        <x:v>242.9</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3012,7 +3018,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>41.06</x:v>
+        <x:v>40.38</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3047,7 +3053,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>10.07</x:v>
+        <x:v>10.02</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3082,7 +3088,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>93.25</x:v>
+        <x:v>88.15</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3117,7 +3123,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>19.83</x:v>
+        <x:v>19.9</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3149,7 +3155,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>24.5</x:v>
+        <x:v>24.26</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3184,7 +3190,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>89.5</x:v>
+        <x:v>91.05</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3219,7 +3225,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>63.1</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3251,7 +3257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.11</x:v>
+        <x:v>6.06</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3283,7 +3289,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>41.3</x:v>
+        <x:v>40.02</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3315,7 +3321,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>9.46</x:v>
+        <x:v>9.44</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3350,7 +3356,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.93</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3385,7 +3391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3420,7 +3426,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.47</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3455,7 +3461,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>121.9</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3490,7 +3496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>40.8</x:v>
+        <x:v>40.76</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3522,7 +3528,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>3.04</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3557,7 +3563,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>63.8</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3592,7 +3598,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>20.44</x:v>
+        <x:v>19.52</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3627,7 +3633,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>24.94</x:v>
+        <x:v>24.2</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3662,7 +3668,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>8.05</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3697,7 +3703,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>57.5</x:v>
+        <x:v>56.7</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3732,7 +3738,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>76.5</x:v>
+        <x:v>76.8</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3767,7 +3773,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>46.28</x:v>
+        <x:v>46.2</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3799,7 +3805,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.06</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3831,7 +3837,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.58</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3866,7 +3872,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>14.48</x:v>
+        <x:v>14.85</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3901,7 +3907,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.73</x:v>
+        <x:v>12.44</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3936,7 +3942,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.23</x:v>
+        <x:v>4.12</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3971,7 +3977,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>252</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4006,7 +4012,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>13.01</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4041,7 +4047,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>256.25</x:v>
+        <x:v>245.5</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4076,7 +4082,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.86</x:v>
+        <x:v>32.92</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4111,7 +4117,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.93</x:v>
+        <x:v>14.92</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4146,7 +4152,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.19</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4181,7 +4187,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>19.8</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4213,7 +4219,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.45</x:v>
+        <x:v>17.06</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4248,7 +4254,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>135</x:v>
+        <x:v>133.8</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4283,7 +4289,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>100.9</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4300,7 +4306,7 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>23682251</x:v>
+        <x:v>24225701</x:v>
       </x:c>
       <x:c r="D90" s="0">
         <x:v>100000000</x:v>
@@ -4309,27 +4315,27 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>107041261</x:v>
+        <x:v>109977521</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>2.37</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.57</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>4.52</x:v>
+        <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>188</x:v>
@@ -4353,7 +4359,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>774.5</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4388,7 +4394,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>4.34</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4423,7 +4429,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>14.91</x:v>
+        <x:v>13.99</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4458,7 +4464,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.4</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4490,7 +4496,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>33.08</x:v>
+        <x:v>31.44</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4525,7 +4531,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.2</x:v>
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4560,7 +4566,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.87</x:v>
+        <x:v>3.88</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4592,7 +4598,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>28.86</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4627,7 +4633,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.94</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4662,7 +4668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.81</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4694,7 +4700,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>9.1</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4726,7 +4732,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>119</x:v>
+        <x:v>120.1</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4761,18 +4767,18 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>13.22</x:v>
+        <x:v>13.28</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>188</x:v>
@@ -4796,18 +4802,18 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>41.84</x:v>
+        <x:v>40.62</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>188</x:v>
@@ -4831,18 +4837,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>117.3</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>188</x:v>
@@ -4866,7 +4872,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>519</x:v>
+        <x:v>521.5</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4874,7 +4880,7 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>188</x:v>
@@ -4898,7 +4904,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.77</x:v>
+        <x:v>11.43</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4909,7 +4915,7 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>188</x:v>
@@ -4933,7 +4939,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>16.91</x:v>
+        <x:v>18.12</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4944,7 +4950,7 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>188</x:v>
@@ -4968,21 +4974,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32.42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5003,7 +5009,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>29.24</x:v>
+        <x:v>28.3</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5014,10 +5020,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5038,24 +5044,24 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>16.18</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>27956143</x:v>
+        <x:v>28956143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5064,30 +5070,30 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>277049643</x:v>
+        <x:v>292174643</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>15.11</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>9.91</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5108,21 +5114,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>60.6</x:v>
+        <x:v>60.7</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5143,7 +5149,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5151,10 +5157,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5175,21 +5181,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.37</x:v>
+        <x:v>9.36</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5210,21 +5216,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>18.27</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5245,7 +5251,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>88.5</x:v>
+        <x:v>89.5</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5253,10 +5259,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5277,7 +5283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>519</x:v>
+        <x:v>521.5</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5285,10 +5291,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5309,7 +5315,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>249.5</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5320,10 +5326,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5344,21 +5350,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.27</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5379,7 +5385,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.27</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5390,10 +5396,10 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5414,7 +5420,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.92</x:v>
+        <x:v>6.03</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5425,10 +5431,10 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5449,7 +5455,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>575</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5460,10 +5466,10 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5484,21 +5490,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>519</x:v>
+        <x:v>521.5</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5519,21 +5525,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.27</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5554,21 +5560,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.27</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>281228</x:v>
@@ -5589,7 +5595,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5603,7 +5609,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5624,7 +5630,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>171</x:v>
+        <x:v>188.1</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5635,7 +5641,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5656,21 +5662,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5691,7 +5697,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>62.15</x:v>
+        <x:v>62.75</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5702,10 +5708,10 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5726,7 +5732,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.62</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5737,10 +5743,10 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5761,21 +5767,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5796,13 +5802,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5810,7 +5816,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>8578668</x:v>
@@ -5831,21 +5837,21 @@
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>23.16</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.49</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5863,16 +5869,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>3.18</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>9.63</x:v>
+        <x:v>9.58</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -5880,7 +5886,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5901,21 +5907,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>86.55</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5936,7 +5942,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5950,7 +5956,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5971,13 +5977,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>51.05</x:v>
+        <x:v>50.25</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -5985,7 +5991,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6006,13 +6012,13 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>239</x:v>
+        <x:v>242.9</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6020,7 +6026,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6041,7 +6047,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.54</x:v>
+        <x:v>3.23</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6052,10 +6058,10 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6076,21 +6082,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>10.64</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6111,21 +6117,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>7.88</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6146,21 +6152,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.58</x:v>
+        <x:v>6.41</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6181,21 +6187,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>387.75</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6216,13 +6222,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>21.74</x:v>
+        <x:v>20.16</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -812,9 +812,6 @@
   </x:si>
   <x:si>
     <x:t>26.07.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>FRIGO</x:t>
@@ -1307,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>11.31</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1342,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>19.52</x:v>
+        <x:v>19.42</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1377,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.65</x:v>
+        <x:v>8.53</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1409,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.16</x:v>
+        <x:v>7.03</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1444,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>133.8</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1476,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.82</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1511,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>29.28</x:v>
+        <x:v>28.72</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1546,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>16</x:v>
+        <x:v>14.97</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1581,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.93</x:v>
+        <x:v>5.95</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1613,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.28</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1648,7 +1645,7 @@
         <x:v>0.74</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.46</x:v>
+        <x:v>31.16</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>25.24</x:v>
@@ -1683,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>13.33</x:v>
+        <x:v>12.88</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1718,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>46.8</x:v>
+        <x:v>45.4</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1753,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>63.3</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1788,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7.44</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1823,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.32</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1855,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>121.6</x:v>
+        <x:v>122.4</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1890,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.46</x:v>
+        <x:v>6.54</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1925,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>83.4</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1960,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.5</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1995,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7.44</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2027,7 +2024,7 @@
         <x:v>0.97</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.98</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.81</x:v>
@@ -2062,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>52.35</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2097,7 +2094,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>781</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2132,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.46</x:v>
+        <x:v>31.16</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2167,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.98</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2202,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.35</x:v>
+        <x:v>7.18</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2237,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.96</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2272,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.42</x:v>
+        <x:v>3.76</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2307,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.49</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2342,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>40.2</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2374,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>6.34</x:v>
+        <x:v>6.11</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2409,7 +2406,7 @@
         <x:v>1.7</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>43.84</x:v>
+        <x:v>43.76</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.46</x:v>
@@ -2444,7 +2441,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>95.2</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2479,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>40.54</x:v>
+        <x:v>39.6</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2511,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.63</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2546,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>50.25</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2578,7 +2575,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>305.75</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2613,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>20.64</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2645,7 +2642,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>188.1</x:v>
+        <x:v>186.1</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
@@ -2680,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.94</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2712,7 +2709,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>43.8</x:v>
+        <x:v>44.12</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2747,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>11.31</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2782,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>13.28</x:v>
+        <x:v>12.62</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2814,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.66</x:v>
+        <x:v>8.63</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2846,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.64</x:v>
+        <x:v>6.49</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2881,7 +2878,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.23</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2916,7 +2913,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22.96</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2951,7 +2948,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.4</x:v>
+        <x:v>26.42</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2986,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>242.9</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3018,7 +3015,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>40.38</x:v>
+        <x:v>39.58</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3053,7 +3050,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>10.02</x:v>
+        <x:v>9.71</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3088,7 +3085,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>88.15</x:v>
+        <x:v>86.15</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3123,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>19.9</x:v>
+        <x:v>19.73</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3155,7 +3152,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>24.26</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3190,7 +3187,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>91.05</x:v>
+        <x:v>91.15</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3225,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>61.45</x:v>
+        <x:v>61.25</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3257,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.06</x:v>
+        <x:v>6.08</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3289,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>40.02</x:v>
+        <x:v>39.72</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3321,7 +3318,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>9.44</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3356,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.93</x:v>
+        <x:v>18.55</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3391,7 +3388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3426,7 +3423,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3461,7 +3458,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3496,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>40.76</x:v>
+        <x:v>39.5</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3563,7 +3560,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>61.35</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3598,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>19.52</x:v>
+        <x:v>19.42</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3633,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>24.2</x:v>
+        <x:v>23.74</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3668,7 +3665,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.76</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3703,7 +3700,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>56.7</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3738,7 +3735,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>76.8</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3773,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>46.2</x:v>
+        <x:v>44.2</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3805,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.04</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3837,7 +3834,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.5</x:v>
+        <x:v>7.31</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3872,7 +3869,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>14.85</x:v>
+        <x:v>13.93</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3907,7 +3904,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.44</x:v>
+        <x:v>12.08</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3942,7 +3939,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.12</x:v>
+        <x:v>4.14</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3977,7 +3974,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>241.4</x:v>
+        <x:v>239.8</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4012,7 +4009,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.77</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4047,7 +4044,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>245.5</x:v>
+        <x:v>259.75</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4082,7 +4079,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.92</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4117,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.92</x:v>
+        <x:v>14.24</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4152,7 +4149,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.59</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4187,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.9</x:v>
+        <x:v>18.62</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4219,7 +4216,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.06</x:v>
+        <x:v>16.94</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4254,7 +4251,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>133.8</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4289,7 +4286,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>101</x:v>
+        <x:v>100.4</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4324,7 +4321,7 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.6</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
@@ -4359,7 +4356,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>781</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4394,7 +4391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>4.06</x:v>
+        <x:v>3.96</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4429,7 +4426,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>13.99</x:v>
+        <x:v>15.38</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4464,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.29</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4496,7 +4493,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>31.44</x:v>
+        <x:v>29.66</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4531,7 +4528,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.32</x:v>
+        <x:v>4.12</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4566,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.88</x:v>
+        <x:v>3.97</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4598,7 +4595,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.46</x:v>
+        <x:v>31.16</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4633,7 +4630,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.98</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4668,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.98</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4700,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>8.7</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4732,7 +4729,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>120.1</x:v>
+        <x:v>116.6</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4767,7 +4764,7 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>13.28</x:v>
+        <x:v>12.62</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
@@ -4802,7 +4799,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>40.62</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4837,7 +4834,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4872,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>521.5</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4904,7 +4901,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.43</x:v>
+        <x:v>11.49</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4939,7 +4936,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>18.12</x:v>
+        <x:v>18.25</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4974,7 +4971,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32</x:v>
+        <x:v>32.42</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5009,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>28.3</x:v>
+        <x:v>31.12</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5044,7 +5041,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.7</x:v>
+        <x:v>15.82</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5079,7 +5076,7 @@
         <x:v>1.48</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.6</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>10.09</x:v>
@@ -5114,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>60.7</x:v>
+        <x:v>59.2</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5149,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.63</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5181,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.36</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5251,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>89.5</x:v>
+        <x:v>86.1</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5283,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>521.5</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5315,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5350,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.4</x:v>
+        <x:v>13.45</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5385,7 +5382,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.13</x:v>
+        <x:v>2.09</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5420,7 +5417,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.03</x:v>
+        <x:v>5.78</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5455,7 +5452,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>580</x:v>
+        <x:v>592.5</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5490,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>521.5</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5525,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.4</x:v>
+        <x:v>13.45</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5560,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.13</x:v>
+        <x:v>2.09</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5595,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>164</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5630,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>188.1</x:v>
+        <x:v>186.1</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5662,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.63</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5697,7 +5694,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>62.75</x:v>
+        <x:v>60.55</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5732,7 +5729,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.57</x:v>
+        <x:v>8.46</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5767,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.54</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5802,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.94</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5819,7 +5816,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>8578668</x:v>
+        <x:v>9301948</x:v>
       </x:c>
       <x:c r="D134" s="0">
         <x:v>17500000</x:v>
@@ -5828,30 +5825,30 @@
         <x:v>525000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>184312813</x:v>
+        <x:v>201194168</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>23.5</x:v>
+        <x:v>22.52</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>21.49</x:v>
+        <x:v>21.63</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5872,13 +5869,13 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>9.58</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -5886,7 +5883,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5907,21 +5904,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>95.2</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5942,7 +5939,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5956,7 +5953,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5977,13 +5974,13 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>50.25</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -5991,7 +5988,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6012,13 +6009,13 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>242.9</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6026,7 +6023,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6047,7 +6044,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.23</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6058,10 +6055,10 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>280</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6082,21 +6079,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>11.41</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6117,21 +6114,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>8.2</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6152,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.41</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6163,10 +6160,10 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6187,21 +6184,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>360</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6222,13 +6219,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>20.16</x:v>
+        <x:v>19.63</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,468 +130,471 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>12.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>GLRYH</x:t>
   </x:si>
   <x:si>
@@ -680,9 +683,6 @@
   </x:si>
   <x:si>
     <x:t>14.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>ADGYO</x:t>
@@ -1304,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>11.33</x:v>
+        <x:v>10.83</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>19.42</x:v>
+        <x:v>19.4</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.53</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.03</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>129.5</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.7</x:v>
+        <x:v>12.44</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>28.72</x:v>
+        <x:v>28.84</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>14.97</x:v>
+        <x:v>15.13</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.95</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.26</x:v>
+        <x:v>22.34</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1627,7 +1627,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>19270446</x:v>
+        <x:v>19659503</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1636,19 +1636,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>486418782</x:v>
+        <x:v>498518291</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.74</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.16</x:v>
+        <x:v>31.1</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.24</x:v>
+        <x:v>25.36</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.88</x:v>
+        <x:v>12.97</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>45.4</x:v>
+        <x:v>49.94</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>61.1</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>7</x:v>
+        <x:v>6.86</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.15</x:v>
+        <x:v>6.29</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>122.4</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.54</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>81.65</x:v>
+        <x:v>81.6</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.52</x:v>
+        <x:v>22.84</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>7</x:v>
+        <x:v>6.86</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2006,7 +2006,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>87387201</x:v>
+        <x:v>87987201</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>200000000</x:v>
@@ -2015,19 +2015,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>857184832</x:v>
+        <x:v>862443832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.97</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.76</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>9.81</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>65</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>52.45</x:v>
+        <x:v>52.4</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2091,10 +2091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>813</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.16</x:v>
+        <x:v>31.1</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.76</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.18</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22</x:v>
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.76</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.1</x:v>
+        <x:v>8.12</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>38.34</x:v>
+        <x:v>39.46</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>6.11</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>13512000</x:v>
+        <x:v>13712000</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>79451200</x:v>
@@ -2397,19 +2397,19 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>533126017</x:v>
+        <x:v>541757609</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1.7</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>43.76</x:v>
+        <x:v>43.14</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>39.46</x:v>
+        <x:v>39.51</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
         <x:v>38</x:v>
@@ -2441,7 +2441,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>95.5</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>39.6</x:v>
+        <x:v>41.88</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2508,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>52.15</x:v>
+        <x:v>55.85</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>304</x:v>
+        <x:v>305.75</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>20.02</x:v>
+        <x:v>20.36</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>36.4</x:v>
+        <x:v>37.06</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.12</x:v>
+        <x:v>43.92</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>11.33</x:v>
+        <x:v>10.83</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>12.62</x:v>
+        <x:v>13.35</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.63</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2843,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.49</x:v>
+        <x:v>6.66</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2878,7 +2878,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.91</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22</x:v>
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2948,7 +2948,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.42</x:v>
+        <x:v>26.52</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>242</x:v>
+        <x:v>241.5</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>39.58</x:v>
+        <x:v>39.38</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.71</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>86.15</x:v>
+        <x:v>88.3</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>19.73</x:v>
+        <x:v>19.65</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>24.52</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>91.15</x:v>
+        <x:v>91.2</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3222,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.55</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.08</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>39.72</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.97</x:v>
+        <x:v>8.91</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.55</x:v>
+        <x:v>18.61</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3</x:v>
+        <x:v>3.04</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3423,7 +3423,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.22</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3458,7 +3458,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>114</x:v>
+        <x:v>114.5</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>39.5</x:v>
+        <x:v>41.18</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.96</x:v>
+        <x:v>2.99</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>61</x:v>
+        <x:v>60.4</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3595,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>19.42</x:v>
+        <x:v>19.4</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>23.74</x:v>
+        <x:v>24.12</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.59</x:v>
+        <x:v>7.71</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>58.4</x:v>
+        <x:v>64.2</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>72.1</x:v>
+        <x:v>74.95</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>44.2</x:v>
+        <x:v>43.72</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.96</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.31</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3869,7 +3869,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.93</x:v>
+        <x:v>13.84</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.08</x:v>
+        <x:v>12.16</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.14</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3974,7 +3974,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>239.8</x:v>
+        <x:v>242.5</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.85</x:v>
+        <x:v>13.39</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>259.75</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.3</x:v>
+        <x:v>33.32</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4114,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.24</x:v>
+        <x:v>14.62</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4149,7 +4149,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.27</x:v>
+        <x:v>7.33</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.62</x:v>
+        <x:v>18.45</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4216,7 +4216,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.94</x:v>
+        <x:v>17.35</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4251,7 +4251,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>129.5</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>100.4</x:v>
+        <x:v>97.6</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4321,13 +4321,13 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.4</x:v>
+        <x:v>5.31</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -4353,10 +4353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.17</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>813</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4367,7 +4367,7 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>188</x:v>
@@ -4391,7 +4391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.96</x:v>
+        <x:v>3.93</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4402,7 +4402,7 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>188</x:v>
@@ -4426,7 +4426,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>15.38</x:v>
+        <x:v>13.85</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4437,7 +4437,7 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>188</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.71</x:v>
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4469,7 +4469,7 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>188</x:v>
@@ -4493,18 +4493,18 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>29.66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>188</x:v>
@@ -4528,18 +4528,18 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.12</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>188</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.97</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4595,13 +4595,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.16</x:v>
+        <x:v>31.1</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -4630,18 +4630,18 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.76</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>188</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.73</x:v>
+        <x:v>4.79</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4673,7 +4673,7 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>188</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>8.21</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4705,7 +4705,7 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>188</x:v>
@@ -4729,13 +4729,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>116.6</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -4764,18 +4764,18 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>12.62</x:v>
+        <x:v>13.35</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>188</x:v>
@@ -4799,18 +4799,18 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>40.08</x:v>
+        <x:v>39.1</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>188</x:v>
@@ -4834,18 +4834,18 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>129</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>188</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4877,7 +4877,7 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>188</x:v>
@@ -4901,7 +4901,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.49</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4912,7 +4912,7 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>188</x:v>
@@ -4936,7 +4936,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>18.25</x:v>
+        <x:v>17.87</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4947,7 +4947,7 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>188</x:v>
@@ -4971,21 +4971,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32.42</x:v>
+        <x:v>32.06</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>31.12</x:v>
+        <x:v>34.22</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5017,10 +5017,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5041,24 +5041,24 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.82</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>28956143</x:v>
+        <x:v>30756143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5067,22 +5067,22 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>292174643</x:v>
+        <x:v>317583443</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.99</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>10.09</x:v>
+        <x:v>10.33</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -5090,7 +5090,7 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5111,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>59.2</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5146,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5178,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.32</x:v>
+        <x:v>9.39</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5213,7 +5213,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>17.8</x:v>
+        <x:v>18.26</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>86.1</x:v>
+        <x:v>86.4</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5256,7 +5256,7 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>235</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>244</x:v>
+        <x:v>243.6</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5347,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.45</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.09</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5417,13 +5417,13 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.78</x:v>
+        <x:v>6.35</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5452,18 +5452,18 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>592.5</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>246</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5522,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.45</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5557,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.09</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5592,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>157</x:v>
+        <x:v>160.9</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5659,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5694,7 +5694,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>60.55</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5764,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.76</x:v>
+        <x:v>4.91</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5816,7 +5816,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>9301948</x:v>
+        <x:v>10195940</x:v>
       </x:c>
       <x:c r="D134" s="0">
         <x:v>17500000</x:v>
@@ -5825,22 +5825,22 @@
         <x:v>525000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>201194168</x:v>
+        <x:v>221326868</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22.52</x:v>
+        <x:v>22.84</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>21.63</x:v>
+        <x:v>21.71</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
@@ -5869,7 +5869,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>3.26</x:v>
+        <x:v>3.36</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>95.5</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
@@ -5939,7 +5939,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5974,7 +5974,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>52.15</x:v>
+        <x:v>55.85</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>242</x:v>
+        <x:v>241.5</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
@@ -6044,13 +6044,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.91</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6079,7 +6079,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>12.55</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
@@ -6114,7 +6114,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>8.61</x:v>
+        <x:v>9.03</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
@@ -6149,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.15</x:v>
+        <x:v>6.27</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6184,7 +6184,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>324</x:v>
+        <x:v>292.5</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>19.63</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -1304,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>10.83</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>19.4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.73</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7</x:v>
+        <x:v>6.82</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>128</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.44</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>28.84</x:v>
+        <x:v>28.34</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>15.13</x:v>
+        <x:v>14.75</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.97</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.34</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>0.76</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.1</x:v>
+        <x:v>31.22</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>25.36</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.97</x:v>
+        <x:v>12.63</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>49.94</x:v>
+        <x:v>47.2</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.05</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.86</x:v>
+        <x:v>6.97</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.29</x:v>
+        <x:v>6.14</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>126</x:v>
+        <x:v>125.9</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.63</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>81.6</x:v>
+        <x:v>78.35</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.84</x:v>
+        <x:v>22.92</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.86</x:v>
+        <x:v>6.97</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.77</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.8</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>52.4</x:v>
+        <x:v>51.45</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>414</x:v>
+        <x:v>405.25</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.1</x:v>
+        <x:v>31.22</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.77</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.89</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>23.1</x:v>
+        <x:v>22.3</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.12</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>39.46</x:v>
+        <x:v>37.5</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>5.87</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2406,7 +2406,7 @@
         <x:v>1.73</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>43.14</x:v>
+        <x:v>42.74</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.51</x:v>
@@ -2441,7 +2441,7 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>97.3</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>41.88</x:v>
+        <x:v>43.66</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2508,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.62</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>55.85</x:v>
+        <x:v>50.55</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>305.75</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>20.36</x:v>
+        <x:v>20.32</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2642,7 +2642,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>186.1</x:v>
+        <x:v>188.1</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.06</x:v>
+        <x:v>38.38</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>43.92</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>10.83</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>13.35</x:v>
+        <x:v>12.73</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.7</x:v>
+        <x:v>8.62</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2843,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.66</x:v>
+        <x:v>6.52</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2878,7 +2878,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>3.01</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>23.1</x:v>
+        <x:v>22.3</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2948,7 +2948,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>26.52</x:v>
+        <x:v>25.72</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>241.5</x:v>
+        <x:v>237.9</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>39.38</x:v>
+        <x:v>38.16</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.92</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>88.3</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>19.65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.4</x:v>
+        <x:v>23.18</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>91.2</x:v>
+        <x:v>89.25</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3222,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>61.55</x:v>
+        <x:v>61.25</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>5.97</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>40.1</x:v>
+        <x:v>40.3</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.61</x:v>
+        <x:v>18.3</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3.04</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3423,7 +3423,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.32</x:v>
+        <x:v>2.26</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3458,7 +3458,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>114.5</x:v>
+        <x:v>109.5</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>41.18</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.99</x:v>
+        <x:v>2.93</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>60.4</x:v>
+        <x:v>57.65</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3595,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>19.4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>24.12</x:v>
+        <x:v>23.74</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.71</x:v>
+        <x:v>7.51</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>64.2</x:v>
+        <x:v>64.15</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>74.95</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>43.72</x:v>
+        <x:v>42.4</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.75</x:v>
+        <x:v>8.83</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.76</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3869,7 +3869,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.84</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>12.16</x:v>
+        <x:v>11.95</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.13</x:v>
+        <x:v>4.12</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3974,7 +3974,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>242.5</x:v>
+        <x:v>232.4</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>13.39</x:v>
+        <x:v>14.15</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>264</x:v>
+        <x:v>247.8</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>33.32</x:v>
+        <x:v>33.36</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4114,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.62</x:v>
+        <x:v>14.19</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4149,7 +4149,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.33</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4216,7 +4216,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.35</x:v>
+        <x:v>17.36</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4251,7 +4251,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>128</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>97.6</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4321,7 +4321,7 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
@@ -4356,7 +4356,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>414</x:v>
+        <x:v>405.25</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4391,7 +4391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.93</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4426,7 +4426,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>13.85</x:v>
+        <x:v>13.41</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.57</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>30</x:v>
+        <x:v>29.34</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4528,7 +4528,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.1</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.95</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4595,7 +4595,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.1</x:v>
+        <x:v>31.22</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4630,7 +4630,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.77</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.79</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>8.1</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4729,7 +4729,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>118</x:v>
+        <x:v>119.9</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4764,7 +4764,7 @@
         <x:v>4.72</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>13.35</x:v>
+        <x:v>12.73</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>9.97</x:v>
@@ -4799,7 +4799,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>39.1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4834,7 +4834,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>123.9</x:v>
+        <x:v>124.7</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>530</x:v>
+        <x:v>545.5</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4901,7 +4901,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.46</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4936,7 +4936,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>17.87</x:v>
+        <x:v>17.15</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4971,7 +4971,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>32.06</x:v>
+        <x:v>30.8</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>34.22</x:v>
+        <x:v>31.58</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.9</x:v>
+        <x:v>15.39</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5076,7 +5076,7 @@
         <x:v>1.58</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.99</x:v>
+        <x:v>14.68</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>10.33</x:v>
@@ -5111,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>59</x:v>
+        <x:v>58.35</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5146,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5178,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.39</x:v>
+        <x:v>9.21</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5213,7 +5213,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>18.26</x:v>
+        <x:v>18.74</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>86.4</x:v>
+        <x:v>84.75</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>530</x:v>
+        <x:v>545.5</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>243.6</x:v>
+        <x:v>237.6</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5347,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.5</x:v>
+        <x:v>13.3</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.12</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5417,7 +5417,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.35</x:v>
+        <x:v>6.98</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5452,7 +5452,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>590</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>530</x:v>
+        <x:v>545.5</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5522,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.5</x:v>
+        <x:v>13.3</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5557,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.12</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5592,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>160.9</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>186.1</x:v>
+        <x:v>188.1</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5659,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.62</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5694,7 +5694,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>59.55</x:v>
+        <x:v>59.25</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5729,7 +5729,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.46</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5764,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.45</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.91</x:v>
+        <x:v>4.78</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5834,7 +5834,7 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22.84</x:v>
+        <x:v>22.92</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>3.36</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>97.3</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
@@ -5939,7 +5939,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5974,7 +5974,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>55.85</x:v>
+        <x:v>50.55</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>241.5</x:v>
+        <x:v>237.9</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
@@ -6044,7 +6044,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>3.01</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6079,7 +6079,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>12.77</x:v>
+        <x:v>12.44</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
@@ -6114,7 +6114,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>9.03</x:v>
+        <x:v>9.23</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
@@ -6149,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.27</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6184,7 +6184,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>292.5</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>20.06</x:v>
+        <x:v>19.19</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -295,6 +295,9 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
@@ -632,9 +635,6 @@
   </x:si>
   <x:si>
     <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>BLUME</x:t>
@@ -1304,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>10.98</x:v>
+        <x:v>10.62</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>19</x:v>
+        <x:v>18.95</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.4</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.82</x:v>
+        <x:v>7.24</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>129.5</x:v>
+        <x:v>125.6</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>11.2</x:v>
+        <x:v>10.62</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>28.34</x:v>
+        <x:v>27.4</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>14.75</x:v>
+        <x:v>14.23</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>6</x:v>
+        <x:v>5.88</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.5</x:v>
+        <x:v>22.34</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>0.76</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.22</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>25.36</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.63</x:v>
+        <x:v>12.52</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>47.2</x:v>
+        <x:v>46.06</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>63</x:v>
+        <x:v>60.25</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.97</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.14</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>125.9</x:v>
+        <x:v>127.4</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.61</x:v>
+        <x:v>6.78</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>78.35</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22.92</x:v>
+        <x:v>23.96</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.97</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.6</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.8</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>51.45</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>405.25</x:v>
+        <x:v>392.5</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.22</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.6</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.3</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.3</x:v>
+        <x:v>22.04</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.76</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>8.21</x:v>
+        <x:v>7.91</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>37.5</x:v>
+        <x:v>35.72</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>5.43</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>13712000</x:v>
+        <x:v>13762000</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>79451200</x:v>
@@ -2397,7 +2397,7 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>541757609</x:v>
+        <x:v>543888662</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
@@ -2406,21 +2406,21 @@
         <x:v>1.73</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>42.74</x:v>
+        <x:v>41.52</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>39.51</x:v>
+        <x:v>39.52</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>1973951</x:v>
@@ -2441,21 +2441,21 @@
         <x:v>2.47</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>99.5</x:v>
+        <x:v>93.15</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.65</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>18</x:v>
@@ -2476,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>43.66</x:v>
+        <x:v>40.76</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2484,10 +2484,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>3337681</x:v>
@@ -2508,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.62</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2519,10 +2519,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>18</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>50.55</x:v>
+        <x:v>47.76</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2551,10 +2551,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>1364000</x:v>
@@ -2575,21 +2575,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>300</x:v>
+        <x:v>294.5</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>18</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>20.32</x:v>
+        <x:v>19.86</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2618,10 +2618,10 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>507440</x:v>
@@ -2642,21 +2642,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>188.1</x:v>
+        <x:v>206.9</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>18</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>38.38</x:v>
+        <x:v>37.94</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2685,10 +2685,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>2000000</x:v>
@@ -2709,13 +2709,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44</x:v>
+        <x:v>45.1</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2723,7 +2723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>324474</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>10.98</x:v>
+        <x:v>10.62</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2755,10 +2755,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>18</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>12.73</x:v>
+        <x:v>12.58</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2787,10 +2787,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>18</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.62</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2819,10 +2819,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>2000000</x:v>
@@ -2843,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.52</x:v>
+        <x:v>6.33</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2854,10 +2854,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>174500000</x:v>
@@ -2878,13 +2878,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2892,7 +2892,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>635229</x:v>
@@ -2913,21 +2913,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22.3</x:v>
+        <x:v>22.04</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>130000</x:v>
@@ -2948,21 +2948,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>25.72</x:v>
+        <x:v>24.92</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>237.9</x:v>
+        <x:v>224.7</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -2991,10 +2991,10 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>447761</x:v>
@@ -3015,21 +3015,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>38.16</x:v>
+        <x:v>37.62</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>200000</x:v>
@@ -3050,21 +3050,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.96</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>946718</x:v>
@@ -3085,21 +3085,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>87.2</x:v>
+        <x:v>85.15</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>18</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>19</x:v>
+        <x:v>17.85</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3128,10 +3128,10 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>3043115</x:v>
@@ -3152,21 +3152,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.18</x:v>
+        <x:v>22.6</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2382736</x:v>
@@ -3187,21 +3187,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>89.25</x:v>
+        <x:v>84.7</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>18</x:v>
@@ -3222,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>61.25</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3230,10 +3230,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>18</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3262,10 +3262,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>18</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>40.3</x:v>
+        <x:v>39.98</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3294,10 +3294,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>310000</x:v>
@@ -3318,21 +3318,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.91</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>2000000</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.3</x:v>
+        <x:v>18.37</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3364,10 +3364,10 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>1250000</x:v>
@@ -3388,21 +3388,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>3</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>12500000</x:v>
@@ -3423,21 +3423,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.26</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>2093944</x:v>
@@ -3458,21 +3458,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>109.5</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>18</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>40.4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3501,10 +3501,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>51245979</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.93</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3536,10 +3536,10 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1584837</x:v>
@@ -3560,13 +3560,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>57.65</x:v>
+        <x:v>57.7</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3574,7 +3574,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>7999148</x:v>
@@ -3595,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>19</x:v>
+        <x:v>18.95</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3606,10 +3606,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>14000000</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>23.74</x:v>
+        <x:v>22.58</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3641,10 +3641,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>1700005</x:v>
@@ -3665,21 +3665,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.51</x:v>
+        <x:v>7.28</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>6000000</x:v>
@@ -3700,21 +3700,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>64.15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>1675000</x:v>
@@ -3735,21 +3735,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>75.1</x:v>
+        <x:v>73.8</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>18</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>42.4</x:v>
+        <x:v>41.76</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3778,10 +3778,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>18</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.83</x:v>
+        <x:v>9.29</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3810,10 +3810,10 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1000000</x:v>
@@ -3834,21 +3834,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.32</x:v>
+        <x:v>8.05</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>98551</x:v>
@@ -3869,21 +3869,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.9</x:v>
+        <x:v>13.51</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>6049315</x:v>
@@ -3904,21 +3904,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.95</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>37225000</x:v>
@@ -3939,21 +3939,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>4.12</x:v>
+        <x:v>3.96</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1000000</x:v>
@@ -3974,21 +3974,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>232.4</x:v>
+        <x:v>220.5</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>600000</x:v>
@@ -4009,21 +4009,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>14.15</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>11703083</x:v>
@@ -4044,21 +4044,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>247.8</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4079,21 +4079,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>33.36</x:v>
+        <x:v>32.2</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>3228679</x:v>
@@ -4114,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>14.19</x:v>
+        <x:v>13.93</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4125,10 +4125,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>150000</x:v>
@@ -4149,21 +4149,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.15</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>18</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18</x:v>
+        <x:v>17.92</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4192,10 +4192,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>366107</x:v>
@@ -4216,13 +4216,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.36</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -4230,7 +4230,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>120000</x:v>
@@ -4251,21 +4251,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>129.5</x:v>
+        <x:v>125.6</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>13050000</x:v>
@@ -4286,21 +4286,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>97</x:v>
+        <x:v>92.85</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>24225701</x:v>
@@ -4321,13 +4321,13 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.84</x:v>
+        <x:v>5.36</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -4335,7 +4335,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>1000000</x:v>
@@ -4356,21 +4356,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>405.25</x:v>
+        <x:v>392.5</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>300000</x:v>
@@ -4391,21 +4391,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.8</x:v>
+        <x:v>3.71</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>2175097</x:v>
@@ -4426,21 +4426,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>13.41</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>18</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.28</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4469,10 +4469,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>43000</x:v>
@@ -4493,21 +4493,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>29.34</x:v>
+        <x:v>31.22</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>9937037</x:v>
@@ -4528,21 +4528,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.29</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.7</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4574,7 +4574,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>13064888</x:v>
@@ -4595,13 +4595,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.22</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -4609,7 +4609,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>111673026</x:v>
@@ -4630,21 +4630,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.6</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.76</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4673,10 +4673,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>7.9</x:v>
+        <x:v>7.67</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4705,10 +4705,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>1100000</x:v>
@@ -4729,24 +4729,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>119.9</x:v>
+        <x:v>116.5</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>5267479</x:v>
+        <x:v>5647479</x:v>
       </x:c>
       <x:c r="D103" s="0">
         <x:v>11160000</x:v>
@@ -4755,22 +4755,22 @@
         <x:v>125000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>52505825</x:v>
+        <x:v>57363901</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>4.72</x:v>
+        <x:v>5.06</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>12.73</x:v>
+        <x:v>12.58</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>9.97</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4778,7 +4778,7 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1590000</x:v>
@@ -4799,7 +4799,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>39</x:v>
+        <x:v>39.4</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4813,7 +4813,7 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1989802</x:v>
@@ -4834,7 +4834,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>124.7</x:v>
+        <x:v>125.4</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4848,7 +4848,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>18</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>545.5</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4880,7 +4880,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>300000</x:v>
@@ -4901,13 +4901,13 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.1</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -4915,7 +4915,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>8291656</x:v>
@@ -4936,13 +4936,13 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>17.15</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -4950,7 +4950,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>76908759</x:v>
@@ -4971,7 +4971,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>30.8</x:v>
+        <x:v>30.94</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>31.58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5058,7 +5058,7 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>30756143</x:v>
+        <x:v>31006143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5067,22 +5067,22 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>317583443</x:v>
+        <x:v>321270943</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.58</x:v>
+        <x:v>1.59</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.68</x:v>
+        <x:v>14.56</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>10.33</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -5111,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>58.35</x:v>
+        <x:v>57.6</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5146,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5178,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.21</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5213,7 +5213,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>18.74</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>84.75</x:v>
+        <x:v>82.55</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>545.5</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>237.6</x:v>
+        <x:v>236.7</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5347,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.3</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5382,13 +5382,13 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.25</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -5417,13 +5417,13 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.98</x:v>
+        <x:v>7.67</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5452,13 +5452,13 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>594</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
@@ -5487,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>545.5</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5522,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.3</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5557,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.25</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5592,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5603,7 +5603,7 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>252</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>188.1</x:v>
+        <x:v>206.9</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5635,7 +5635,7 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>253</x:v>
@@ -5659,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.62</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5694,13 +5694,13 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>59.25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
@@ -5729,13 +5729,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.45</x:v>
+        <x:v>8.44</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -5764,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.78</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5834,7 +5834,7 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22.92</x:v>
+        <x:v>23.96</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>3.26</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
@@ -5880,7 +5880,7 @@
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>269</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>99.5</x:v>
+        <x:v>93.15</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
@@ -5939,18 +5939,18 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>273</x:v>
@@ -5974,7 +5974,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>50.55</x:v>
+        <x:v>47.76</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
@@ -5985,7 +5985,7 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>275</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>237.9</x:v>
+        <x:v>224.7</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
@@ -6020,7 +6020,7 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>277</x:v>
@@ -6044,13 +6044,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6079,7 +6079,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>12.44</x:v>
+        <x:v>12.01</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
@@ -6149,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.22</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6184,7 +6184,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>283</x:v>
+        <x:v>280.75</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>19.19</x:v>
+        <x:v>18.25</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,688 +130,685 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1YEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>14.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.02.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.01.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.12.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.11.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.11.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.10.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.10.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.09.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.05.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.07.2024</x:t>
   </x:si>
   <x:si>
     <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1YEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.01.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.12.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.11.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.11.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.07.2024</x:t>
   </x:si>
   <x:si>
     <x:t>FRIGO</x:t>
@@ -1304,7 +1301,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>10.62</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1336,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>18.95</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1371,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.24</x:v>
+        <x:v>8.16</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1403,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.24</x:v>
+        <x:v>7.06</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1438,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>125.6</x:v>
+        <x:v>116.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1470,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>10.62</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1505,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>27.4</x:v>
+        <x:v>27.9</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1540,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>14.23</x:v>
+        <x:v>14.62</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1575,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.88</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1607,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>22.34</x:v>
+        <x:v>23.42</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1627,7 +1624,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>19659503</x:v>
+        <x:v>20459503</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1636,19 +1633,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>498518291</x:v>
+        <x:v>522826291</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.76</x:v>
+        <x:v>0.79</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>30.22</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.36</x:v>
+        <x:v>25.55</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1680,7 +1677,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.52</x:v>
+        <x:v>12.31</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1712,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>46.06</x:v>
+        <x:v>46.86</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1747,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>60.25</x:v>
+        <x:v>59.3</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1782,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.61</x:v>
+        <x:v>6.54</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1852,7 +1849,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>127.4</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1884,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.78</x:v>
+        <x:v>7.02</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1919,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>73.25</x:v>
+        <x:v>69.3</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1954,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.96</x:v>
+        <x:v>23.9</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1989,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.61</x:v>
+        <x:v>6.54</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2006,7 +2003,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>87987201</x:v>
+        <x:v>88087201</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>200000000</x:v>
@@ -2015,7 +2012,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>862443832</x:v>
+        <x:v>863285832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
@@ -2024,21 +2021,21 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.65</x:v>
+        <x:v>8.71</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.8</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>16445115</x:v>
@@ -2059,21 +2056,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>50.35</x:v>
+        <x:v>49.38</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1110000</x:v>
@@ -2094,7 +2091,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>392.5</x:v>
+        <x:v>392.75</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2108,7 +2105,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>24398659</x:v>
@@ -2129,13 +2126,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>30.22</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2143,7 +2140,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>46563878</x:v>
@@ -2164,21 +2161,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.65</x:v>
+        <x:v>8.71</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>226257</x:v>
@@ -2199,21 +2196,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.38</x:v>
+        <x:v>7.26</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1969635</x:v>
@@ -2234,21 +2231,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>22.04</x:v>
+        <x:v>21.62</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>1000000</x:v>
@@ -2269,21 +2266,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.76</x:v>
+        <x:v>3.72</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100000</x:v>
@@ -2304,21 +2301,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.91</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>18</x:v>
@@ -2339,7 +2336,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>35.72</x:v>
+        <x:v>36.9</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2347,10 +2344,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>5831653</x:v>
@@ -2371,24 +2368,24 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>5.97</x:v>
+        <x:v>6.27</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="C34" s="0">
-        <x:v>13762000</x:v>
+        <x:v>14012000</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>79451200</x:v>
@@ -2397,33 +2394,33 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>543888662</x:v>
+        <x:v>554294062</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>41.52</x:v>
+        <x:v>41.86</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>39.52</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>1973951</x:v>
+        <x:v>1993951</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>3000000</x:v>
@@ -2432,30 +2429,30 @@
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>135510760</x:v>
+        <x:v>137370760</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>2.47</x:v>
+        <x:v>2.49</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>93.15</x:v>
+        <x:v>102.4</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>68.65</x:v>
+        <x:v>68.89</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>18</x:v>
@@ -2476,7 +2473,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>40.76</x:v>
+        <x:v>40.72</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2484,10 +2481,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>3337681</x:v>
@@ -2508,7 +2505,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2519,10 +2516,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>18</x:v>
@@ -2543,7 +2540,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>47.76</x:v>
+        <x:v>51.65</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2551,10 +2548,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>1364000</x:v>
@@ -2575,21 +2572,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>294.5</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>18</x:v>
@@ -2610,7 +2607,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>19.86</x:v>
+        <x:v>19.84</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2618,10 +2615,10 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>507440</x:v>
@@ -2642,21 +2639,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>206.9</x:v>
+        <x:v>193.9</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>18</x:v>
@@ -2677,7 +2674,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.94</x:v>
+        <x:v>37.1</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2685,10 +2682,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>2000000</x:v>
@@ -2709,13 +2706,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>45.1</x:v>
+        <x:v>44.14</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2723,7 +2720,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>324474</x:v>
@@ -2744,7 +2741,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>10.62</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2755,10 +2752,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>18</x:v>
@@ -2779,7 +2776,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>12.58</x:v>
+        <x:v>12.13</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2787,10 +2784,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>18</x:v>
@@ -2811,7 +2808,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.59</x:v>
+        <x:v>8.74</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2819,10 +2816,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>2000000</x:v>
@@ -2843,7 +2840,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.33</x:v>
+        <x:v>6.35</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2854,10 +2851,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>174500000</x:v>
@@ -2878,21 +2875,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>635229</x:v>
@@ -2913,21 +2910,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>22.04</x:v>
+        <x:v>21.62</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>130000</x:v>
@@ -2948,21 +2945,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.92</x:v>
+        <x:v>24.24</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -2983,7 +2980,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>224.7</x:v>
+        <x:v>230.3</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -2991,10 +2988,10 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>447761</x:v>
@@ -3015,21 +3012,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>37.62</x:v>
+        <x:v>41.38</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>200000</x:v>
@@ -3050,21 +3047,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>10.2</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>946718</x:v>
@@ -3085,21 +3082,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>85.15</x:v>
+        <x:v>81.6</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>18</x:v>
@@ -3120,7 +3117,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>17.85</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3128,10 +3125,10 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>3043115</x:v>
@@ -3152,21 +3149,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>22.6</x:v>
+        <x:v>23.44</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2382736</x:v>
@@ -3193,15 +3190,15 @@
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>18</x:v>
@@ -3222,7 +3219,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>60.3</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3230,10 +3227,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>18</x:v>
@@ -3254,7 +3251,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.44</x:v>
+        <x:v>6.35</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3262,10 +3259,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>18</x:v>
@@ -3286,7 +3283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>39.98</x:v>
+        <x:v>39.28</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3294,10 +3291,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>310000</x:v>
@@ -3318,21 +3315,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.8</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>2000000</x:v>
@@ -3353,7 +3350,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.37</x:v>
+        <x:v>19.33</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3364,10 +3361,10 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>1250000</x:v>
@@ -3388,21 +3385,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.95</x:v>
+        <x:v>2.92</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>12500000</x:v>
@@ -3423,21 +3420,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.15</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>2093944</x:v>
@@ -3458,21 +3455,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>106.8</x:v>
+        <x:v>108.6</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>18</x:v>
@@ -3493,7 +3490,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>40</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3501,10 +3498,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>51245979</x:v>
@@ -3525,7 +3522,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.84</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3536,10 +3533,10 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1584837</x:v>
@@ -3560,13 +3557,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>57.7</x:v>
+        <x:v>56.2</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3574,7 +3571,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>7999148</x:v>
@@ -3595,7 +3592,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>18.95</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3606,10 +3603,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>14000000</x:v>
@@ -3630,7 +3627,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>22.58</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3641,10 +3638,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>1700005</x:v>
@@ -3665,21 +3662,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.28</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>6000000</x:v>
@@ -3700,21 +3697,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>65</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>1675000</x:v>
@@ -3735,21 +3732,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>73.8</x:v>
+        <x:v>72.45</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>18</x:v>
@@ -3770,7 +3767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>41.76</x:v>
+        <x:v>41.12</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3778,10 +3775,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>18</x:v>
@@ -3802,7 +3799,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>9.29</x:v>
+        <x:v>8.37</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3810,10 +3807,10 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1000000</x:v>
@@ -3834,21 +3831,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>8.05</x:v>
+        <x:v>8.15</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>98551</x:v>
@@ -3869,21 +3866,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.51</x:v>
+        <x:v>13.26</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>6049315</x:v>
@@ -3904,21 +3901,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.7</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>37225000</x:v>
@@ -3939,21 +3936,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>3.96</x:v>
+        <x:v>3.84</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1000000</x:v>
@@ -3974,21 +3971,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>220.5</x:v>
+        <x:v>217.1</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>600000</x:v>
@@ -4009,21 +4006,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>14.2</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>11703083</x:v>
@@ -4044,21 +4041,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>238</x:v>
+        <x:v>226.7</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4079,21 +4076,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>3228679</x:v>
@@ -4114,7 +4111,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>13.93</x:v>
+        <x:v>13.67</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4125,10 +4122,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>150000</x:v>
@@ -4149,21 +4146,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.07</x:v>
+        <x:v>7.03</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>18</x:v>
@@ -4184,7 +4181,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>17.92</x:v>
+        <x:v>17.24</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4192,10 +4189,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>366107</x:v>
@@ -4216,13 +4213,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.3</x:v>
+        <x:v>17.48</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -4230,7 +4227,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>120000</x:v>
@@ -4251,21 +4248,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>125.6</x:v>
+        <x:v>116.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>13050000</x:v>
@@ -4286,21 +4283,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>92.85</x:v>
+        <x:v>95.45</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>24225701</x:v>
@@ -4321,21 +4318,21 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.36</x:v>
+        <x:v>5.33</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>1000000</x:v>
@@ -4356,21 +4353,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>392.5</x:v>
+        <x:v>392.75</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>300000</x:v>
@@ -4391,21 +4388,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.71</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>2175097</x:v>
@@ -4426,21 +4423,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>12.7</x:v>
+        <x:v>12.42</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>18</x:v>
@@ -4461,7 +4458,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.31</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4469,10 +4466,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>43000</x:v>
@@ -4493,21 +4490,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>31.22</x:v>
+        <x:v>33.76</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>9937037</x:v>
@@ -4528,21 +4525,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.42</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
@@ -4563,7 +4560,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.54</x:v>
+        <x:v>3.43</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4574,7 +4571,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>13064888</x:v>
@@ -4595,13 +4592,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>30.22</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -4609,7 +4606,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>111673026</x:v>
@@ -4630,21 +4627,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.65</x:v>
+        <x:v>8.71</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4673,10 +4670,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
@@ -4697,7 +4694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>7.67</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4705,10 +4702,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>1100000</x:v>
@@ -4729,21 +4726,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>116.5</x:v>
+        <x:v>113.3</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>5647479</x:v>
@@ -4764,21 +4761,21 @@
         <x:v>5.06</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>12.58</x:v>
+        <x:v>12.13</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>10.16</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1590000</x:v>
@@ -4799,21 +4796,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>39.4</x:v>
+        <x:v>38.5</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1989802</x:v>
@@ -4834,21 +4831,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>125.4</x:v>
+        <x:v>129.9</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>18</x:v>
@@ -4869,7 +4866,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>562</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4877,10 +4874,10 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>300000</x:v>
@@ -4901,21 +4898,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>10.7</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>8291656</x:v>
@@ -4936,21 +4933,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>16.4</x:v>
+        <x:v>16.66</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>76908759</x:v>
@@ -4971,21 +4968,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>30.94</x:v>
+        <x:v>30.42</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5006,7 +5003,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>29</x:v>
+        <x:v>27.82</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5017,10 +5014,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5041,24 +5038,24 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15</x:v>
+        <x:v>15.72</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>31006143</x:v>
+        <x:v>31506143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5067,30 +5064,30 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>321270943</x:v>
+        <x:v>328458443</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.59</x:v>
+        <x:v>1.62</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.56</x:v>
+        <x:v>14.72</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>10.36</x:v>
+        <x:v>10.43</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5111,21 +5108,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>57.6</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5146,7 +5143,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5154,10 +5151,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5184,15 +5181,15 @@
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5219,15 +5216,15 @@
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5248,7 +5245,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>82.55</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5256,10 +5253,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5280,7 +5277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>562</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5288,10 +5285,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5312,7 +5309,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>236.7</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5323,10 +5320,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5347,21 +5344,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.2</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5382,21 +5379,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.12</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5417,21 +5414,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>7.67</x:v>
+        <x:v>6.91</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5452,21 +5449,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>590</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5487,21 +5484,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>562</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5522,21 +5519,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.2</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5557,21 +5554,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.12</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>281228</x:v>
@@ -5592,7 +5589,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>155</x:v>
+        <x:v>153.4</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5603,10 +5600,10 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5627,7 +5624,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>206.9</x:v>
+        <x:v>193.9</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5635,10 +5632,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5659,21 +5656,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5694,21 +5691,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>57</x:v>
+        <x:v>56.6</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5729,21 +5726,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.44</x:v>
+        <x:v>8.46</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5764,21 +5761,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.18</x:v>
+        <x:v>3.16</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5799,13 +5796,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.71</x:v>
+        <x:v>4.66</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5813,7 +5810,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>10195940</x:v>
@@ -5834,21 +5831,21 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>23.96</x:v>
+        <x:v>23.9</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5869,21 +5866,21 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>3.14</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5904,21 +5901,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>93.15</x:v>
+        <x:v>102.4</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5939,21 +5936,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.58</x:v>
+        <x:v>2.39</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5974,21 +5971,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>47.76</x:v>
+        <x:v>51.65</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6009,21 +6006,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>224.7</x:v>
+        <x:v>230.3</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6044,21 +6041,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6079,21 +6076,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>12.01</x:v>
+        <x:v>12.18</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>282</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6114,21 +6111,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6149,21 +6146,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.04</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6184,21 +6181,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>280.75</x:v>
+        <x:v>255.5</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6219,13 +6216,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>18.25</x:v>
+        <x:v>17.78</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,166 +130,169 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.10.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.07.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.06.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.10.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.06.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.09.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
     <x:t>ORGE</x:t>
@@ -1301,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>9.92</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1336,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>18.9</x:v>
+        <x:v>18.13</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1371,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.16</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1403,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.06</x:v>
+        <x:v>6.87</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1438,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>116.5</x:v>
+        <x:v>112.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1470,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>11.68</x:v>
+        <x:v>10.52</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1505,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>27.9</x:v>
+        <x:v>25.12</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1540,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>14.62</x:v>
+        <x:v>13.72</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1575,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.82</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1607,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>23.42</x:v>
+        <x:v>21.14</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1624,7 +1627,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>20459503</x:v>
+        <x:v>20586022</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1633,7 +1636,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>522826291</x:v>
+        <x:v>526783426</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
@@ -1642,10 +1645,10 @@
         <x:v>0.79</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.5</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.55</x:v>
+        <x:v>25.59</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1677,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.31</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1712,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>46.86</x:v>
+        <x:v>42.18</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1747,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.3</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1782,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.54</x:v>
+        <x:v>6.28</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1817,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.13</x:v>
+        <x:v>5.52</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1849,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>128</x:v>
+        <x:v>119.9</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1884,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>7.02</x:v>
+        <x:v>6.32</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1919,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>69.3</x:v>
+        <x:v>69.05</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1954,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23.9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1989,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.54</x:v>
+        <x:v>6.28</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2003,7 +2006,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>88087201</x:v>
+        <x:v>88187201</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>200000000</x:v>
@@ -2012,7 +2015,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>863285832</x:v>
+        <x:v>864156832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
@@ -2021,7 +2024,7 @@
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.71</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.8</x:v>
@@ -2056,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>49.38</x:v>
+        <x:v>45.52</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2091,7 +2094,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>392.75</x:v>
+        <x:v>376.5</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2126,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.5</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2161,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.71</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2196,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.26</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2231,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>21.62</x:v>
+        <x:v>19.46</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2266,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.72</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2301,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.69</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2336,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>36.9</x:v>
+        <x:v>33.44</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2368,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>6.27</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2403,21 +2406,21 @@
         <x:v>1.76</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>41.86</x:v>
+        <x:v>39.54</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>1993951</x:v>
@@ -2438,21 +2441,21 @@
         <x:v>2.49</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>102.4</x:v>
+        <x:v>97.05</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.89</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>18</x:v>
@@ -2473,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>40.72</x:v>
+        <x:v>36.66</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2481,10 +2484,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>3337681</x:v>
@@ -2505,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2516,10 +2519,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>18</x:v>
@@ -2540,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>51.65</x:v>
+        <x:v>47.44</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2548,10 +2551,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>1364000</x:v>
@@ -2572,21 +2575,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>295</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>18</x:v>
@@ -2607,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>19.84</x:v>
+        <x:v>18.41</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2615,10 +2618,10 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>507440</x:v>
@@ -2639,21 +2642,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>193.9</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>18</x:v>
@@ -2674,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.1</x:v>
+        <x:v>33.98</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2682,10 +2685,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>2000000</x:v>
@@ -2706,13 +2709,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2720,7 +2723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>324474</x:v>
@@ -2741,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>9.92</x:v>
+        <x:v>8.98</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2752,10 +2755,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>18</x:v>
@@ -2776,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>12.13</x:v>
+        <x:v>11.32</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2784,10 +2787,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>18</x:v>
@@ -2808,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.74</x:v>
+        <x:v>8.48</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2816,10 +2819,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>2000000</x:v>
@@ -2840,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.35</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2851,10 +2854,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>174500000</x:v>
@@ -2875,13 +2878,13 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.81</x:v>
+        <x:v>2.53</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2889,7 +2892,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>635229</x:v>
@@ -2910,21 +2913,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.62</x:v>
+        <x:v>19.46</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>130000</x:v>
@@ -2945,21 +2948,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.24</x:v>
+        <x:v>22.76</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -2980,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>230.3</x:v>
+        <x:v>228.6</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -2988,10 +2991,10 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>447761</x:v>
@@ -3012,21 +3015,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>41.38</x:v>
+        <x:v>37.26</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>200000</x:v>
@@ -3047,21 +3050,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.99</x:v>
+        <x:v>9.55</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>946718</x:v>
@@ -3082,21 +3085,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>81.6</x:v>
+        <x:v>73.45</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>18</x:v>
@@ -3117,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>17.26</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3125,10 +3128,10 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>3043115</x:v>
@@ -3149,21 +3152,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.44</x:v>
+        <x:v>21.54</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2382736</x:v>
@@ -3184,21 +3187,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>84.7</x:v>
+        <x:v>76.25</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>18</x:v>
@@ -3219,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>59.85</x:v>
+        <x:v>54.5</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3227,10 +3230,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>18</x:v>
@@ -3251,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.35</x:v>
+        <x:v>5.72</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3259,10 +3262,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>18</x:v>
@@ -3283,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>39.28</x:v>
+        <x:v>36.6</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3291,10 +3294,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>310000</x:v>
@@ -3315,21 +3318,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.6</x:v>
+        <x:v>8.01</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>2000000</x:v>
@@ -3350,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>19.33</x:v>
+        <x:v>18.38</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3361,10 +3364,10 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>1250000</x:v>
@@ -3385,21 +3388,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>12500000</x:v>
@@ -3420,21 +3423,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.25</x:v>
+        <x:v>2.07</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>2093944</x:v>
@@ -3455,21 +3458,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>108.6</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>18</x:v>
@@ -3490,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>38.88</x:v>
+        <x:v>35.02</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3498,10 +3501,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>51245979</x:v>
@@ -3522,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3533,10 +3536,10 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1584837</x:v>
@@ -3557,13 +3560,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>56.2</x:v>
+        <x:v>55.35</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3571,7 +3574,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>7999148</x:v>
@@ -3592,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>18.9</x:v>
+        <x:v>18.13</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3603,10 +3606,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>14000000</x:v>
@@ -3627,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>22.2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3638,10 +3641,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>1700005</x:v>
@@ -3662,21 +3665,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>7.2</x:v>
+        <x:v>6.48</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>6000000</x:v>
@@ -3697,21 +3700,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>62.8</x:v>
+        <x:v>56.55</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>1675000</x:v>
@@ -3732,21 +3735,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>72.45</x:v>
+        <x:v>70.1</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>18</x:v>
@@ -3767,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>41.12</x:v>
+        <x:v>37.5</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3775,10 +3778,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>18</x:v>
@@ -3799,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>8.37</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3807,10 +3810,10 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1000000</x:v>
@@ -3831,21 +3834,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>8.15</x:v>
+        <x:v>7.91</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>98551</x:v>
@@ -3866,21 +3869,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>13.26</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>6049315</x:v>
@@ -3901,21 +3904,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.6</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>37225000</x:v>
@@ -3936,21 +3939,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>3.84</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1000000</x:v>
@@ -3971,21 +3974,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>217.1</x:v>
+        <x:v>203.9</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>600000</x:v>
@@ -4006,21 +4009,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>14.5</x:v>
+        <x:v>14.35</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>11703083</x:v>
@@ -4041,21 +4044,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>226.7</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4076,21 +4079,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>33</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>3228679</x:v>
@@ -4111,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>13.67</x:v>
+        <x:v>13.02</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4122,10 +4125,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>150000</x:v>
@@ -4146,21 +4149,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>7.03</x:v>
+        <x:v>6.68</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>18</x:v>
@@ -4181,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>17.24</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4189,10 +4192,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>366107</x:v>
@@ -4213,13 +4216,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>17.48</x:v>
+        <x:v>16.03</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -4227,7 +4230,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>120000</x:v>
@@ -4248,21 +4251,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>116.5</x:v>
+        <x:v>112.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>13050000</x:v>
@@ -4283,21 +4286,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>95.45</x:v>
+        <x:v>90.7</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>24225701</x:v>
@@ -4318,13 +4321,13 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.33</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -4332,7 +4335,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>1000000</x:v>
@@ -4353,21 +4356,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>392.75</x:v>
+        <x:v>376.5</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>300000</x:v>
@@ -4388,21 +4391,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.54</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>2175097</x:v>
@@ -4423,21 +4426,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>12.42</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>18</x:v>
@@ -4458,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>4.03</x:v>
+        <x:v>3.65</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4466,10 +4469,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>43000</x:v>
@@ -4490,21 +4493,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>33.76</x:v>
+        <x:v>32.6</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>9937037</x:v>
@@ -4525,21 +4528,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.42</x:v>
+        <x:v>4.02</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
@@ -4560,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.43</x:v>
+        <x:v>3.09</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4571,7 +4574,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>13064888</x:v>
@@ -4592,13 +4595,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.5</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -4606,7 +4609,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>111673026</x:v>
@@ -4627,21 +4630,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.71</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4662,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.73</x:v>
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4670,10 +4673,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
@@ -4694,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>7.76</x:v>
+        <x:v>7.31</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4702,10 +4705,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>1100000</x:v>
@@ -4726,21 +4729,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>113.3</x:v>
+        <x:v>104.3</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>5647479</x:v>
@@ -4761,21 +4764,21 @@
         <x:v>5.06</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>12.13</x:v>
+        <x:v>11.32</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>10.16</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1590000</x:v>
@@ -4796,21 +4799,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>38.5</x:v>
+        <x:v>34.66</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1989802</x:v>
@@ -4831,21 +4834,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>129.9</x:v>
+        <x:v>128.5</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>18</x:v>
@@ -4866,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4874,10 +4877,10 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>300000</x:v>
@@ -4898,21 +4901,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>10.4</x:v>
+        <x:v>9.42</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>8291656</x:v>
@@ -4933,21 +4936,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>16.66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>76908759</x:v>
@@ -4968,21 +4971,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>30.42</x:v>
+        <x:v>29.74</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5003,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>27.82</x:v>
+        <x:v>26.5</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5014,10 +5017,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5038,21 +5041,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.72</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>31506143</x:v>
@@ -5073,21 +5076,21 @@
         <x:v>1.62</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.72</x:v>
+        <x:v>13.58</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>10.43</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5108,21 +5111,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>58</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5143,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.42</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5151,10 +5154,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5175,21 +5178,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.25</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5210,21 +5213,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>17.8</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5245,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>81.65</x:v>
+        <x:v>76.65</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5253,10 +5256,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5277,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5285,10 +5288,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5309,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>236</x:v>
+        <x:v>228.2</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5320,10 +5323,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5344,21 +5347,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>12.86</x:v>
+        <x:v>12.89</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5379,21 +5382,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2.22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5414,21 +5417,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.91</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5449,21 +5452,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>598</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5484,21 +5487,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5519,21 +5522,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>12.86</x:v>
+        <x:v>12.89</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5554,21 +5557,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>281228</x:v>
@@ -5589,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>153.4</x:v>
+        <x:v>142.2</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5600,10 +5603,10 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5624,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>193.9</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5632,10 +5635,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5656,21 +5659,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.66</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5691,21 +5694,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>56.6</x:v>
+        <x:v>52.6</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5726,21 +5729,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.46</x:v>
+        <x:v>8.51</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5761,21 +5764,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.16</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5796,13 +5799,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.66</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5810,7 +5813,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>10195940</x:v>
@@ -5831,21 +5834,21 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>23.9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5866,21 +5869,21 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>2.96</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5901,21 +5904,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>102.4</x:v>
+        <x:v>97.05</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5936,21 +5939,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.39</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5971,21 +5974,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>51.65</x:v>
+        <x:v>47.44</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6006,21 +6009,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>230.3</x:v>
+        <x:v>228.6</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6041,21 +6044,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.81</x:v>
+        <x:v>2.53</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6076,21 +6079,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>12.18</x:v>
+        <x:v>10.97</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>10000000</x:v>
@@ -6111,21 +6114,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>9.3</x:v>
+        <x:v>8.94</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>3081843</x:v>
@@ -6146,21 +6149,21 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>6.01</x:v>
+        <x:v>5.71</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>1348769</x:v>
@@ -6181,21 +6184,21 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>255.5</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>927506</x:v>
@@ -6216,13 +6219,13 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>17.78</x:v>
+        <x:v>16.05</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,7 +130,7 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>20.05.2026</x:t>
+    <x:t>21.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
@@ -292,13 +292,13 @@
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.05.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.05.2025</x:t>
   </x:si>
   <x:si>
     <x:t>MOPAS</x:t>
@@ -1304,7 +1304,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>8.98</x:v>
+        <x:v>9.87</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1339,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>18.13</x:v>
+        <x:v>18.66</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>7.7</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.87</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>112.5</x:v>
+        <x:v>123.7</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1473,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>10.52</x:v>
+        <x:v>10.55</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1508,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>25.12</x:v>
+        <x:v>26.2</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1543,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>13.72</x:v>
+        <x:v>14.35</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.5</x:v>
+        <x:v>5.77</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1610,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.14</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1627,7 +1627,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>20586022</x:v>
+        <x:v>20946022</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1636,19 +1636,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>526783426</x:v>
+        <x:v>538072666</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.79</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>30.1</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.59</x:v>
+        <x:v>25.69</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>11.6</x:v>
+        <x:v>12.25</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>42.18</x:v>
+        <x:v>46.38</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1750,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.28</x:v>
+        <x:v>6.31</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>5.52</x:v>
+        <x:v>6.07</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>119.9</x:v>
+        <x:v>109.7</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.32</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>69.05</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>61.87</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1992,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.28</x:v>
+        <x:v>6.31</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2006,7 +2006,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>88187201</x:v>
+        <x:v>88687201</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>200000000</x:v>
@@ -2015,19 +2015,19 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>864156832</x:v>
+        <x:v>868401832</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.98</x:v>
+        <x:v>0.99</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.23</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>9.8</x:v>
+        <x:v>9.79</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>38</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>45.52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>376.5</x:v>
+        <x:v>392.75</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>30.1</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
@@ -2164,7 +2164,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.23</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>6.8</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
@@ -2234,7 +2234,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>19.46</x:v>
+        <x:v>20.66</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
@@ -2269,7 +2269,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.79</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.4</x:v>
+        <x:v>7.57</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
@@ -2339,7 +2339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>33.44</x:v>
+        <x:v>36.02</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>5.7</x:v>
+        <x:v>5.65</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>14012000</x:v>
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>79451200</x:v>
@@ -2397,30 +2397,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>554294062</x:v>
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1.76</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>39.54</x:v>
+        <x:v>41.4</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>39.56</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>1993951</x:v>
@@ -2441,13 +2441,13 @@
         <x:v>2.49</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>97.05</x:v>
+        <x:v>106.7</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.89</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -2476,7 +2476,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>36.66</x:v>
+        <x:v>38.92</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2508,7 +2508,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>47.44</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>274</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>18.41</x:v>
+        <x:v>19.29</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2642,13 +2642,13 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>182</x:v>
+        <x:v>198.9</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -2677,7 +2677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>33.98</x:v>
+        <x:v>37.06</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>42</x:v>
+        <x:v>43.66</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>8.98</x:v>
+        <x:v>9.87</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2779,7 +2779,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>11.32</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.48</x:v>
+        <x:v>8.34</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2843,7 +2843,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.04</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2878,7 +2878,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.53</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
@@ -2913,7 +2913,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>19.46</x:v>
+        <x:v>20.66</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
@@ -2948,7 +2948,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>22.76</x:v>
+        <x:v>24.4</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>228.6</x:v>
+        <x:v>230.9</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>37.26</x:v>
+        <x:v>38.64</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>41.13</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.55</x:v>
+        <x:v>9.71</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>73.45</x:v>
+        <x:v>75.15</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>15.6</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>21.54</x:v>
+        <x:v>23.54</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>76.25</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
@@ -3222,7 +3222,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>54.5</x:v>
+        <x:v>58.75</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3254,7 +3254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>5.72</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3286,7 +3286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>36.6</x:v>
+        <x:v>38.58</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.01</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
@@ -3353,7 +3353,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.38</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3388,7 +3388,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.87</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
@@ -3423,7 +3423,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
@@ -3458,7 +3458,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>106</x:v>
+        <x:v>106.5</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
@@ -3493,7 +3493,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>35.02</x:v>
+        <x:v>38.08</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>55.35</x:v>
+        <x:v>58.45</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
@@ -3595,7 +3595,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>18.13</x:v>
+        <x:v>18.66</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3630,7 +3630,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>20</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>6.48</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
@@ -3700,7 +3700,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>56.55</x:v>
+        <x:v>59.9</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>70.1</x:v>
+        <x:v>72.55</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>37.5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.55</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>7.91</x:v>
+        <x:v>8.29</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
@@ -3869,7 +3869,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>12.5</x:v>
+        <x:v>12.88</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
@@ -3904,7 +3904,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.38</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.78</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
@@ -3974,7 +3974,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>203.9</x:v>
+        <x:v>213.4</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>14.35</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>221</x:v>
+        <x:v>224.4</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>30.1</x:v>
+        <x:v>33.1</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
@@ -4114,7 +4114,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>13.02</x:v>
+        <x:v>13.26</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4149,7 +4149,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>6.68</x:v>
+        <x:v>6.86</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>16.18</x:v>
+        <x:v>16.86</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4216,7 +4216,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.03</x:v>
+        <x:v>16.52</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
@@ -4251,7 +4251,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>112.5</x:v>
+        <x:v>123.7</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>90.7</x:v>
+        <x:v>96.3</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
@@ -4321,7 +4321,7 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.1</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
@@ -4356,7 +4356,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>376.5</x:v>
+        <x:v>392.75</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
@@ -4391,7 +4391,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.38</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
@@ -4426,7 +4426,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>11.8</x:v>
+        <x:v>12.09</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.79</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>32.6</x:v>
+        <x:v>35.74</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
@@ -4528,7 +4528,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.02</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
@@ -4563,7 +4563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.09</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4595,7 +4595,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>30.1</x:v>
+        <x:v>31.46</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
@@ -4630,7 +4630,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.23</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.32</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4697,7 +4697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>7.31</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4729,7 +4729,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>104.3</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
@@ -4764,7 +4764,7 @@
         <x:v>5.06</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>11.32</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>10.16</x:v>
@@ -4799,7 +4799,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>34.66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>38.14</x:v>
@@ -4834,7 +4834,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>128.5</x:v>
+        <x:v>141.3</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>573</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4901,7 +4901,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>9.42</x:v>
+        <x:v>10.06</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
@@ -4936,7 +4936,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>15</x:v>
+        <x:v>15.93</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
@@ -4971,7 +4971,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>29.74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>26.5</x:v>
+        <x:v>28.1</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5041,7 +5041,7 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>15.5</x:v>
+        <x:v>16.35</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
@@ -5058,7 +5058,7 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>31506143</x:v>
+        <x:v>31956143</x:v>
       </x:c>
       <x:c r="D112" s="0">
         <x:v>195000000</x:v>
@@ -5067,22 +5067,22 @@
         <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>328458443</x:v>
+        <x:v>334978943</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.62</x:v>
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>13.58</x:v>
+        <x:v>14.93</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>10.43</x:v>
+        <x:v>10.48</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -5111,7 +5111,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>53.2</x:v>
+        <x:v>57.6</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
@@ -5146,7 +5146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.31</x:v>
+        <x:v>2.43</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5178,7 +5178,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>8.88</x:v>
+        <x:v>9.18</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
@@ -5213,7 +5213,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>16.42</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>76.65</x:v>
+        <x:v>79.35</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>573</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5312,7 +5312,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>228.2</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5347,7 +5347,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>12.89</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>2</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>13.82</x:v>
@@ -5417,7 +5417,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.22</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
@@ -5452,7 +5452,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>590</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>573</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
@@ -5522,7 +5522,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>12.89</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
@@ -5557,7 +5557,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>14.58</x:v>
@@ -5592,7 +5592,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>142.2</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>135.2</x:v>
@@ -5627,7 +5627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>182</x:v>
+        <x:v>198.9</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5659,7 +5659,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.57</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
@@ -5694,7 +5694,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>52.6</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
@@ -5729,7 +5729,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.51</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
@@ -5764,7 +5764,7 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>2.85</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.4</x:v>
+        <x:v>4.57</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
@@ -5834,7 +5834,7 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.93</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
@@ -5880,7 +5880,7 @@
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>269</x:v>
@@ -5904,7 +5904,7 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>97.05</x:v>
+        <x:v>106.7</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
@@ -5939,7 +5939,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.16</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
@@ -5974,7 +5974,7 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>47.44</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>228.6</x:v>
+        <x:v>230.9</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
@@ -6044,7 +6044,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.53</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
@@ -6079,7 +6079,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>10.97</x:v>
+        <x:v>12.06</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>63.77</x:v>
@@ -6114,7 +6114,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>8.94</x:v>
+        <x:v>9.83</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>13.33</x:v>
@@ -6149,7 +6149,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>5.71</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>14.27</x:v>
@@ -6184,7 +6184,7 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>230</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>166.26</x:v>
@@ -6219,7 +6219,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>16.05</x:v>
+        <x:v>17.15</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>20.88</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -130,85 +130,88 @@
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.01.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.11.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.01.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.11.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2025</x:t>
   </x:si>
   <x:si>
     <x:t>ESCAR</x:t>
@@ -1304,7 +1307,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>9.87</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>5.49</x:v>
@@ -1339,7 +1342,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>18.66</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>21.09</x:v>
@@ -1374,7 +1377,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>7.95</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1406,7 +1409,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>7.25</x:v>
+        <x:v>7.43</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>6.43</x:v>
@@ -1441,7 +1444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>123.7</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1473,7 +1476,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>10.55</x:v>
+        <x:v>11.53</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>7.13</x:v>
@@ -1508,7 +1511,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>26.2</x:v>
+        <x:v>27.28</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>28.89</x:v>
@@ -1543,7 +1546,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>14.35</x:v>
+        <x:v>14.57</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>15.08</x:v>
@@ -1578,7 +1581,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.77</x:v>
+        <x:v>6.03</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>0</x:v>
@@ -1610,7 +1613,7 @@
         <x:v>2.52</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>21.9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>23.54</x:v>
@@ -1627,7 +1630,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>20946022</x:v>
+        <x:v>21078935</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>80000000</x:v>
@@ -1636,7 +1639,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>538072666</x:v>
+        <x:v>542184197</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
@@ -1645,10 +1648,10 @@
         <x:v>0.81</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>31.46</x:v>
+        <x:v>32.86</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>25.69</x:v>
+        <x:v>25.72</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>38</x:v>
@@ -1680,7 +1683,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>12.25</x:v>
+        <x:v>12.37</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>13.34</x:v>
@@ -1715,7 +1718,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>46.38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>39.18</x:v>
@@ -1750,7 +1753,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>60</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>59.93</x:v>
@@ -1785,7 +1788,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>6.31</x:v>
+        <x:v>6.33</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>48.39</x:v>
@@ -1820,7 +1823,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.07</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>0</x:v>
@@ -1852,7 +1855,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>109.7</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J18" s="0">
         <x:v>64.47</x:v>
@@ -1887,7 +1890,7 @@
         <x:v>1.56</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>6.65</x:v>
+        <x:v>6.94</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>6.75</x:v>
@@ -1957,7 +1960,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>23</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>21.06</x:v>
@@ -1992,7 +1995,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>6.31</x:v>
+        <x:v>6.33</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2024,21 +2027,21 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.69</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>9.79</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>16445115</x:v>
@@ -2059,21 +2062,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>49</x:v>
+        <x:v>48.82</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>1110000</x:v>
@@ -2094,7 +2097,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>392.75</x:v>
+        <x:v>378.75</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>528.86</x:v>
@@ -2108,7 +2111,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>24398659</x:v>
@@ -2129,13 +2132,13 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>31.46</x:v>
+        <x:v>32.86</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2143,7 +2146,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>46563878</x:v>
@@ -2164,21 +2167,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.69</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>226257</x:v>
@@ -2199,21 +2202,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.3</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>24.08</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>1969635</x:v>
@@ -2234,21 +2237,21 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>20.66</x:v>
+        <x:v>21.22</x:v>
       </x:c>
       <x:c r="J29" s="0">
         <x:v>27.31</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>1000000</x:v>
@@ -2269,21 +2272,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>3.79</x:v>
+        <x:v>3.99</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100000</x:v>
@@ -2304,21 +2307,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.57</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>13.09</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>18</x:v>
@@ -2339,7 +2342,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>36.02</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>0</x:v>
@@ -2347,10 +2350,10 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>5831653</x:v>
@@ -2371,21 +2374,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>5.65</x:v>
+        <x:v>5.47</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>14512000</x:v>
@@ -2406,21 +2409,21 @@
         <x:v>1.83</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>41.4</x:v>
+        <x:v>42.04</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>39.62</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>1993951</x:v>
@@ -2441,21 +2444,21 @@
         <x:v>2.49</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>106.7</x:v>
+        <x:v>103.8</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>68.89</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>18</x:v>
@@ -2476,7 +2479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>38.92</x:v>
+        <x:v>39.9</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>0</x:v>
@@ -2484,10 +2487,10 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>3337681</x:v>
@@ -2508,7 +2511,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>6.14</x:v>
@@ -2519,10 +2522,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>18</x:v>
@@ -2543,7 +2546,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>50.35</x:v>
+        <x:v>55.35</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2551,10 +2554,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>1364000</x:v>
@@ -2575,21 +2578,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>288</x:v>
+        <x:v>297.5</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>18</x:v>
@@ -2610,7 +2613,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.58</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>0</x:v>
@@ -2618,10 +2621,10 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>507440</x:v>
@@ -2642,21 +2645,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>198.9</x:v>
+        <x:v>218.7</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>18</x:v>
@@ -2677,7 +2680,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.06</x:v>
+        <x:v>37.24</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>0</x:v>
@@ -2685,10 +2688,10 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>2000000</x:v>
@@ -2709,13 +2712,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>43.66</x:v>
+        <x:v>44.74</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2723,7 +2726,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>324474</x:v>
@@ -2744,7 +2747,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>9.87</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>5.49</x:v>
@@ -2755,10 +2758,10 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>18</x:v>
@@ -2779,7 +2782,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>11.68</x:v>
+        <x:v>12.04</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>0</x:v>
@@ -2787,10 +2790,10 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>18</x:v>
@@ -2811,7 +2814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.34</x:v>
+        <x:v>8.14</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>0</x:v>
@@ -2819,10 +2822,10 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>2000000</x:v>
@@ -2843,7 +2846,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>6.22</x:v>
+        <x:v>6.29</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>6.12</x:v>
@@ -2854,10 +2857,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>174500000</x:v>
@@ -2875,24 +2878,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>635229</x:v>
@@ -2913,21 +2916,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>20.66</x:v>
+        <x:v>21.22</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>130000</x:v>
@@ -2948,21 +2951,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>24.4</x:v>
+        <x:v>25.6</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>18</x:v>
@@ -2983,7 +2986,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>230.9</x:v>
+        <x:v>234.3</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>0</x:v>
@@ -2991,10 +2994,10 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>447761</x:v>
@@ -3021,15 +3024,15 @@
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>200000</x:v>
@@ -3050,21 +3053,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>9.71</x:v>
+        <x:v>9.98</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>946718</x:v>
@@ -3085,21 +3088,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>75.15</x:v>
+        <x:v>77.95</x:v>
       </x:c>
       <x:c r="J54" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>18</x:v>
@@ -3120,7 +3123,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>16.8</x:v>
+        <x:v>17.4</x:v>
       </x:c>
       <x:c r="J55" s="0">
         <x:v>0</x:v>
@@ -3128,10 +3131,10 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>3043115</x:v>
@@ -3152,21 +3155,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>23.54</x:v>
+        <x:v>22.9</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2382736</x:v>
@@ -3187,21 +3190,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>77.8</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>18</x:v>
@@ -3222,7 +3225,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>58.75</x:v>
+        <x:v>59.1</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>0</x:v>
@@ -3230,10 +3233,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>18</x:v>
@@ -3254,7 +3257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.26</x:v>
+        <x:v>6.23</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>0</x:v>
@@ -3262,10 +3265,10 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>18</x:v>
@@ -3286,7 +3289,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>38.58</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>0</x:v>
@@ -3294,10 +3297,10 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>310000</x:v>
@@ -3318,21 +3321,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>8.39</x:v>
+        <x:v>9.22</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>2000000</x:v>
@@ -3353,7 +3356,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.9</x:v>
+        <x:v>18.89</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>15.68</x:v>
@@ -3364,10 +3367,10 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>1250000</x:v>
@@ -3388,21 +3391,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.87</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>8.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>12500000</x:v>
@@ -3423,21 +3426,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.2</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>2093944</x:v>
@@ -3458,21 +3461,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>106.5</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="J65" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>18</x:v>
@@ -3493,7 +3496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>38.08</x:v>
+        <x:v>41.88</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3501,10 +3504,10 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>51245979</x:v>
@@ -3525,7 +3528,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.45</x:v>
@@ -3536,10 +3539,10 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1584837</x:v>
@@ -3560,13 +3563,13 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>58.45</x:v>
+        <x:v>59.3</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3574,7 +3577,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>7999148</x:v>
@@ -3595,7 +3598,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>18.66</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="J69" s="0">
         <x:v>21.09</x:v>
@@ -3606,10 +3609,10 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>14000000</x:v>
@@ -3630,7 +3633,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>21.6</x:v>
+        <x:v>21.52</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>16.87</x:v>
@@ -3641,10 +3644,10 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>1700005</x:v>
@@ -3665,21 +3668,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>6.9</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>6000000</x:v>
@@ -3700,21 +3703,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>59.9</x:v>
+        <x:v>65.85</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>1675000</x:v>
@@ -3735,21 +3738,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>72.55</x:v>
+        <x:v>79.8</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>18</x:v>
@@ -3770,7 +3773,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>40</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>0</x:v>
@@ -3778,10 +3781,10 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>18</x:v>
@@ -3802,7 +3805,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>7.89</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3810,10 +3813,10 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1000000</x:v>
@@ -3834,21 +3837,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>8.29</x:v>
+        <x:v>8.86</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>98551</x:v>
@@ -3869,21 +3872,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>12.88</x:v>
+        <x:v>13.08</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>6049315</x:v>
@@ -3904,21 +3907,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.6</x:v>
+        <x:v>11.83</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>37225000</x:v>
@@ -3939,21 +3942,21 @@
         <x:v>6.89</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>3.78</x:v>
+        <x:v>3.87</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1000000</x:v>
@@ -3974,21 +3977,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>213.4</x:v>
+        <x:v>217.1</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>600000</x:v>
@@ -4009,21 +4012,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>12.99</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>11703083</x:v>
@@ -4044,21 +4047,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>224.4</x:v>
+        <x:v>216.9</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>5100000</x:v>
@@ -4079,21 +4082,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>33.1</x:v>
+        <x:v>35.34</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>3228679</x:v>
@@ -4114,7 +4117,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>13.26</x:v>
+        <x:v>13.42</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>15.92</x:v>
@@ -4125,10 +4128,10 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>150000</x:v>
@@ -4149,21 +4152,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>6.86</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>18</x:v>
@@ -4184,7 +4187,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>16.86</x:v>
+        <x:v>17.22</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0</x:v>
@@ -4192,10 +4195,10 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>366107</x:v>
@@ -4216,13 +4219,13 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.52</x:v>
+        <x:v>16.96</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -4230,7 +4233,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>120000</x:v>
@@ -4251,21 +4254,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>123.7</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>13050000</x:v>
@@ -4286,21 +4289,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>96.3</x:v>
+        <x:v>96.9</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>24225701</x:v>
@@ -4321,21 +4324,21 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>5.13</x:v>
+        <x:v>5.33</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>4.54</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>1000000</x:v>
@@ -4356,21 +4359,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>392.75</x:v>
+        <x:v>378.75</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>300000</x:v>
@@ -4391,21 +4394,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>2175097</x:v>
@@ -4426,21 +4429,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>12.09</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>18</x:v>
@@ -4461,7 +4464,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>3.79</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4469,10 +4472,10 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>43000</x:v>
@@ -4493,21 +4496,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>35.74</x:v>
+        <x:v>33.32</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>23.83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>9937037</x:v>
@@ -4528,21 +4531,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>4.23</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
@@ -4563,7 +4566,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>0</x:v>
@@ -4574,7 +4577,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>13064888</x:v>
@@ -4595,13 +4598,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>31.46</x:v>
+        <x:v>32.86</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -4609,7 +4612,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>111673026</x:v>
@@ -4630,21 +4633,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.69</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4665,7 +4668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>4.52</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>0</x:v>
@@ -4673,10 +4676,10 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
@@ -4697,7 +4700,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>7.6</x:v>
+        <x:v>7.73</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>0</x:v>
@@ -4705,10 +4708,10 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>1100000</x:v>
@@ -4729,21 +4732,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>5647479</x:v>
@@ -4764,21 +4767,21 @@
         <x:v>5.06</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>11.68</x:v>
+        <x:v>12.04</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>10.16</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>1590000</x:v>
@@ -4805,15 +4808,15 @@
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>1989802</x:v>
@@ -4834,21 +4837,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>141.3</x:v>
+        <x:v>155.4</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>18</x:v>
@@ -4869,7 +4872,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>586</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>0</x:v>
@@ -4877,10 +4880,10 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C107" s="0">
         <x:v>300000</x:v>
@@ -4901,21 +4904,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>10.06</x:v>
+        <x:v>10.07</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>8291656</x:v>
@@ -4936,21 +4939,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>15.93</x:v>
+        <x:v>16.37</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>76908759</x:v>
@@ -4971,21 +4974,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>30</x:v>
+        <x:v>31.48</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>25.74</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>2975773</x:v>
@@ -5006,7 +5009,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>28.1</x:v>
+        <x:v>30.06</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>15.05</x:v>
@@ -5017,10 +5020,10 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>10994323</x:v>
@@ -5041,21 +5044,21 @@
         <x:v>5.09</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>16.35</x:v>
+        <x:v>16.94</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>16.65</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>31956143</x:v>
@@ -5076,21 +5079,21 @@
         <x:v>1.64</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>14.93</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>10.48</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
         <x:v>5100000</x:v>
@@ -5111,21 +5114,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>57.6</x:v>
+        <x:v>57.95</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>18</x:v>
@@ -5146,7 +5149,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>2.43</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>0</x:v>
@@ -5154,10 +5157,10 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>5000000</x:v>
@@ -5178,21 +5181,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>9.18</x:v>
+        <x:v>9.2</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>590777</x:v>
@@ -5213,21 +5216,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>16.95</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -5248,7 +5251,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>79.35</x:v>
+        <x:v>80.3</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>0</x:v>
@@ -5256,10 +5259,10 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -5280,7 +5283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>586</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5288,10 +5291,10 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>53584</x:v>
@@ -5312,7 +5315,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>235</x:v>
+        <x:v>231.9</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>154.36</x:v>
@@ -5323,10 +5326,10 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>7550000</x:v>
@@ -5347,21 +5350,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.88</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C121" s="0">
         <x:v>2097716</x:v>
@@ -5388,15 +5391,15 @@
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C122" s="0">
         <x:v>5185302</x:v>
@@ -5417,21 +5420,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>6.12</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J122" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>669111</x:v>
@@ -5452,21 +5455,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>610</x:v>
+        <x:v>615.5</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>38840</x:v>
@@ -5487,21 +5490,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>586</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C125" s="0">
         <x:v>2250000</x:v>
@@ -5522,21 +5525,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.88</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>1500000</x:v>
@@ -5563,18 +5566,18 @@
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>281228</x:v>
+        <x:v>344326</x:v>
       </x:c>
       <x:c r="D127" s="0">
         <x:v>8299326</x:v>
@@ -5583,30 +5586,30 @@
         <x:v>600000000</x:v>
       </x:c>
       <x:c r="F127" s="0">
-        <x:v>38021885</x:v>
+        <x:v>47341196</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>151</x:v>
+        <x:v>152.9</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>135.2</x:v>
+        <x:v>137.49</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -5627,7 +5630,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>198.9</x:v>
+        <x:v>218.7</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>0</x:v>
@@ -5635,10 +5638,10 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>845945</x:v>
@@ -5659,21 +5662,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>21446</x:v>
@@ -5694,21 +5697,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>55.65</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>850000</x:v>
@@ -5729,21 +5732,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>8.73</x:v>
+        <x:v>8.78</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>7.7</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>15000000</x:v>
@@ -5764,21 +5767,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.02</x:v>
+        <x:v>3.17</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>6397124</x:v>
@@ -5799,13 +5802,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.57</x:v>
+        <x:v>4.69</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
@@ -5813,7 +5816,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>10195940</x:v>
@@ -5834,21 +5837,21 @@
         <x:v>2.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>23</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>21.71</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C135" s="0">
         <x:v>9350000</x:v>
@@ -5869,21 +5872,21 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>2.93</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>1468255</x:v>
@@ -5904,21 +5907,21 @@
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>106.7</x:v>
+        <x:v>103.8</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>500000</x:v>
@@ -5939,21 +5942,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.37</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>725000</x:v>
@@ -5974,21 +5977,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>50.35</x:v>
+        <x:v>55.35</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C139" s="0">
         <x:v>1060056</x:v>
@@ -6009,21 +6012,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>230.9</x:v>
+        <x:v>234.3</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>132750000</x:v>
@@ -6041,24 +6044,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>373000</x:v>
@@ -6079,21 +6082,21 @@
         <x:v>0.02</x:v>
       <